--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -2953,10 +2953,10 @@
         <v>0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-33.2</v>
+        <v>-33.24</v>
       </c>
       <c r="G21" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="H21" t="n">
         <v>0.02</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="K21" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="L21" t="n">
         <v>0.49</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:CA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,100 +518,196 @@
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>δ13C (‰ v.s.V-PDB)</t>
+          <t>[C]%</t>
         </is>
       </c>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>height_2024</t>
+          <t>δ13C (‰ v.s.V-PDB)</t>
         </is>
       </c>
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean toughness (kN/m)</t>
+          <t>height_2024</t>
         </is>
       </c>
       <c r="U1" s="1" t="n"/>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean thickness (mm)</t>
+          <t>force to punch (kN/m)</t>
         </is>
       </c>
       <c r="W1" s="1" t="n"/>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Leaf fresh weight (g)</t>
+          <t>thickness (mm)</t>
         </is>
       </c>
       <c r="Y1" s="1" t="n"/>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Leaf dry weight (g)</t>
+          <t>Leaf fresh weight (g)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="n"/>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Leaf area (cm²)</t>
+          <t>Leaf dry weight (g)</t>
         </is>
       </c>
       <c r="AC1" s="1" t="n"/>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (g/cm²)</t>
+          <t>Leaf area (cm²)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="n"/>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>area_basal_m2</t>
+          <t>Specific leaf area (g/cm²)</t>
         </is>
       </c>
       <c r="AG1" s="1" t="n"/>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>area_basal_m2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="n"/>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>N_P</t>
+          <t>number of leaves</t>
         </is>
       </c>
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>C:N</t>
+          <t>dry matter content (mg/g)</t>
         </is>
       </c>
       <c r="AM1" s="1" t="n"/>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>△13C_cell</t>
+          <t>C (mg/g)</t>
         </is>
       </c>
       <c r="AO1" s="1" t="n"/>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Ci</t>
+          <t>N (mg/g)</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="n"/>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Ci/Ca</t>
+          <t>P (mg/g)</t>
         </is>
       </c>
       <c r="AS1" s="1" t="n"/>
       <c r="AT1" s="1" t="inlineStr">
         <is>
+          <t>Al (mg/g)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="n"/>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Ca (mg/g)</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="n"/>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Fe (mg/g)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="n"/>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>K (mg/g)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="n"/>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Mg (mg/g)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="n"/>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Na (mg/g)</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="n"/>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>S (mg/g)</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="n"/>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>△13C_cell</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="n"/>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Ci</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="n"/>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Ci/Ca</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="n"/>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
           <t>iWUE (μmol/mol)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="n"/>
+      <c r="BO1" s="1" t="n"/>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>annual_precipitation_mm</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="n"/>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>elevation_m</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="n"/>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_annual_temperature_C</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="n"/>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="n"/>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>C:N</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="n"/>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>13dC/18dO</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -840,6 +936,166 @@
           <t>std</t>
         </is>
       </c>
+      <c r="AV2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="AW2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="AX2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="AY2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="AZ2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BA2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BB2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BC2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BD2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BE2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BF2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BG2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BH2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BI2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BJ2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BK2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BL2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BM2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BN2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BO2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BP2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BQ2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BR2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BS2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BT2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BU2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BV2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BW2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BX2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="BY2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="BZ2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CA2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -904,68 +1160,180 @@
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R4" t="n">
         <v>-26.51</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.89</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>1.75</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.15</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.54</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.05</v>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.22</v>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
       <c r="AL4" t="n">
+        <v>429.04</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>515.61</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>274.06</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
         <v>43.02</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="BY4" t="n">
         <v>6.87</v>
       </c>
-      <c r="AN4" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>274.06</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>93.16</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10.84</v>
+      <c r="BZ4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
@@ -1015,68 +1383,180 @@
         <v>1.14</v>
       </c>
       <c r="P5" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
         <v>-26.57</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>1.13</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
         <v>1.66</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.12</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.52</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.03</v>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.22</v>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>519.77</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>275.16</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
         <v>37.7</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BY5" t="n">
         <v>4.76</v>
       </c>
-      <c r="AN5" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>275.16</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>92.47</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>13.88</v>
+      <c r="BZ5" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="6">
@@ -1126,68 +1606,180 @@
         <v>1.12</v>
       </c>
       <c r="P6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R6" t="n">
         <v>-26.77</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>1.45</v>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>1.64</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.21</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.53</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.03</v>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.41</v>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
       <c r="AL6" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>515.91</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>279.11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
         <v>40.44</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BY6" t="n">
         <v>4.32</v>
       </c>
-      <c r="AN6" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>279.11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="BZ6" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="CA6" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>17.73</v>
       </c>
     </row>
     <row r="7">
@@ -1237,68 +1829,180 @@
         <v>1.57</v>
       </c>
       <c r="P7" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R7" t="n">
         <v>-27.06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>1.51</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>1.64</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.12</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.53</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
       <c r="AL7" t="n">
+        <v>426.71</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>510.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>284.71</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
         <v>44.34</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BY7" t="n">
         <v>5.43</v>
       </c>
-      <c r="AN7" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>284.71</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>18.45</v>
+      <c r="BZ7" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="8">
@@ -1352,92 +2056,148 @@
         <v>0.53</v>
       </c>
       <c r="P8" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R8" t="n">
         <v>-30.63</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.42</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>14.9</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3.83</v>
       </c>
-      <c r="T8" t="n">
-        <v>36</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>0.96</v>
       </c>
       <c r="W8" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="X8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z8" t="n">
         <v>18.64</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>5.97</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>8.59</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>2.67</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>789.23</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>252.02</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>92.05</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>10.83</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="n">
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
         <v>24.51</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="BY8" t="n">
         <v>2.92</v>
       </c>
-      <c r="AN8" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>354.96</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="BZ8" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="CA8" t="n">
         <v>0.02</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.21</v>
       </c>
     </row>
     <row r="9">
@@ -1475,65 +2235,109 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-31.8</v>
+        <v>42.05</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>15.6</v>
+        <v>-31.8</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>32.63</v>
+        <v>15.6</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>7.38</v>
+        <v>16.6</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>827</v>
+        <v>7.38</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>112.06</v>
+        <v>827</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
+        <v>112.06</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="n">
         <v>22.29</v>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>23.46</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>378.08</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="CA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -1582,92 +2386,148 @@
         <v>2.31</v>
       </c>
       <c r="P10" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R10" t="n">
         <v>-30.88</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.36</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>14.08</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>5.91</v>
       </c>
-      <c r="T10" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7.41</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0.97</v>
       </c>
       <c r="W10" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="X10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z10" t="n">
         <v>19.36</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>9.26</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>4.96</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>705.84</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>95.02</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>91.5</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>38.65</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="n">
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
         <v>18.28</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BY10" t="n">
         <v>1.73</v>
       </c>
-      <c r="AN10" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>359.8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.45</v>
+      <c r="BZ10" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
@@ -1717,92 +2577,148 @@
         <v>2.73</v>
       </c>
       <c r="P11" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R11" t="n">
         <v>-29.84</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>1.24</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>14.55</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>2.55</v>
       </c>
-      <c r="T11" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.34</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>0.98</v>
       </c>
       <c r="W11" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="X11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z11" t="n">
         <v>16.71</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>1.99</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>7.54</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.77</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>720.42</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>95.65000000000001</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>6.27</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
         <v>22.65</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="BY11" t="n">
         <v>3.13</v>
       </c>
-      <c r="AN11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>339.45</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>15.26</v>
+      <c r="BZ11" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -1856,92 +2772,148 @@
         <v>0.71</v>
       </c>
       <c r="P12" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R12" t="n">
         <v>-26.81</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>1.44</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.45</v>
       </c>
-      <c r="T12" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="U12" t="n">
-        <v>7.51</v>
-      </c>
       <c r="V12" t="n">
-        <v>2.76</v>
+        <v>0.85</v>
       </c>
       <c r="W12" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="X12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z12" t="n">
         <v>19.56</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>1.69</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>5.44</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>1.24</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>360.5</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>26.75</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>68.88</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>16.18</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="n">
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
         <v>30.78</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="BY12" t="n">
         <v>2.77</v>
       </c>
-      <c r="AN12" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>279.79</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>28.28</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>89.58</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>17.68</v>
+      <c r="BZ12" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
@@ -1991,92 +2963,148 @@
         <v>1.99</v>
       </c>
       <c r="P13" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R13" t="n">
         <v>-26.35</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>2.06</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>5.83</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>1.83</v>
       </c>
-      <c r="T13" t="n">
-        <v>33.87</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7.33</v>
-      </c>
       <c r="V13" t="n">
-        <v>2.74</v>
+        <v>0.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="X13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z13" t="n">
         <v>16.19</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>6.75</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>5.01</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>2.33</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>294.31</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>117.09</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>60.87</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>6.61</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="n">
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>270.97</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>95.09</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
         <v>25.77</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="BY13" t="n">
         <v>5.26</v>
       </c>
-      <c r="AN13" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>270.97</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>95.09</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>25.19</v>
+      <c r="BZ13" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">
@@ -2126,92 +3154,148 @@
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R14" t="n">
         <v>-24.85</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>1.27</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>5.33</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>1.04</v>
       </c>
-      <c r="T14" t="n">
-        <v>33.92</v>
-      </c>
-      <c r="U14" t="n">
-        <v>7.32</v>
-      </c>
       <c r="V14" t="n">
-        <v>2.78</v>
+        <v>0.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="X14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z14" t="n">
         <v>17.95</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>3.71</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>4.73</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.98</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>310.01</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>55.44</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>65.98</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>5.04</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="n">
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>241.54</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>113.48</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
         <v>26.1</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="BY14" t="n">
         <v>2.81</v>
       </c>
-      <c r="AN14" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>241.54</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>113.48</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>15.43</v>
+      <c r="BZ14" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -2261,92 +3345,148 @@
         <v>1.31</v>
       </c>
       <c r="P15" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="R15" t="n">
         <v>-27.29</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>1.59</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>4.03</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>1.11</v>
       </c>
-      <c r="T15" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="V15" t="n">
-        <v>2.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="X15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z15" t="n">
         <v>23.2</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>5.08</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>5.79</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>431.72</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>97.78</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>75.91</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>12.42</v>
       </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="n">
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>289.26</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
         <v>28.12</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="BY15" t="n">
         <v>2.51</v>
       </c>
-      <c r="AN15" t="n">
-        <v>18.72</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>289.26</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>83.66</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>19.44</v>
+      <c r="BZ15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
@@ -2400,68 +3540,180 @@
         <v>0.52</v>
       </c>
       <c r="P16" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R16" t="n">
         <v>-27.79</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>1.15</v>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>1.5</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.12</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.48</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.03</v>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.79</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
       <c r="AL16" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>500.27</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>299.16</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
         <v>51.73</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="BY16" t="n">
         <v>11.71</v>
       </c>
-      <c r="AN16" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>299.16</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>77.47</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>14.13</v>
+      <c r="BZ16" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -2511,68 +3763,180 @@
         <v>1.73</v>
       </c>
       <c r="P17" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="R17" t="n">
         <v>-27.24</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.92</v>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>1.48</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.11</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.46</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>0.03</v>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.48</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AJ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
       <c r="AL17" t="n">
+        <v>493.11</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>495.57</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>288.34</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
         <v>47.43</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="BY17" t="n">
         <v>4.13</v>
       </c>
-      <c r="AN17" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>288.34</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>84.23999999999999</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>11.28</v>
+      <c r="BZ17" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="18">
@@ -2622,68 +3986,180 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P18" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="R18" t="n">
         <v>-27.27</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>1.48</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.09</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.47</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.02</v>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.83</v>
+      </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AJ18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
       <c r="AL18" t="n">
+        <v>478.69</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>492.06</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
         <v>47.79</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="BY18" t="n">
         <v>4.16</v>
       </c>
-      <c r="AN18" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>83.88</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>12.23</v>
+      <c r="BZ18" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="19">
@@ -2733,68 +4209,180 @@
         <v>0.95</v>
       </c>
       <c r="P19" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R19" t="n">
         <v>-27.34</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.66</v>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
         <v>1.46</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.11</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.47</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.02</v>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.83</v>
+      </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
       <c r="AL19" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>491.78</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>290.17</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
         <v>58.04</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="BY19" t="n">
         <v>6.25</v>
       </c>
-      <c r="AN19" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>290.17</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AS19" t="n">
+      <c r="BZ19" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="CA19" t="n">
         <v>0.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2848,92 +4436,148 @@
         <v>1.47</v>
       </c>
       <c r="P20" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R20" t="n">
         <v>-31.55</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.76</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>14.74</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>3.19</v>
       </c>
-      <c r="T20" t="n">
-        <v>29.47</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.94</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>0.78</v>
       </c>
       <c r="W20" t="n">
         <v>0.08</v>
       </c>
       <c r="X20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z20" t="n">
         <v>33.84</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>11.77</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>17.25</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>5.19</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>1383.64</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>423.28</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>80.27</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>8.75</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="n">
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
         <v>31.55</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="BY20" t="n">
         <v>2.43</v>
       </c>
-      <c r="AN20" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>373.2</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>9.390000000000001</v>
+      <c r="BZ20" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="21">
@@ -2983,92 +4627,148 @@
         <v>1.39</v>
       </c>
       <c r="P21" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R21" t="n">
         <v>-30.37</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>1.83</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>12.58</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>4.95</v>
       </c>
-      <c r="T21" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6.68</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="W21" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="X21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z21" t="n">
         <v>34.73</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>8.74</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>19.18</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>3.49</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>1481.98</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>393.07</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>15.42</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="n">
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
         <v>30.55</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="BY21" t="n">
         <v>2.74</v>
       </c>
-      <c r="AN21" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>349.83</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>22.53</v>
+      <c r="BZ21" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3118,92 +4818,148 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="R22" t="n">
         <v>-31.74</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>1.35</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>14.6</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>4.56</v>
       </c>
-      <c r="T22" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5.02</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>0.85</v>
       </c>
       <c r="W22" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="X22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z22" t="n">
         <v>28.98</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>10.17</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>14.71</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>5.75</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>1332.49</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>479.13</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>101.47</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>52.75</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>376.84</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
         <v>29.27</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="BY22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AN22" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>376.84</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>26.65</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>16.66</v>
+      <c r="BZ22" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3253,92 +5009,148 @@
         <v>1.24</v>
       </c>
       <c r="P23" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R23" t="n">
         <v>-31.27</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.93</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>12.84</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>2.52</v>
       </c>
-      <c r="T23" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5.06</v>
-      </c>
       <c r="V23" t="n">
-        <v>24.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>66.70999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="X23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z23" t="n">
         <v>36.82</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>6.78</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>18.29</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>3.36</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>1415.82</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>289.8</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>78.02</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>10.48</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>0.04</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="n">
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
         <v>28.9</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="BY23" t="n">
         <v>2.18</v>
       </c>
-      <c r="AN23" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>367.57</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>11.53</v>
+      <c r="BZ23" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
@@ -3392,92 +5204,148 @@
         <v>1.65</v>
       </c>
       <c r="P24" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R24" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.27</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>4.5</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>1.12</v>
       </c>
-      <c r="T24" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.64</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.93</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.42</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>29.36</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>4.07</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>5.89</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.01</v>
       </c>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="n">
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>297.29</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
         <v>43.15</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="BY24" t="n">
         <v>5.79</v>
       </c>
-      <c r="AN24" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>297.29</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>78.64</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.3</v>
+      <c r="BZ24" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="25">
@@ -3527,92 +5395,148 @@
         <v>0.77</v>
       </c>
       <c r="P25" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R25" t="n">
         <v>-28.06</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.9</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>5.8</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>1.15</v>
       </c>
-      <c r="T25" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.59</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="X25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.46</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>0.52</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>35.25</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>12.72</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>69.55</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.01</v>
       </c>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="n">
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>304.29</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
         <v>39.49</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="BY25" t="n">
         <v>5.23</v>
       </c>
-      <c r="AN25" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>304.29</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>11</v>
+      <c r="BZ25" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
@@ -3662,92 +5586,148 @@
         <v>0.75</v>
       </c>
       <c r="P26" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R26" t="n">
         <v>-29.03</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.79</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>4.75</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>1.77</v>
       </c>
-      <c r="T26" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.34</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="W26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.1</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>38.68</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>3.7</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>6.39</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="n">
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>323.43</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
         <v>41.18</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="BY26" t="n">
         <v>0.31</v>
       </c>
-      <c r="AN26" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>323.43</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9.74</v>
+      <c r="BZ26" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3797,101 +5777,164 @@
         <v>0.88</v>
       </c>
       <c r="P27" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R27" t="n">
         <v>-28.38</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>1.13</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>5.08</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>1.96</v>
       </c>
-      <c r="T27" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.19</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.58</v>
+        <v>0.86</v>
       </c>
       <c r="W27" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="X27" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.08</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.49</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.04</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>35.36</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>2.13</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>72.58</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>4.07</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="n">
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>310.66</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
         <v>41.73</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="BY27" t="n">
         <v>5.19</v>
       </c>
-      <c r="AN27" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>310.66</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>70.28</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>13.86</v>
+      <c r="BZ27" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="44">
     <mergeCell ref="C1:E1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="A16:A19"/>
+    <mergeCell ref="BV1:BW1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="V1:W1"/>
@@ -3899,11 +5942,19 @@
     <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="BX1:BY1"/>
+    <mergeCell ref="BF1:BG1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="T1:U1"/>
+    <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="L1:M1"/>
+    <mergeCell ref="BD1:BE1"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BN1:BO1"/>
+    <mergeCell ref="BZ1:CA1"/>
+    <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="X1:Y1"/>
@@ -3911,6 +5962,7 @@
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="BT1:BU1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="F1:G1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -481,7 +481,7 @@
       <c r="B1" s="1" t="inlineStr"/>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>[C_b]%</t>
+          <t>[C_b]</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
@@ -518,7 +518,7 @@
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>[C]%</t>
+          <t>[C]</t>
         </is>
       </c>
       <c r="Q1" s="1" t="n"/>
@@ -2117,8 +2117,12 @@
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>462.21</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>25.6</v>
+      </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
@@ -2276,7 +2280,9 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>444.58</v>
+      </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
@@ -2447,8 +2453,12 @@
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AL10" t="n">
+        <v>461.81</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>65.73</v>
+      </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
@@ -2638,8 +2648,12 @@
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>452.38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>16.12</v>
+      </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
@@ -2833,8 +2847,12 @@
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AL12" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>45.98</v>
+      </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
@@ -3024,8 +3042,12 @@
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>303.57</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>21.05</v>
+      </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
@@ -3215,8 +3237,12 @@
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>263.47</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4.56</v>
+      </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
@@ -3406,8 +3432,12 @@
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>248.34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>11.95</v>
+      </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
@@ -4497,8 +4527,12 @@
       </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>517.2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>36.65</v>
+      </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
@@ -4688,8 +4722,12 @@
       </c>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>567.65</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>103.37</v>
+      </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
@@ -4879,8 +4917,12 @@
       </c>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>498.3</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>49.19</v>
+      </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
@@ -5070,8 +5112,12 @@
       </c>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>497.57</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>47.07</v>
+      </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
@@ -5265,8 +5311,12 @@
       </c>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>458.37</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>24.12</v>
+      </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
@@ -5456,8 +5506,12 @@
       </c>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>484.91</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>63.86</v>
+      </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
@@ -5647,8 +5701,12 @@
       </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AL26" t="n">
+        <v>447.24</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>11.29</v>
+      </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
@@ -5838,8 +5896,12 @@
       </c>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>29.2</v>
+      </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA27"/>
+  <dimension ref="A1:CE27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,18 @@
         </is>
       </c>
       <c r="CA1" s="1" t="n"/>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Narea</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="n"/>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Carea</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1092,6 +1104,26 @@
         </is>
       </c>
       <c r="CA2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="CB2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CC2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="CD2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CE2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
@@ -1335,6 +1367,10 @@
       <c r="CA4" t="n">
         <v>0.05</v>
       </c>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -1558,6 +1594,10 @@
       <c r="CA5" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -1781,6 +1821,10 @@
       <c r="CA6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -2004,6 +2048,10 @@
       <c r="CA7" t="n">
         <v>0.09</v>
       </c>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2202,6 +2250,18 @@
       </c>
       <c r="CA8" t="n">
         <v>0.02</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -2344,6 +2404,14 @@
         <v>-1.02</v>
       </c>
       <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="CE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2539,6 +2607,18 @@
       <c r="CA10" t="n">
         <v>0.08</v>
       </c>
+      <c r="CB10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -2734,6 +2814,18 @@
       <c r="CA11" t="n">
         <v>0.11</v>
       </c>
+      <c r="CB11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2933,6 +3025,18 @@
       <c r="CA12" t="n">
         <v>0.08</v>
       </c>
+      <c r="CB12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>1.65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -3128,6 +3232,18 @@
       <c r="CA13" t="n">
         <v>0.12</v>
       </c>
+      <c r="CB13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -3323,6 +3439,18 @@
       <c r="CA14" t="n">
         <v>0.1</v>
       </c>
+      <c r="CB14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -3518,6 +3646,18 @@
       <c r="CA15" t="n">
         <v>0.08</v>
       </c>
+      <c r="CB15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3745,6 +3885,10 @@
       <c r="CA16" t="n">
         <v>0.04</v>
       </c>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -3968,6 +4112,10 @@
       <c r="CA17" t="n">
         <v>0.05</v>
       </c>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -4191,6 +4339,10 @@
       <c r="CA18" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -4414,6 +4566,10 @@
       <c r="CA19" t="n">
         <v>0.03</v>
       </c>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4613,6 +4769,18 @@
       <c r="CA20" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB20" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.74</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -4808,6 +4976,18 @@
       <c r="CA21" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="CB21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>1.34</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -5003,6 +5183,18 @@
       <c r="CA22" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="CB22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>1.53</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -5198,6 +5390,18 @@
       <c r="CA23" t="n">
         <v>0.05</v>
       </c>
+      <c r="CB23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5397,6 +5601,18 @@
       <c r="CA24" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -5592,6 +5808,18 @@
       <c r="CA25" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -5787,6 +6015,18 @@
       <c r="CA26" t="n">
         <v>0</v>
       </c>
+      <c r="CB26" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -5982,9 +6222,21 @@
       <c r="CA27" t="n">
         <v>0.06</v>
       </c>
+      <c r="CB27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0.37</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="46">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
@@ -5995,6 +6247,7 @@
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="BR1:BS1"/>
+    <mergeCell ref="CD1:CE1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="BV1:BW1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -6026,6 +6279,7 @@
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="BT1:BU1"/>
     <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="CB1:CC1"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE27"/>
+  <dimension ref="A1:CG27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,148 +578,154 @@
       <c r="AI1" s="1" t="n"/>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>number of leaves</t>
+          <t>sample-ID</t>
         </is>
       </c>
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dry matter content (mg/g)</t>
+          <t>number of leaves</t>
         </is>
       </c>
       <c r="AM1" s="1" t="n"/>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>C (mg/g)</t>
+          <t>dry matter content (mg/g)</t>
         </is>
       </c>
       <c r="AO1" s="1" t="n"/>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>N (mg/g)</t>
+          <t>C (mg/g)</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="n"/>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>P (mg/g)</t>
+          <t>N (mg/g)</t>
         </is>
       </c>
       <c r="AS1" s="1" t="n"/>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Al (mg/g)</t>
+          <t>P (mg/g)</t>
         </is>
       </c>
       <c r="AU1" s="1" t="n"/>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Ca (mg/g)</t>
+          <t>Al (mg/g)</t>
         </is>
       </c>
       <c r="AW1" s="1" t="n"/>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>Fe (mg/g)</t>
+          <t>Ca (mg/g)</t>
         </is>
       </c>
       <c r="AY1" s="1" t="n"/>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>K (mg/g)</t>
+          <t>Fe (mg/g)</t>
         </is>
       </c>
       <c r="BA1" s="1" t="n"/>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>Mg (mg/g)</t>
+          <t>K (mg/g)</t>
         </is>
       </c>
       <c r="BC1" s="1" t="n"/>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>Na (mg/g)</t>
+          <t>Mg (mg/g)</t>
         </is>
       </c>
       <c r="BE1" s="1" t="n"/>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>S (mg/g)</t>
+          <t>Na (mg/g)</t>
         </is>
       </c>
       <c r="BG1" s="1" t="n"/>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>△13C_cell</t>
+          <t>S (mg/g)</t>
         </is>
       </c>
       <c r="BI1" s="1" t="n"/>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>Ci</t>
+          <t>△13C_cell</t>
         </is>
       </c>
       <c r="BK1" s="1" t="n"/>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>Ci/Ca</t>
+          <t>Ci</t>
         </is>
       </c>
       <c r="BM1" s="1" t="n"/>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>iWUE (μmol/mol)</t>
+          <t>Ci/Ca</t>
         </is>
       </c>
       <c r="BO1" s="1" t="n"/>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>annual_precipitation_mm</t>
+          <t>iWUE (μmol/mol)</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="n"/>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>elevation_m</t>
+          <t>annual_precipitation_mm</t>
         </is>
       </c>
       <c r="BS1" s="1" t="n"/>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>mean_annual_temperature_C</t>
+          <t>elevation_m</t>
         </is>
       </c>
       <c r="BU1" s="1" t="n"/>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>mean_annual_temperature_C</t>
         </is>
       </c>
       <c r="BW1" s="1" t="n"/>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>C:N</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="BY1" s="1" t="n"/>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>13dC/18dO</t>
+          <t>C:N</t>
         </is>
       </c>
       <c r="CA1" s="1" t="n"/>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>Narea</t>
+          <t>13dC/18dO</t>
         </is>
       </c>
       <c r="CC1" s="1" t="n"/>
       <c r="CD1" s="1" t="inlineStr">
         <is>
+          <t>Narea</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="n"/>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
           <t>Carea</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="n"/>
+      <c r="CG1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1128,6 +1134,16 @@
           <t>std</t>
         </is>
       </c>
+      <c r="CF2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CG2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1206,136 +1222,140 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>38.88</v>
+        <v>27.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.29</v>
+        <v>8.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.7</v>
+        <v>12.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+        <v>3.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>148.92</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
+        <v>592166.17</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="AL4" t="n">
         <v>20</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>429.04</v>
-      </c>
       <c r="AM4" t="n">
-        <v>17.73</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>515.61</v>
+        <v>458.84</v>
       </c>
       <c r="AO4" t="n">
-        <v>11.93</v>
+        <v>40.17</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.43</v>
+        <v>510.89</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.52</v>
+        <v>13.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.78</v>
+        <v>12.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.12</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.53</v>
+        <v>0.89</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.52</v>
+        <v>0.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.53</v>
+        <v>0.04</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.36</v>
+        <v>0.04</v>
       </c>
       <c r="AX4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BO4" t="n">
         <v>0.04</v>
       </c>
-      <c r="AY4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>274.06</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>93.16</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>10.84</v>
-      </c>
       <c r="BP4" t="n">
-        <v>2000</v>
+        <v>106.54</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="BR4" t="n">
         <v>2000</v>
@@ -1344,33 +1364,39 @@
         <v>0</v>
       </c>
       <c r="BT4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
         <v>15</v>
       </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>43.02</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CA4" t="n">
         <v>6.87</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CB4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CC4" t="n">
         <v>0.05</v>
       </c>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -1380,7 +1406,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>0.49</v>
@@ -1389,10 +1415,10 @@
         <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>-29.24</v>
+        <v>-29.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="H5" t="n">
         <v>0.01</v>
@@ -1401,168 +1427,172 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.57</v>
+        <v>-2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N5" t="n">
-        <v>29.74</v>
+        <v>29.73</v>
       </c>
       <c r="O5" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>44.47</v>
+        <v>44.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>-26.57</v>
+        <v>-26.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="X5" t="n">
         <v>0.52</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.73</v>
+        <v>38.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.45</v>
+        <v>15.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.92</v>
+        <v>16.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+        <v>6.85</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>585.75</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>208.63</v>
+      </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
+        <v>592154.89</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="AL5" t="n">
         <v>20</v>
       </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>438.2</v>
-      </c>
       <c r="AM5" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>519.77</v>
+        <v>436.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.380000000000001</v>
+        <v>43.22</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.12</v>
+        <v>512.6900000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.72</v>
+        <v>9.93</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.79</v>
+        <v>11.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.15</v>
+        <v>1.6</v>
       </c>
       <c r="AT5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0.01</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AW5" t="n">
         <v>0.01</v>
       </c>
-      <c r="AV5" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AX5" t="n">
-        <v>0.04</v>
+        <v>3.59</v>
       </c>
       <c r="AY5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BG5" t="n">
         <v>0.05</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.3</v>
-      </c>
       <c r="BH5" t="n">
-        <v>17.96</v>
+        <v>0.62</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>275.16</v>
+        <v>17.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>22.2</v>
+        <v>1.1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.65</v>
+        <v>293.36</v>
       </c>
       <c r="BM5" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BO5" t="n">
         <v>0.05</v>
       </c>
-      <c r="BN5" t="n">
-        <v>92.47</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>13.88</v>
-      </c>
       <c r="BP5" t="n">
-        <v>2000</v>
+        <v>103.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>13.97</v>
       </c>
       <c r="BR5" t="n">
         <v>2000</v>
@@ -1571,33 +1601,39 @@
         <v>0</v>
       </c>
       <c r="BT5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
         <v>15</v>
       </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.7</v>
+        <v>0.52</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.89</v>
+        <v>37.95</v>
       </c>
       <c r="CA5" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
       <c r="CD5" t="inlineStr"/>
       <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -1660,136 +1696,140 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W6" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="X6" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.05</v>
+        <v>32.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.86</v>
+        <v>8.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+        <v>3.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>526.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>151.86</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
+        <v>592184.38</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="AL6" t="n">
         <v>20</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>436.4</v>
-      </c>
       <c r="AM6" t="n">
-        <v>23.45</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>515.91</v>
+        <v>443.24</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.94</v>
+        <v>46.75</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.56</v>
+        <v>509.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.24</v>
+        <v>15.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.32</v>
+        <v>13.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.33</v>
+        <v>2.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01</v>
+        <v>0.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>0.02</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.08</v>
+        <v>0.02</v>
       </c>
       <c r="AX6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AY6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.71</v>
-      </c>
       <c r="BG6" t="n">
-        <v>0.32</v>
+        <v>0.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>18.17</v>
+        <v>0.67</v>
       </c>
       <c r="BI6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="BK6" t="n">
         <v>1.52</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>279.11</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>28.37</v>
-      </c>
       <c r="BL6" t="n">
-        <v>0.66</v>
+        <v>293.97</v>
       </c>
       <c r="BM6" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BO6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BN6" t="n">
-        <v>90</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>17.73</v>
-      </c>
       <c r="BP6" t="n">
-        <v>2000</v>
+        <v>103.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>19.23</v>
       </c>
       <c r="BR6" t="n">
         <v>2000</v>
@@ -1798,33 +1838,39 @@
         <v>0</v>
       </c>
       <c r="BT6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
         <v>15</v>
       </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>40.44</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CA6" t="n">
         <v>4.32</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CB6" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CC6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -1887,136 +1933,140 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>43.89</v>
+        <v>36.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.34</v>
+        <v>11.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.77</v>
+        <v>15.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+        <v>4.42</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>569.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>157.74</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
+        <v>592154.27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>103.52</v>
+      </c>
+      <c r="AL7" t="n">
         <v>20</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>426.71</v>
-      </c>
       <c r="AM7" t="n">
-        <v>27.97</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>510.49</v>
+        <v>445.05</v>
       </c>
       <c r="AO7" t="n">
-        <v>10.09</v>
+        <v>31.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.08</v>
+        <v>506.63</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.83</v>
+        <v>11.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.41</v>
+        <v>13.43</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.7</v>
+        <v>2.12</v>
       </c>
       <c r="AT7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0.03</v>
       </c>
-      <c r="AU7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.66</v>
-      </c>
       <c r="AW7" t="n">
-        <v>1.57</v>
+        <v>0.04</v>
       </c>
       <c r="AX7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA7" t="n">
         <v>0.02</v>
       </c>
-      <c r="AY7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BB7" t="n">
-        <v>2.16</v>
+        <v>4.38</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.4</v>
+        <v>1.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04</v>
+        <v>2.02</v>
       </c>
       <c r="BE7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BF7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BF7" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BG7" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="BH7" t="n">
-        <v>18.47</v>
+        <v>0.66</v>
       </c>
       <c r="BI7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="BK7" t="n">
         <v>1.58</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>284.71</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>29.52</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>300.04</v>
       </c>
       <c r="BM7" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BO7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BN7" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>18.45</v>
-      </c>
       <c r="BP7" t="n">
-        <v>2000</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>20.01</v>
       </c>
       <c r="BR7" t="n">
         <v>2000</v>
@@ -2025,33 +2075,39 @@
         <v>0</v>
       </c>
       <c r="BT7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
         <v>15</v>
       </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>44.34</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CA7" t="n">
         <v>5.43</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CB7" t="n">
         <v>-0.92</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CC7" t="n">
         <v>0.09</v>
       </c>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2165,14 +2221,14 @@
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="n">
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
         <v>462.21</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>25.6</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
@@ -2191,76 +2247,78 @@
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="BI8" t="n">
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="BK8" t="n">
         <v>0.45</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>354.96</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>8.34</v>
-      </c>
       <c r="BL8" t="n">
-        <v>0.84</v>
+        <v>376.21</v>
       </c>
       <c r="BM8" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BO8" t="n">
         <v>0.02</v>
       </c>
-      <c r="BN8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.21</v>
-      </c>
       <c r="BP8" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="BR8" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
         <v>1000</v>
       </c>
-      <c r="BS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT8" t="n">
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
         <v>19</v>
       </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>24.51</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CA8" t="n">
         <v>2.92</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CB8" t="n">
         <v>-1.16</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.19</v>
       </c>
       <c r="CC8" t="n">
         <v>0.02</v>
       </c>
       <c r="CD8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CF8" t="n">
         <v>4.61</v>
       </c>
-      <c r="CE8" t="n">
+      <c r="CG8" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -2340,11 +2398,11 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
         <v>444.58</v>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
@@ -2364,54 +2422,56 @@
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="n">
-        <v>23.46</v>
-      </c>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="n">
-        <v>378.08</v>
+        <v>23.11</v>
       </c>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="n">
-        <v>0.89</v>
+        <v>401.28</v>
       </c>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>28.14</v>
+        <v>0.87</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="n">
-        <v>2000</v>
+        <v>36.04</v>
       </c>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>0.58</v>
+        <v>19</v>
       </c>
       <c r="BW9" t="inlineStr"/>
       <c r="BX9" t="n">
-        <v>22.29</v>
+        <v>0.58</v>
       </c>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>-1.02</v>
+        <v>22.29</v>
       </c>
       <c r="CA9" t="inlineStr"/>
       <c r="CB9" t="n">
-        <v>0.18</v>
+        <v>-1.02</v>
       </c>
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="n">
         <v>3.99</v>
       </c>
-      <c r="CE9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2521,14 +2581,14 @@
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="n">
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
         <v>461.81</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
         <v>65.73</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
@@ -2547,76 +2607,78 @@
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="BI10" t="n">
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.38</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>359.8</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>7.12</v>
-      </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>381.45</v>
       </c>
       <c r="BM10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BO10" t="n">
         <v>0.02</v>
       </c>
-      <c r="BN10" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.45</v>
-      </c>
       <c r="BP10" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="BR10" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
         <v>1000</v>
       </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
         <v>19</v>
       </c>
-      <c r="BU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV10" t="n">
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>18.28</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CA10" t="n">
         <v>1.73</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CB10" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CC10" t="n">
         <v>0.08</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CD10" t="n">
         <v>0.33</v>
       </c>
-      <c r="CC10" t="n">
+      <c r="CE10" t="n">
         <v>0.22</v>
       </c>
-      <c r="CD10" t="n">
+      <c r="CF10" t="n">
         <v>6.11</v>
       </c>
-      <c r="CE10" t="n">
+      <c r="CG10" t="n">
         <v>4.46</v>
       </c>
     </row>
@@ -2728,14 +2790,14 @@
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
         <v>452.38</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
         <v>16.12</v>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
@@ -2754,76 +2816,78 @@
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="BI11" t="n">
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="BK11" t="n">
         <v>1.3</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>339.45</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>24.42</v>
-      </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>359.39</v>
       </c>
       <c r="BM11" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BO11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BN11" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>15.26</v>
-      </c>
       <c r="BP11" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="BR11" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR11" t="n">
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
         <v>1000</v>
       </c>
-      <c r="BS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT11" t="n">
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
         <v>19</v>
       </c>
-      <c r="BU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV11" t="n">
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX11" t="n">
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>22.65</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CA11" t="n">
         <v>3.13</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CB11" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CC11" t="n">
         <v>0.11</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CD11" t="n">
         <v>0.21</v>
       </c>
-      <c r="CC11" t="n">
+      <c r="CE11" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD11" t="n">
+      <c r="CF11" t="n">
         <v>4.59</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CG11" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -2939,14 +3003,14 @@
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="n">
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
         <v>276.6</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AO12" t="n">
         <v>45.98</v>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
@@ -2965,76 +3029,78 @@
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="BI12" t="n">
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.51</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>279.79</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>28.28</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0.66</v>
+        <v>294.7</v>
       </c>
       <c r="BM12" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BO12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BN12" t="n">
-        <v>89.58</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>17.68</v>
-      </c>
       <c r="BP12" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="BR12" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
         <v>3000</v>
       </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
         <v>10</v>
       </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>30.78</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CA12" t="n">
         <v>2.77</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CB12" t="n">
         <v>-1.02</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CC12" t="n">
         <v>0.08</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CD12" t="n">
         <v>0.21</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CE12" t="n">
         <v>0.04</v>
       </c>
-      <c r="CD12" t="n">
+      <c r="CF12" t="n">
         <v>6.66</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CG12" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -3146,14 +3212,14 @@
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="n">
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
         <v>303.57</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AO13" t="n">
         <v>21.05</v>
       </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
@@ -3172,76 +3238,78 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="BI13" t="n">
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="BK13" t="n">
         <v>2.15</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>270.97</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>40.3</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0.64</v>
+        <v>285.13</v>
       </c>
       <c r="BM13" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.1</v>
       </c>
-      <c r="BN13" t="n">
-        <v>95.09</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>25.19</v>
-      </c>
       <c r="BP13" t="n">
+        <v>108.64</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="BR13" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
         <v>3000</v>
       </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
         <v>10</v>
       </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>25.77</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CA13" t="n">
         <v>5.26</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CB13" t="n">
         <v>-0.96</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CC13" t="n">
         <v>0.12</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CD13" t="n">
         <v>0.28</v>
       </c>
-      <c r="CC13" t="n">
+      <c r="CE13" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD13" t="n">
+      <c r="CF13" t="n">
         <v>7.21</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CG13" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -3353,14 +3421,14 @@
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="n">
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
         <v>263.47</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AO14" t="n">
         <v>4.56</v>
       </c>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
@@ -3379,76 +3447,78 @@
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="BI14" t="n">
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="BK14" t="n">
         <v>1.32</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>241.54</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>24.69</v>
-      </c>
       <c r="BL14" t="n">
-        <v>0.57</v>
+        <v>253.23</v>
       </c>
       <c r="BM14" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BO14" t="n">
         <v>0.06</v>
       </c>
-      <c r="BN14" t="n">
-        <v>113.48</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BP14" t="n">
+        <v>128.58</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="BR14" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
         <v>3000</v>
       </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
         <v>10</v>
       </c>
-      <c r="BU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV14" t="n">
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>26.1</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CA14" t="n">
         <v>2.81</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CB14" t="n">
         <v>-0.93</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CC14" t="n">
         <v>0.1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CD14" t="n">
         <v>0.26</v>
       </c>
-      <c r="CC14" t="n">
+      <c r="CE14" t="n">
         <v>0.02</v>
       </c>
-      <c r="CD14" t="n">
+      <c r="CF14" t="n">
         <v>6.74</v>
       </c>
-      <c r="CE14" t="n">
+      <c r="CG14" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -3560,14 +3630,14 @@
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="n">
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
         <v>248.34</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AO15" t="n">
         <v>11.95</v>
       </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
@@ -3586,76 +3656,78 @@
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="n">
-        <v>18.72</v>
-      </c>
-      <c r="BI15" t="n">
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="BK15" t="n">
         <v>1.66</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>289.26</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>31.11</v>
-      </c>
       <c r="BL15" t="n">
-        <v>0.68</v>
+        <v>304.97</v>
       </c>
       <c r="BM15" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BO15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BN15" t="n">
-        <v>83.66</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>19.44</v>
-      </c>
       <c r="BP15" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="BR15" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR15" t="n">
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
         <v>3000</v>
       </c>
-      <c r="BS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT15" t="n">
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
         <v>10</v>
       </c>
-      <c r="BU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV15" t="n">
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
         <v>0.58</v>
       </c>
-      <c r="BW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX15" t="n">
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>28.12</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CA15" t="n">
         <v>2.51</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CB15" t="n">
         <v>-1</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CC15" t="n">
         <v>0.08</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CD15" t="n">
         <v>0.21</v>
       </c>
-      <c r="CC15" t="n">
+      <c r="CE15" t="n">
         <v>0.05</v>
       </c>
-      <c r="CD15" t="n">
+      <c r="CF15" t="n">
         <v>5.89</v>
       </c>
-      <c r="CE15" t="n">
+      <c r="CG15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3724,136 +3796,140 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="X16" t="n">
         <v>0.48</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.74</v>
+        <v>25.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.14</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.99</v>
+        <v>11.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+        <v>3.35</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>441.58</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>138.78</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
+        <v>592162.27</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>130.48</v>
+      </c>
+      <c r="AL16" t="n">
         <v>20</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>485.3</v>
-      </c>
       <c r="AM16" t="n">
-        <v>33.83</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>500.27</v>
+        <v>479.82</v>
       </c>
       <c r="AO16" t="n">
-        <v>7.48</v>
+        <v>36.04</v>
       </c>
       <c r="AP16" t="n">
-        <v>12.13</v>
+        <v>497.47</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.81</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.43</v>
+        <v>12.69</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.17</v>
+        <v>4.66</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="AU16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BF16" t="n">
         <v>0.05</v>
       </c>
-      <c r="AV16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BO16" t="n">
         <v>0.05</v>
       </c>
-      <c r="AY16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>299.16</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>77.47</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>14.13</v>
-      </c>
       <c r="BP16" t="n">
-        <v>2000</v>
+        <v>89.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>15.32</v>
       </c>
       <c r="BR16" t="n">
         <v>2000</v>
@@ -3862,33 +3938,39 @@
         <v>0</v>
       </c>
       <c r="BT16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
         <v>15</v>
       </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>51.73</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CA16" t="n">
         <v>11.71</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CB16" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CC16" t="n">
         <v>0.04</v>
       </c>
-      <c r="CB16" t="inlineStr"/>
-      <c r="CC16" t="inlineStr"/>
       <c r="CD16" t="inlineStr"/>
       <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -3951,136 +4033,140 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="X17" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>22.27</v>
+        <v>25.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.91</v>
+        <v>10.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.97</v>
+        <v>11.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+        <v>4.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>403.35</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>141.02</v>
+      </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
+        <v>592190.7</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>124.79</v>
+      </c>
+      <c r="AL17" t="n">
         <v>20</v>
       </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>493.11</v>
-      </c>
       <c r="AM17" t="n">
-        <v>27.24</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>495.57</v>
+        <v>465.81</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.369999999999999</v>
+        <v>30.98</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.72</v>
+        <v>499.64</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.71</v>
+        <v>11.64</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.43</v>
+        <v>11.29</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.02</v>
+        <v>0.46</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.86</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.03</v>
+        <v>2.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.02</v>
+        <v>3.37</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.63</v>
+        <v>0.04</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.75</v>
+        <v>0.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>3.57</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.23</v>
+        <v>1.17</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.08</v>
+        <v>1.86</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.08</v>
+        <v>1.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.79</v>
+        <v>0.05</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="BH17" t="n">
-        <v>18.67</v>
+        <v>0.72</v>
       </c>
       <c r="BI17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="BK17" t="n">
         <v>0.96</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>288.34</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>18.05</v>
-      </c>
       <c r="BL17" t="n">
-        <v>0.68</v>
+        <v>303.97</v>
       </c>
       <c r="BM17" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BO17" t="n">
         <v>0.04</v>
       </c>
-      <c r="BN17" t="n">
-        <v>84.23999999999999</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>11.28</v>
-      </c>
       <c r="BP17" t="n">
-        <v>2000</v>
+        <v>96.87</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>12.23</v>
       </c>
       <c r="BR17" t="n">
         <v>2000</v>
@@ -4089,33 +4175,39 @@
         <v>0</v>
       </c>
       <c r="BT17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
         <v>15</v>
       </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>47.43</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CA17" t="n">
         <v>4.13</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CB17" t="n">
         <v>-0.86</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CC17" t="n">
         <v>0.05</v>
       </c>
-      <c r="CB17" t="inlineStr"/>
-      <c r="CC17" t="inlineStr"/>
       <c r="CD17" t="inlineStr"/>
       <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -4178,136 +4270,140 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.73</v>
+        <v>26.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.82</v>
+        <v>14.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.42</v>
+        <v>12.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+        <v>5.67</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>440.98</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>241.41</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
+        <v>592235.54</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="AL18" t="n">
         <v>20</v>
       </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>478.69</v>
-      </c>
       <c r="AM18" t="n">
-        <v>20.94</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>492.06</v>
+        <v>472.77</v>
       </c>
       <c r="AO18" t="n">
-        <v>7.87</v>
+        <v>38.37</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.74</v>
+        <v>504.06</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.74</v>
+        <v>14.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.88</v>
+        <v>12.12</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.36</v>
+        <v>1.94</v>
       </c>
       <c r="AT18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BF18" t="n">
         <v>0.05</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BG18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BO18" t="n">
         <v>0.05</v>
       </c>
-      <c r="AV18" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>83.88</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>12.23</v>
-      </c>
       <c r="BP18" t="n">
-        <v>2000</v>
+        <v>96.48</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>13.26</v>
       </c>
       <c r="BR18" t="n">
         <v>2000</v>
@@ -4316,33 +4412,39 @@
         <v>0</v>
       </c>
       <c r="BT18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
         <v>15</v>
       </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>47.79</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CA18" t="n">
         <v>4.16</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CB18" t="n">
         <v>-0.88</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CC18" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB18" t="inlineStr"/>
-      <c r="CC18" t="inlineStr"/>
       <c r="CD18" t="inlineStr"/>
       <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -4352,7 +4454,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>0.47</v>
@@ -4361,10 +4463,10 @@
         <v>0.01</v>
       </c>
       <c r="F19" t="n">
-        <v>-30.78</v>
+        <v>-30.82</v>
       </c>
       <c r="G19" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H19" t="n">
         <v>0.01</v>
@@ -4373,168 +4475,172 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.48</v>
+        <v>-4.6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="L19" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N19" t="n">
-        <v>30.44</v>
+        <v>30.31</v>
       </c>
       <c r="O19" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="P19" t="n">
-        <v>42.22</v>
+        <v>42.31</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
         <v>-27.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="X19" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.33</v>
+        <v>25.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.71</v>
+        <v>9.19</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.880000000000001</v>
+        <v>11.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+        <v>4.07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>403.88</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>144.57</v>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="n">
+        <v>592200.27</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="AL19" t="n">
         <v>20</v>
       </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>485.8</v>
-      </c>
       <c r="AM19" t="n">
-        <v>13.48</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>491.78</v>
+        <v>467.3</v>
       </c>
       <c r="AO19" t="n">
-        <v>6.17</v>
+        <v>24.91</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.35</v>
+        <v>499.05</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.93</v>
+        <v>17.89</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.7</v>
+        <v>10.39</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.66</v>
+        <v>2.92</v>
       </c>
       <c r="AT19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AW19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>306.12</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BO19" t="n">
         <v>0.03</v>
       </c>
-      <c r="AV19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>290.17</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>8.119999999999999</v>
-      </c>
       <c r="BP19" t="n">
-        <v>2000</v>
+        <v>95.52</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="BR19" t="n">
         <v>2000</v>
@@ -4543,33 +4649,39 @@
         <v>0</v>
       </c>
       <c r="BT19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
         <v>15</v>
       </c>
-      <c r="BU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.04</v>
+        <v>0.72</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="BZ19" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB19" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CC19" t="n">
         <v>0.03</v>
       </c>
-      <c r="CB19" t="inlineStr"/>
-      <c r="CC19" t="inlineStr"/>
       <c r="CD19" t="inlineStr"/>
       <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4683,14 +4795,14 @@
       </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="n">
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
         <v>517.2</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AO20" t="n">
         <v>36.65</v>
       </c>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
@@ -4709,76 +4821,78 @@
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="BI20" t="n">
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="BK20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BJ20" t="n">
-        <v>373.2</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>15.02</v>
-      </c>
       <c r="BL20" t="n">
-        <v>0.88</v>
+        <v>395.99</v>
       </c>
       <c r="BM20" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BO20" t="n">
         <v>0.04</v>
       </c>
-      <c r="BN20" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>9.390000000000001</v>
-      </c>
       <c r="BP20" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="BR20" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR20" t="n">
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
         <v>1000</v>
       </c>
-      <c r="BS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT20" t="n">
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
         <v>19</v>
       </c>
-      <c r="BU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV20" t="n">
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
         <v>0.79</v>
       </c>
-      <c r="BW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX20" t="n">
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>31.55</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CA20" t="n">
         <v>2.43</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CB20" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CC20" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CD20" t="n">
         <v>0.19</v>
       </c>
-      <c r="CC20" t="n">
+      <c r="CE20" t="n">
         <v>0.02</v>
       </c>
-      <c r="CD20" t="n">
+      <c r="CF20" t="n">
         <v>6.05</v>
       </c>
-      <c r="CE20" t="n">
+      <c r="CG20" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -4890,14 +5004,14 @@
       </c>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="n">
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="n">
         <v>567.65</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AO21" t="n">
         <v>103.37</v>
       </c>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
@@ -4916,76 +5030,78 @@
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="BI21" t="n">
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="BK21" t="n">
         <v>1.93</v>
       </c>
-      <c r="BJ21" t="n">
-        <v>349.83</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>36.06</v>
-      </c>
       <c r="BL21" t="n">
-        <v>0.83</v>
+        <v>370.64</v>
       </c>
       <c r="BM21" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BO21" t="n">
         <v>0.09</v>
       </c>
-      <c r="BN21" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>22.53</v>
-      </c>
       <c r="BP21" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="BR21" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR21" t="n">
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
         <v>1000</v>
       </c>
-      <c r="BS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT21" t="n">
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
         <v>19</v>
       </c>
-      <c r="BU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV21" t="n">
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
         <v>0.79</v>
       </c>
-      <c r="BW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX21" t="n">
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>30.55</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CA21" t="n">
         <v>2.74</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CB21" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CC21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CD21" t="n">
         <v>0.21</v>
       </c>
-      <c r="CC21" t="n">
+      <c r="CE21" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD21" t="n">
+      <c r="CF21" t="n">
         <v>6.38</v>
       </c>
-      <c r="CE21" t="n">
+      <c r="CG21" t="n">
         <v>1.34</v>
       </c>
     </row>
@@ -5097,14 +5213,14 @@
       </c>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="n">
         <v>498.3</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AO22" t="n">
         <v>49.19</v>
       </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
@@ -5123,76 +5239,78 @@
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="BI22" t="n">
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="BK22" t="n">
         <v>1.42</v>
       </c>
-      <c r="BJ22" t="n">
-        <v>376.84</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>26.65</v>
-      </c>
       <c r="BL22" t="n">
-        <v>0.89</v>
+        <v>399.94</v>
       </c>
       <c r="BM22" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BO22" t="n">
         <v>0.06</v>
       </c>
-      <c r="BN22" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>16.66</v>
-      </c>
       <c r="BP22" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="BR22" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR22" t="n">
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
         <v>1000</v>
       </c>
-      <c r="BS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT22" t="n">
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
         <v>19</v>
       </c>
-      <c r="BU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV22" t="n">
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
         <v>0.79</v>
       </c>
-      <c r="BW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX22" t="n">
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>29.27</v>
       </c>
-      <c r="BY22" t="n">
+      <c r="CA22" t="n">
         <v>1.73</v>
       </c>
-      <c r="BZ22" t="n">
+      <c r="CB22" t="n">
         <v>-1.12</v>
       </c>
-      <c r="CA22" t="n">
+      <c r="CC22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CB22" t="n">
+      <c r="CD22" t="n">
         <v>0.18</v>
       </c>
-      <c r="CC22" t="n">
+      <c r="CE22" t="n">
         <v>0.05</v>
       </c>
-      <c r="CD22" t="n">
+      <c r="CF22" t="n">
         <v>5.37</v>
       </c>
-      <c r="CE22" t="n">
+      <c r="CG22" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -5304,14 +5422,14 @@
       </c>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="n">
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="n">
         <v>497.57</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AO23" t="n">
         <v>47.07</v>
       </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
@@ -5330,76 +5448,78 @@
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="BI23" t="n">
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="BK23" t="n">
         <v>0.99</v>
       </c>
-      <c r="BJ23" t="n">
-        <v>367.57</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>18.45</v>
-      </c>
       <c r="BL23" t="n">
-        <v>0.87</v>
+        <v>389.88</v>
       </c>
       <c r="BM23" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BO23" t="n">
         <v>0.04</v>
       </c>
-      <c r="BN23" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>11.53</v>
-      </c>
       <c r="BP23" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR23" t="n">
         <v>2000</v>
       </c>
-      <c r="BQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR23" t="n">
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
         <v>1000</v>
       </c>
-      <c r="BS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT23" t="n">
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
         <v>19</v>
       </c>
-      <c r="BU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV23" t="n">
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
         <v>0.79</v>
       </c>
-      <c r="BW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX23" t="n">
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>28.9</v>
       </c>
-      <c r="BY23" t="n">
+      <c r="CA23" t="n">
         <v>2.18</v>
       </c>
-      <c r="BZ23" t="n">
+      <c r="CB23" t="n">
         <v>-1.08</v>
       </c>
-      <c r="CA23" t="n">
+      <c r="CC23" t="n">
         <v>0.05</v>
       </c>
-      <c r="CB23" t="n">
+      <c r="CD23" t="n">
         <v>0.22</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CE23" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CF23" t="n">
         <v>6.25</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CG23" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -5515,14 +5635,14 @@
       </c>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="n">
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="n">
         <v>458.37</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AO24" t="n">
         <v>24.12</v>
       </c>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
@@ -5541,76 +5661,78 @@
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="BI24" t="n">
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BK24" t="n">
         <v>0.28</v>
       </c>
-      <c r="BJ24" t="n">
-        <v>297.29</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.28</v>
-      </c>
       <c r="BL24" t="n">
-        <v>0.7</v>
+        <v>313.67</v>
       </c>
       <c r="BM24" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BO24" t="n">
         <v>0.01</v>
       </c>
-      <c r="BN24" t="n">
-        <v>78.64</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BP24" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BR24" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR24" t="n">
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
         <v>3000</v>
       </c>
-      <c r="BS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT24" t="n">
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
         <v>10</v>
       </c>
-      <c r="BU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV24" t="n">
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
         <v>0.54</v>
       </c>
-      <c r="BW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX24" t="n">
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>43.15</v>
       </c>
-      <c r="BY24" t="n">
+      <c r="CA24" t="n">
         <v>5.79</v>
       </c>
-      <c r="BZ24" t="n">
+      <c r="CB24" t="n">
         <v>-1.05</v>
       </c>
-      <c r="CA24" t="n">
+      <c r="CC24" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB24" t="n">
+      <c r="CD24" t="n">
         <v>0.15</v>
       </c>
-      <c r="CC24" t="n">
+      <c r="CE24" t="n">
         <v>0.01</v>
       </c>
-      <c r="CD24" t="n">
+      <c r="CF24" t="n">
         <v>6.37</v>
       </c>
-      <c r="CE24" t="n">
+      <c r="CG24" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5722,14 +5844,14 @@
       </c>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="n">
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="n">
         <v>484.91</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AO25" t="n">
         <v>63.86</v>
       </c>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
@@ -5748,76 +5870,78 @@
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="BI25" t="n">
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="BK25" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="BJ25" t="n">
-        <v>304.29</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL25" t="n">
-        <v>0.72</v>
+        <v>321.26</v>
       </c>
       <c r="BM25" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BO25" t="n">
         <v>0.04</v>
       </c>
-      <c r="BN25" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>11</v>
-      </c>
       <c r="BP25" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="BR25" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR25" t="n">
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
         <v>3000</v>
       </c>
-      <c r="BS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT25" t="n">
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
         <v>10</v>
       </c>
-      <c r="BU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV25" t="n">
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
         <v>0.54</v>
       </c>
-      <c r="BW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX25" t="n">
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
         <v>39.49</v>
       </c>
-      <c r="BY25" t="n">
+      <c r="CA25" t="n">
         <v>5.23</v>
       </c>
-      <c r="BZ25" t="n">
+      <c r="CB25" t="n">
         <v>-1.06</v>
       </c>
-      <c r="CA25" t="n">
+      <c r="CC25" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB25" t="n">
+      <c r="CD25" t="n">
         <v>0.17</v>
       </c>
-      <c r="CC25" t="n">
+      <c r="CE25" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD25" t="n">
+      <c r="CF25" t="n">
         <v>6.51</v>
       </c>
-      <c r="CE25" t="n">
+      <c r="CG25" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -5929,14 +6053,14 @@
       </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="n">
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="n">
         <v>447.24</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AO26" t="n">
         <v>11.29</v>
       </c>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr"/>
@@ -5955,76 +6079,78 @@
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
       <c r="BG26" t="inlineStr"/>
-      <c r="BH26" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="BI26" t="n">
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BK26" t="n">
         <v>0.83</v>
       </c>
-      <c r="BJ26" t="n">
-        <v>323.43</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>15.58</v>
-      </c>
       <c r="BL26" t="n">
-        <v>0.76</v>
+        <v>342.02</v>
       </c>
       <c r="BM26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BO26" t="n">
         <v>0.04</v>
       </c>
-      <c r="BN26" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>9.74</v>
-      </c>
       <c r="BP26" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="BR26" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR26" t="n">
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
         <v>3000</v>
       </c>
-      <c r="BS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT26" t="n">
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
         <v>10</v>
       </c>
-      <c r="BU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV26" t="n">
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
         <v>0.54</v>
       </c>
-      <c r="BW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX26" t="n">
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>41.18</v>
       </c>
-      <c r="BY26" t="n">
+      <c r="CA26" t="n">
         <v>0.31</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="CB26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="CA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB26" t="n">
+      <c r="CC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" t="n">
         <v>0.16</v>
       </c>
-      <c r="CC26" t="n">
+      <c r="CE26" t="n">
         <v>0.01</v>
       </c>
-      <c r="CD26" t="n">
+      <c r="CF26" t="n">
         <v>6.39</v>
       </c>
-      <c r="CE26" t="n">
+      <c r="CG26" t="n">
         <v>0.44</v>
       </c>
     </row>
@@ -6136,14 +6262,14 @@
       </c>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="n">
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="n">
         <v>450.2</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AO27" t="n">
         <v>29.2</v>
       </c>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
@@ -6162,81 +6288,83 @@
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="BI27" t="n">
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="BK27" t="n">
         <v>1.18</v>
       </c>
-      <c r="BJ27" t="n">
-        <v>310.66</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>22.18</v>
-      </c>
       <c r="BL27" t="n">
-        <v>0.73</v>
+        <v>328.17</v>
       </c>
       <c r="BM27" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BO27" t="n">
         <v>0.05</v>
       </c>
-      <c r="BN27" t="n">
-        <v>70.28</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BP27" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="BR27" t="n">
         <v>4500</v>
       </c>
-      <c r="BQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR27" t="n">
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
         <v>3000</v>
       </c>
-      <c r="BS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" t="n">
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
         <v>10</v>
       </c>
-      <c r="BU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV27" t="n">
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
         <v>0.54</v>
       </c>
-      <c r="BW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX27" t="n">
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
         <v>41.73</v>
       </c>
-      <c r="BY27" t="n">
+      <c r="CA27" t="n">
         <v>5.19</v>
       </c>
-      <c r="BZ27" t="n">
+      <c r="CB27" t="n">
         <v>-1.09</v>
       </c>
-      <c r="CA27" t="n">
+      <c r="CC27" t="n">
         <v>0.06</v>
       </c>
-      <c r="CB27" t="n">
+      <c r="CD27" t="n">
         <v>0.15</v>
       </c>
-      <c r="CC27" t="n">
+      <c r="CE27" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD27" t="n">
+      <c r="CF27" t="n">
         <v>6.09</v>
       </c>
-      <c r="CE27" t="n">
+      <c r="CG27" t="n">
         <v>0.37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
@@ -6250,6 +6378,7 @@
     <mergeCell ref="CD1:CE1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="BV1:BW1"/>
+    <mergeCell ref="CF1:CG1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="V1:W1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG27"/>
+  <dimension ref="A1:CI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,28 +704,34 @@
       <c r="BY1" s="1" t="n"/>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>C:N</t>
+          <t>leaf water content</t>
         </is>
       </c>
       <c r="CA1" s="1" t="n"/>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>13dC/18dO</t>
+          <t>C:N</t>
         </is>
       </c>
       <c r="CC1" s="1" t="n"/>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>Narea</t>
+          <t>13dC/18dO</t>
         </is>
       </c>
       <c r="CE1" s="1" t="n"/>
       <c r="CF1" s="1" t="inlineStr">
         <is>
+          <t>Narea</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="n"/>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
           <t>Carea</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="n"/>
+      <c r="CI1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1144,6 +1150,16 @@
           <t>std</t>
         </is>
       </c>
+      <c r="CH2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CI2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1251,8 +1267,12 @@
       <c r="AE4" t="n">
         <v>148.92</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.16</v>
+      </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
@@ -1382,21 +1402,35 @@
         <v>0</v>
       </c>
       <c r="BZ4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CB4" t="n">
         <v>43.02</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CC4" t="n">
         <v>6.87</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CD4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CE4" t="n">
         <v>0.05</v>
       </c>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr"/>
+      <c r="CF4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -1488,8 +1522,12 @@
       <c r="AE5" t="n">
         <v>208.63</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.79</v>
+      </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
@@ -1619,21 +1657,35 @@
         <v>0</v>
       </c>
       <c r="BZ5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CB5" t="n">
         <v>37.95</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CC5" t="n">
         <v>4.98</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CD5" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CC5" t="n">
+      <c r="CE5" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
+      <c r="CF5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>14</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>2.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -1725,8 +1777,12 @@
       <c r="AE6" t="n">
         <v>151.86</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.96</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
@@ -1856,21 +1912,35 @@
         <v>0</v>
       </c>
       <c r="BZ6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CB6" t="n">
         <v>40.44</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CC6" t="n">
         <v>4.32</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CD6" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CE6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
+      <c r="CF6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -1962,8 +2032,12 @@
       <c r="AE7" t="n">
         <v>157.74</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.67</v>
+      </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
@@ -2093,21 +2167,35 @@
         <v>0</v>
       </c>
       <c r="BZ7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CB7" t="n">
         <v>44.34</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CC7" t="n">
         <v>5.43</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CD7" t="n">
         <v>-0.92</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CE7" t="n">
         <v>0.09</v>
       </c>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
+      <c r="CF7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2298,27 +2386,33 @@
         <v>0</v>
       </c>
       <c r="BZ8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CB8" t="n">
         <v>24.51</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CC8" t="n">
         <v>2.92</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CD8" t="n">
         <v>-1.16</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.19</v>
       </c>
       <c r="CE8" t="n">
         <v>0.02</v>
       </c>
       <c r="CF8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CH8" t="n">
         <v>4.61</v>
       </c>
-      <c r="CG8" t="n">
+      <c r="CI8" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -2457,21 +2551,25 @@
       </c>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>22.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CA9" t="inlineStr"/>
       <c r="CB9" t="n">
-        <v>-1.02</v>
+        <v>22.29</v>
       </c>
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="n">
-        <v>0.18</v>
+        <v>-1.02</v>
       </c>
       <c r="CE9" t="inlineStr"/>
       <c r="CF9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="n">
         <v>3.99</v>
       </c>
-      <c r="CG9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2658,27 +2756,33 @@
         <v>0</v>
       </c>
       <c r="BZ10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="CB10" t="n">
         <v>18.28</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CC10" t="n">
         <v>1.73</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CD10" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CC10" t="n">
+      <c r="CE10" t="n">
         <v>0.08</v>
       </c>
-      <c r="CD10" t="n">
+      <c r="CF10" t="n">
         <v>0.33</v>
       </c>
-      <c r="CE10" t="n">
+      <c r="CG10" t="n">
         <v>0.22</v>
       </c>
-      <c r="CF10" t="n">
+      <c r="CH10" t="n">
         <v>6.11</v>
       </c>
-      <c r="CG10" t="n">
+      <c r="CI10" t="n">
         <v>4.46</v>
       </c>
     </row>
@@ -2867,27 +2971,33 @@
         <v>0</v>
       </c>
       <c r="BZ11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CB11" t="n">
         <v>22.65</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CC11" t="n">
         <v>3.13</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CD11" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CC11" t="n">
+      <c r="CE11" t="n">
         <v>0.11</v>
       </c>
-      <c r="CD11" t="n">
+      <c r="CF11" t="n">
         <v>0.21</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CG11" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF11" t="n">
+      <c r="CH11" t="n">
         <v>4.59</v>
       </c>
-      <c r="CG11" t="n">
+      <c r="CI11" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -3080,27 +3190,33 @@
         <v>0</v>
       </c>
       <c r="BZ12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CB12" t="n">
         <v>30.78</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CC12" t="n">
         <v>2.77</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CD12" t="n">
         <v>-1.02</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CE12" t="n">
         <v>0.08</v>
       </c>
-      <c r="CD12" t="n">
+      <c r="CF12" t="n">
         <v>0.21</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CG12" t="n">
         <v>0.04</v>
       </c>
-      <c r="CF12" t="n">
+      <c r="CH12" t="n">
         <v>6.66</v>
       </c>
-      <c r="CG12" t="n">
+      <c r="CI12" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -3289,27 +3405,33 @@
         <v>0</v>
       </c>
       <c r="BZ13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CB13" t="n">
         <v>25.77</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CC13" t="n">
         <v>5.26</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CD13" t="n">
         <v>-0.96</v>
       </c>
-      <c r="CC13" t="n">
+      <c r="CE13" t="n">
         <v>0.12</v>
       </c>
-      <c r="CD13" t="n">
+      <c r="CF13" t="n">
         <v>0.28</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CG13" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF13" t="n">
+      <c r="CH13" t="n">
         <v>7.21</v>
       </c>
-      <c r="CG13" t="n">
+      <c r="CI13" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -3498,27 +3620,33 @@
         <v>0</v>
       </c>
       <c r="BZ14" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
         <v>26.1</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CC14" t="n">
         <v>2.81</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CD14" t="n">
         <v>-0.93</v>
       </c>
-      <c r="CC14" t="n">
+      <c r="CE14" t="n">
         <v>0.1</v>
       </c>
-      <c r="CD14" t="n">
+      <c r="CF14" t="n">
         <v>0.26</v>
       </c>
-      <c r="CE14" t="n">
+      <c r="CG14" t="n">
         <v>0.02</v>
       </c>
-      <c r="CF14" t="n">
+      <c r="CH14" t="n">
         <v>6.74</v>
       </c>
-      <c r="CG14" t="n">
+      <c r="CI14" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -3707,27 +3835,33 @@
         <v>0</v>
       </c>
       <c r="BZ15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CB15" t="n">
         <v>28.12</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CC15" t="n">
         <v>2.51</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CD15" t="n">
         <v>-1</v>
       </c>
-      <c r="CC15" t="n">
+      <c r="CE15" t="n">
         <v>0.08</v>
       </c>
-      <c r="CD15" t="n">
+      <c r="CF15" t="n">
         <v>0.21</v>
       </c>
-      <c r="CE15" t="n">
+      <c r="CG15" t="n">
         <v>0.05</v>
       </c>
-      <c r="CF15" t="n">
+      <c r="CH15" t="n">
         <v>5.89</v>
       </c>
-      <c r="CG15" t="n">
+      <c r="CI15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3825,8 +3959,12 @@
       <c r="AE16" t="n">
         <v>138.78</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.92</v>
+      </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
@@ -3956,21 +4094,35 @@
         <v>0</v>
       </c>
       <c r="BZ16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CB16" t="n">
         <v>51.73</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CC16" t="n">
         <v>11.71</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CD16" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CC16" t="n">
+      <c r="CE16" t="n">
         <v>0.04</v>
       </c>
-      <c r="CD16" t="inlineStr"/>
-      <c r="CE16" t="inlineStr"/>
-      <c r="CF16" t="inlineStr"/>
-      <c r="CG16" t="inlineStr"/>
+      <c r="CF16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -4062,8 +4214,12 @@
       <c r="AE17" t="n">
         <v>141.02</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.95</v>
+      </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
@@ -4193,21 +4349,35 @@
         <v>0</v>
       </c>
       <c r="BZ17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CB17" t="n">
         <v>47.43</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CC17" t="n">
         <v>4.13</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CD17" t="n">
         <v>-0.86</v>
       </c>
-      <c r="CC17" t="n">
+      <c r="CE17" t="n">
         <v>0.05</v>
       </c>
-      <c r="CD17" t="inlineStr"/>
-      <c r="CE17" t="inlineStr"/>
-      <c r="CF17" t="inlineStr"/>
-      <c r="CG17" t="inlineStr"/>
+      <c r="CF17" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -4299,8 +4469,12 @@
       <c r="AE18" t="n">
         <v>241.41</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.41</v>
+      </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
@@ -4430,21 +4604,35 @@
         <v>0</v>
       </c>
       <c r="BZ18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CB18" t="n">
         <v>47.79</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CC18" t="n">
         <v>4.16</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CD18" t="n">
         <v>-0.88</v>
       </c>
-      <c r="CC18" t="n">
+      <c r="CE18" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD18" t="inlineStr"/>
-      <c r="CE18" t="inlineStr"/>
-      <c r="CF18" t="inlineStr"/>
-      <c r="CG18" t="inlineStr"/>
+      <c r="CF18" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -4536,8 +4724,12 @@
       <c r="AE19" t="n">
         <v>144.57</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.01</v>
+      </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="n">
@@ -4667,21 +4859,35 @@
         <v>0</v>
       </c>
       <c r="BZ19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CB19" t="n">
         <v>58.87</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CC19" t="n">
         <v>5.8</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CD19" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CC19" t="n">
+      <c r="CE19" t="n">
         <v>0.03</v>
       </c>
-      <c r="CD19" t="inlineStr"/>
-      <c r="CE19" t="inlineStr"/>
-      <c r="CF19" t="inlineStr"/>
-      <c r="CG19" t="inlineStr"/>
+      <c r="CF19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1.88</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4872,27 +5078,33 @@
         <v>0</v>
       </c>
       <c r="BZ20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CB20" t="n">
         <v>31.55</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CC20" t="n">
         <v>2.43</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CD20" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CC20" t="n">
+      <c r="CE20" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD20" t="n">
+      <c r="CF20" t="n">
         <v>0.19</v>
       </c>
-      <c r="CE20" t="n">
+      <c r="CG20" t="n">
         <v>0.02</v>
       </c>
-      <c r="CF20" t="n">
+      <c r="CH20" t="n">
         <v>6.05</v>
       </c>
-      <c r="CG20" t="n">
+      <c r="CI20" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -5081,27 +5293,33 @@
         <v>0</v>
       </c>
       <c r="BZ21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CB21" t="n">
         <v>30.55</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CC21" t="n">
         <v>2.74</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CD21" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CC21" t="n">
+      <c r="CE21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CD21" t="n">
+      <c r="CF21" t="n">
         <v>0.21</v>
       </c>
-      <c r="CE21" t="n">
+      <c r="CG21" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF21" t="n">
+      <c r="CH21" t="n">
         <v>6.38</v>
       </c>
-      <c r="CG21" t="n">
+      <c r="CI21" t="n">
         <v>1.34</v>
       </c>
     </row>
@@ -5290,27 +5508,33 @@
         <v>0</v>
       </c>
       <c r="BZ22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CB22" t="n">
         <v>29.27</v>
       </c>
-      <c r="CA22" t="n">
+      <c r="CC22" t="n">
         <v>1.73</v>
       </c>
-      <c r="CB22" t="n">
+      <c r="CD22" t="n">
         <v>-1.12</v>
       </c>
-      <c r="CC22" t="n">
+      <c r="CE22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CD22" t="n">
+      <c r="CF22" t="n">
         <v>0.18</v>
       </c>
-      <c r="CE22" t="n">
+      <c r="CG22" t="n">
         <v>0.05</v>
       </c>
-      <c r="CF22" t="n">
+      <c r="CH22" t="n">
         <v>5.37</v>
       </c>
-      <c r="CG22" t="n">
+      <c r="CI22" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -5499,27 +5723,33 @@
         <v>0</v>
       </c>
       <c r="BZ23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CB23" t="n">
         <v>28.9</v>
       </c>
-      <c r="CA23" t="n">
+      <c r="CC23" t="n">
         <v>2.18</v>
       </c>
-      <c r="CB23" t="n">
+      <c r="CD23" t="n">
         <v>-1.08</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CE23" t="n">
         <v>0.05</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CF23" t="n">
         <v>0.22</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CG23" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF23" t="n">
+      <c r="CH23" t="n">
         <v>6.25</v>
       </c>
-      <c r="CG23" t="n">
+      <c r="CI23" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -5712,27 +5942,33 @@
         <v>0</v>
       </c>
       <c r="BZ24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CB24" t="n">
         <v>43.15</v>
       </c>
-      <c r="CA24" t="n">
+      <c r="CC24" t="n">
         <v>5.79</v>
       </c>
-      <c r="CB24" t="n">
+      <c r="CD24" t="n">
         <v>-1.05</v>
       </c>
-      <c r="CC24" t="n">
+      <c r="CE24" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD24" t="n">
+      <c r="CF24" t="n">
         <v>0.15</v>
       </c>
-      <c r="CE24" t="n">
+      <c r="CG24" t="n">
         <v>0.01</v>
       </c>
-      <c r="CF24" t="n">
+      <c r="CH24" t="n">
         <v>6.37</v>
       </c>
-      <c r="CG24" t="n">
+      <c r="CI24" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5921,27 +6157,33 @@
         <v>0</v>
       </c>
       <c r="BZ25" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CB25" t="n">
         <v>39.49</v>
       </c>
-      <c r="CA25" t="n">
+      <c r="CC25" t="n">
         <v>5.23</v>
       </c>
-      <c r="CB25" t="n">
+      <c r="CD25" t="n">
         <v>-1.06</v>
       </c>
-      <c r="CC25" t="n">
+      <c r="CE25" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD25" t="n">
+      <c r="CF25" t="n">
         <v>0.17</v>
       </c>
-      <c r="CE25" t="n">
+      <c r="CG25" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF25" t="n">
+      <c r="CH25" t="n">
         <v>6.51</v>
       </c>
-      <c r="CG25" t="n">
+      <c r="CI25" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -6130,27 +6372,33 @@
         <v>0</v>
       </c>
       <c r="BZ26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CB26" t="n">
         <v>41.18</v>
       </c>
-      <c r="CA26" t="n">
+      <c r="CC26" t="n">
         <v>0.31</v>
       </c>
-      <c r="CB26" t="n">
+      <c r="CD26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="CC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD26" t="n">
+      <c r="CE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF26" t="n">
         <v>0.16</v>
       </c>
-      <c r="CE26" t="n">
+      <c r="CG26" t="n">
         <v>0.01</v>
       </c>
-      <c r="CF26" t="n">
+      <c r="CH26" t="n">
         <v>6.39</v>
       </c>
-      <c r="CG26" t="n">
+      <c r="CI26" t="n">
         <v>0.44</v>
       </c>
     </row>
@@ -6339,32 +6587,38 @@
         <v>0</v>
       </c>
       <c r="BZ27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CB27" t="n">
         <v>41.73</v>
       </c>
-      <c r="CA27" t="n">
+      <c r="CC27" t="n">
         <v>5.19</v>
       </c>
-      <c r="CB27" t="n">
+      <c r="CD27" t="n">
         <v>-1.09</v>
       </c>
-      <c r="CC27" t="n">
+      <c r="CE27" t="n">
         <v>0.06</v>
       </c>
-      <c r="CD27" t="n">
+      <c r="CF27" t="n">
         <v>0.15</v>
       </c>
-      <c r="CE27" t="n">
+      <c r="CG27" t="n">
         <v>0.03</v>
       </c>
-      <c r="CF27" t="n">
+      <c r="CH27" t="n">
         <v>6.09</v>
       </c>
-      <c r="CG27" t="n">
+      <c r="CI27" t="n">
         <v>0.37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
@@ -6388,6 +6642,7 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="BX1:BY1"/>
     <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="CH1:CI1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="T1:U1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -566,139 +566,139 @@
       <c r="AE1" s="1" t="n"/>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (g/cm²)</t>
+          <t>area_basal_m2</t>
         </is>
       </c>
       <c r="AG1" s="1" t="n"/>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>area_basal_m2</t>
+          <t>sample-ID</t>
         </is>
       </c>
       <c r="AI1" s="1" t="n"/>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>sample-ID</t>
+          <t>number of leaves</t>
         </is>
       </c>
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>number of leaves</t>
+          <t>dry matter content (mg/g)</t>
         </is>
       </c>
       <c r="AM1" s="1" t="n"/>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dry matter content (mg/g)</t>
+          <t>C (mg/g)</t>
         </is>
       </c>
       <c r="AO1" s="1" t="n"/>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>C (mg/g)</t>
+          <t>N (mg/g)</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="n"/>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>N (mg/g)</t>
+          <t>P (mg/g)</t>
         </is>
       </c>
       <c r="AS1" s="1" t="n"/>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>P (mg/g)</t>
+          <t>Al (mg/g)</t>
         </is>
       </c>
       <c r="AU1" s="1" t="n"/>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Al (mg/g)</t>
+          <t>Ca (mg/g)</t>
         </is>
       </c>
       <c r="AW1" s="1" t="n"/>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>Ca (mg/g)</t>
+          <t>Fe (mg/g)</t>
         </is>
       </c>
       <c r="AY1" s="1" t="n"/>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>Fe (mg/g)</t>
+          <t>K (mg/g)</t>
         </is>
       </c>
       <c r="BA1" s="1" t="n"/>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>K (mg/g)</t>
+          <t>Mg (mg/g)</t>
         </is>
       </c>
       <c r="BC1" s="1" t="n"/>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>Mg (mg/g)</t>
+          <t>Na (mg/g)</t>
         </is>
       </c>
       <c r="BE1" s="1" t="n"/>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>Na (mg/g)</t>
+          <t>S (mg/g)</t>
         </is>
       </c>
       <c r="BG1" s="1" t="n"/>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>S (mg/g)</t>
+          <t>△13C_cell</t>
         </is>
       </c>
       <c r="BI1" s="1" t="n"/>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>△13C_cell</t>
+          <t>Ci</t>
         </is>
       </c>
       <c r="BK1" s="1" t="n"/>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>Ci</t>
+          <t>Ci/Ca</t>
         </is>
       </c>
       <c r="BM1" s="1" t="n"/>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>Ci/Ca</t>
+          <t>iWUE (μmol/mol)</t>
         </is>
       </c>
       <c r="BO1" s="1" t="n"/>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>iWUE (μmol/mol)</t>
+          <t>annual_precipitation_mm</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="n"/>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>annual_precipitation_mm</t>
+          <t>elevation_m</t>
         </is>
       </c>
       <c r="BS1" s="1" t="n"/>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>elevation_m</t>
+          <t>mean_annual_temperature_C</t>
         </is>
       </c>
       <c r="BU1" s="1" t="n"/>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>mean_annual_temperature_C</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="BW1" s="1" t="n"/>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>Specific leaf area (g/cm²)</t>
         </is>
       </c>
       <c r="BY1" s="1" t="n"/>
@@ -1267,115 +1267,115 @@
       <c r="AE4" t="n">
         <v>148.92</v>
       </c>
-      <c r="AF4" t="n">
-        <v>35.39</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>592166.17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>131.93</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>592166.17</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>131.93</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>20</v>
+        <v>458.84</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>40.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>458.84</v>
+        <v>510.89</v>
       </c>
       <c r="AO4" t="n">
-        <v>40.17</v>
+        <v>13.98</v>
       </c>
       <c r="AP4" t="n">
-        <v>510.89</v>
+        <v>12.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.98</v>
+        <v>2.04</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.75</v>
+        <v>0.89</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>0.43</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.89</v>
+        <v>0.04</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.43</v>
+        <v>0.04</v>
       </c>
       <c r="AV4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BM4" t="n">
         <v>0.04</v>
       </c>
-      <c r="AW4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>288.48</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>18.81</v>
-      </c>
       <c r="BN4" t="n">
-        <v>0.63</v>
+        <v>106.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.04</v>
+        <v>11.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>106.54</v>
+        <v>2000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
         <v>2000</v>
@@ -1384,22 +1384,22 @@
         <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>0.52</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.52</v>
+        <v>35.39</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="BZ4" t="n">
         <v>0.54</v>
@@ -1522,115 +1522,115 @@
       <c r="AE5" t="n">
         <v>208.63</v>
       </c>
-      <c r="AF5" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>592154.89</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>91.08</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>592154.89</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>91.08</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>20</v>
+        <v>436.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>43.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>436.5</v>
+        <v>512.6900000000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>43.22</v>
+        <v>9.93</v>
       </c>
       <c r="AP5" t="n">
-        <v>512.6900000000001</v>
+        <v>11.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.93</v>
+        <v>1.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.67</v>
+        <v>1.26</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.6</v>
+        <v>0.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.26</v>
+        <v>0.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.26</v>
+        <v>0.01</v>
       </c>
       <c r="AV5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AY5" t="n">
         <v>0.01</v>
       </c>
-      <c r="AW5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>0.02</v>
+        <v>4.49</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01</v>
+        <v>1.41</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.49</v>
+        <v>2.11</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.41</v>
+        <v>0.57</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.11</v>
+        <v>0.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.57</v>
+        <v>0.05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="BG5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>293.36</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM5" t="n">
         <v>0.05</v>
       </c>
-      <c r="BH5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>293.36</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>22.36</v>
-      </c>
       <c r="BN5" t="n">
-        <v>0.64</v>
+        <v>103.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05</v>
+        <v>13.97</v>
       </c>
       <c r="BP5" t="n">
-        <v>103.5</v>
+        <v>2000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13.97</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>2000</v>
@@ -1639,22 +1639,22 @@
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>0.52</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.52</v>
+        <v>35.34</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="BZ5" t="n">
         <v>0.5600000000000001</v>
@@ -1777,115 +1777,115 @@
       <c r="AE6" t="n">
         <v>151.86</v>
       </c>
-      <c r="AF6" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>592184.38</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>102.74</v>
+      </c>
       <c r="AJ6" t="n">
-        <v>592184.38</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>102.74</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>20</v>
+        <v>443.24</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>443.24</v>
+        <v>509.58</v>
       </c>
       <c r="AO6" t="n">
-        <v>46.75</v>
+        <v>15.91</v>
       </c>
       <c r="AP6" t="n">
-        <v>509.58</v>
+        <v>13.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.91</v>
+        <v>2.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.03</v>
+        <v>0.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.6</v>
+        <v>0.45</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.83</v>
+        <v>0.02</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.45</v>
+        <v>0.02</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.02</v>
+        <v>2.42</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.02</v>
+        <v>1.58</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.42</v>
+        <v>0.05</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.58</v>
+        <v>0.05</v>
       </c>
       <c r="AZ6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BE6" t="n">
         <v>0.05</v>
       </c>
-      <c r="BA6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BF6" t="n">
-        <v>0.03</v>
+        <v>0.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.67</v>
+        <v>17.83</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.4</v>
+        <v>1.52</v>
       </c>
       <c r="BJ6" t="n">
-        <v>17.83</v>
+        <v>293.97</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.52</v>
+        <v>30.77</v>
       </c>
       <c r="BL6" t="n">
-        <v>293.97</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>30.77</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.64</v>
+        <v>103.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.07000000000000001</v>
+        <v>19.23</v>
       </c>
       <c r="BP6" t="n">
-        <v>103.12</v>
+        <v>2000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>19.23</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
         <v>2000</v>
@@ -1894,22 +1894,22 @@
         <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>0.52</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.52</v>
+        <v>36.46</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BZ6" t="n">
         <v>0.5600000000000001</v>
@@ -2032,115 +2032,115 @@
       <c r="AE7" t="n">
         <v>157.74</v>
       </c>
-      <c r="AF7" t="n">
-        <v>35.91</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>592154.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>103.52</v>
+      </c>
       <c r="AJ7" t="n">
-        <v>592154.27</v>
+        <v>20</v>
       </c>
       <c r="AK7" t="n">
-        <v>103.52</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>445.05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>31.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>445.05</v>
+        <v>506.63</v>
       </c>
       <c r="AO7" t="n">
-        <v>31.92</v>
+        <v>11.49</v>
       </c>
       <c r="AP7" t="n">
-        <v>506.63</v>
+        <v>13.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.49</v>
+        <v>2.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.43</v>
+        <v>1.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.12</v>
+        <v>0.82</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.2</v>
+        <v>0.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.82</v>
+        <v>0.04</v>
       </c>
       <c r="AV7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX7" t="n">
         <v>0.03</v>
       </c>
-      <c r="AW7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.62</v>
-      </c>
       <c r="AY7" t="n">
-        <v>2.14</v>
+        <v>0.02</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.03</v>
+        <v>4.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.02</v>
+        <v>1.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.38</v>
+        <v>2.02</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.67</v>
+        <v>0.09</v>
       </c>
       <c r="BF7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>300.04</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>300.04</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>32.01</v>
-      </c>
       <c r="BN7" t="n">
-        <v>0.65</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.07000000000000001</v>
+        <v>20.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>99.31999999999999</v>
+        <v>2000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>20.01</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>2000</v>
@@ -2149,22 +2149,22 @@
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>0.52</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.52</v>
+        <v>35.91</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="BZ7" t="n">
         <v>0.55</v>
@@ -2296,27 +2296,23 @@
         <v>252.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>92.05</v>
+        <v>0.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="AH8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI8" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
+      <c r="AL8" t="n">
         <v>462.21</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AM8" t="n">
         <v>25.6</v>
       </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
@@ -2335,55 +2331,59 @@
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
+      <c r="BH8" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BJ8" t="n">
-        <v>21.88</v>
+        <v>376.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.45</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>376.21</v>
+        <v>0.82</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.039999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.82</v>
+        <v>51.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.02</v>
+        <v>5.65</v>
       </c>
       <c r="BP8" t="n">
-        <v>51.71</v>
+        <v>2000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>19</v>
+        <v>0.58</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.58</v>
+        <v>92.05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>10.83</v>
       </c>
       <c r="BZ8" t="n">
         <v>0.54</v>
@@ -2483,20 +2483,18 @@
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>112.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>444.58</v>
+      </c>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>444.58</v>
-      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
@@ -2516,38 +2514,40 @@
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BH9" t="n">
+        <v>23.11</v>
+      </c>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="n">
-        <v>23.11</v>
+        <v>401.28</v>
       </c>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="n">
-        <v>401.28</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>0.87</v>
+        <v>36.04</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="n">
-        <v>36.04</v>
+        <v>2000</v>
       </c>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>19</v>
+        <v>0.58</v>
       </c>
       <c r="BW9" t="inlineStr"/>
       <c r="BX9" t="n">
-        <v>0.58</v>
+        <v>112.06</v>
       </c>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
@@ -2666,27 +2666,23 @@
         <v>95.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>91.5</v>
+        <v>0.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI10" t="n">
         <v>0.03</v>
       </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
+      <c r="AL10" t="n">
         <v>461.81</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AM10" t="n">
         <v>65.73</v>
       </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
@@ -2705,55 +2701,59 @@
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
+      <c r="BH10" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.38</v>
+      </c>
       <c r="BJ10" t="n">
-        <v>22.14</v>
+        <v>381.45</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>7.72</v>
       </c>
       <c r="BL10" t="n">
-        <v>381.45</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.72</v>
+        <v>0.02</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.83</v>
+        <v>48.44</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02</v>
+        <v>4.83</v>
       </c>
       <c r="BP10" t="n">
-        <v>48.44</v>
+        <v>2000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>19</v>
+        <v>0.58</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.58</v>
+        <v>91.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>38.65</v>
       </c>
       <c r="BZ10" t="n">
         <v>0.54</v>
@@ -2881,27 +2881,23 @@
         <v>70.29000000000001</v>
       </c>
       <c r="AF11" t="n">
-        <v>95.65000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI11" t="n">
         <v>0.04</v>
       </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
+      <c r="AL11" t="n">
         <v>452.38</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AM11" t="n">
         <v>16.12</v>
       </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
@@ -2920,55 +2916,59 @@
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
+      <c r="BH11" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.3</v>
+      </c>
       <c r="BJ11" t="n">
-        <v>21.05</v>
+        <v>359.39</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.3</v>
+        <v>26.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>359.39</v>
+        <v>0.78</v>
       </c>
       <c r="BM11" t="n">
-        <v>26.48</v>
+        <v>0.06</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.78</v>
+        <v>62.23</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.06</v>
+        <v>16.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>62.23</v>
+        <v>2000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>16.55</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>19</v>
+        <v>0.58</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.58</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="BZ11" t="n">
         <v>0.55</v>
@@ -3100,27 +3100,23 @@
         <v>26.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>68.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
+      <c r="AL12" t="n">
         <v>276.6</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AM12" t="n">
         <v>45.98</v>
       </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
@@ -3139,55 +3135,59 @@
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
+      <c r="BH12" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.51</v>
+      </c>
       <c r="BJ12" t="n">
-        <v>17.87</v>
+        <v>294.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.51</v>
+        <v>30.67</v>
       </c>
       <c r="BL12" t="n">
-        <v>294.7</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>30.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.64</v>
+        <v>102.66</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.07000000000000001</v>
+        <v>19.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>102.66</v>
+        <v>4500</v>
       </c>
       <c r="BQ12" t="n">
-        <v>19.17</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>0.58</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.58</v>
+        <v>68.88</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>16.18</v>
       </c>
       <c r="BZ12" t="n">
         <v>0.72</v>
@@ -3315,27 +3315,23 @@
         <v>117.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.87</v>
+        <v>0.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="AH13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI13" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
+      <c r="AL13" t="n">
         <v>303.57</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AM13" t="n">
         <v>21.05</v>
       </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
@@ -3354,55 +3350,59 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.15</v>
+      </c>
       <c r="BJ13" t="n">
-        <v>17.39</v>
+        <v>285.13</v>
       </c>
       <c r="BK13" t="n">
-        <v>2.15</v>
+        <v>43.7</v>
       </c>
       <c r="BL13" t="n">
-        <v>285.13</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>43.7</v>
+        <v>0.1</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.62</v>
+        <v>108.64</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1</v>
+        <v>27.31</v>
       </c>
       <c r="BP13" t="n">
-        <v>108.64</v>
+        <v>4500</v>
       </c>
       <c r="BQ13" t="n">
-        <v>27.31</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>0.58</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.58</v>
+        <v>60.87</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="BZ13" t="n">
         <v>0.7</v>
@@ -3530,27 +3530,23 @@
         <v>55.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>65.98</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
+      <c r="AL14" t="n">
         <v>263.47</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AM14" t="n">
         <v>4.56</v>
       </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
@@ -3569,55 +3565,59 @@
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
+      <c r="BH14" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.32</v>
+      </c>
       <c r="BJ14" t="n">
-        <v>15.82</v>
+        <v>253.23</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.32</v>
+        <v>26.77</v>
       </c>
       <c r="BL14" t="n">
-        <v>253.23</v>
+        <v>0.55</v>
       </c>
       <c r="BM14" t="n">
-        <v>26.77</v>
+        <v>0.06</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.55</v>
+        <v>128.58</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.06</v>
+        <v>16.73</v>
       </c>
       <c r="BP14" t="n">
-        <v>128.58</v>
+        <v>4500</v>
       </c>
       <c r="BQ14" t="n">
-        <v>16.73</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>0.58</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.58</v>
+        <v>65.98</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>0.74</v>
@@ -3745,27 +3745,23 @@
         <v>97.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>75.91</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
+      <c r="AL15" t="n">
         <v>248.34</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AM15" t="n">
         <v>11.95</v>
       </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
@@ -3784,55 +3780,59 @@
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
+      <c r="BH15" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.66</v>
+      </c>
       <c r="BJ15" t="n">
-        <v>18.37</v>
+        <v>304.97</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.66</v>
+        <v>33.73</v>
       </c>
       <c r="BL15" t="n">
-        <v>304.97</v>
+        <v>0.66</v>
       </c>
       <c r="BM15" t="n">
-        <v>33.73</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.66</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.07000000000000001</v>
+        <v>21.08</v>
       </c>
       <c r="BP15" t="n">
-        <v>96.23999999999999</v>
+        <v>4500</v>
       </c>
       <c r="BQ15" t="n">
-        <v>21.08</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>0.58</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.58</v>
+        <v>75.91</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>12.42</v>
       </c>
       <c r="BZ15" t="n">
         <v>0.75</v>
@@ -3959,115 +3959,115 @@
       <c r="AE16" t="n">
         <v>138.78</v>
       </c>
-      <c r="AF16" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
+        <v>592162.27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>130.48</v>
+      </c>
       <c r="AJ16" t="n">
-        <v>592162.27</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>130.48</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>20</v>
+        <v>479.82</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>36.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>479.82</v>
+        <v>497.47</v>
       </c>
       <c r="AO16" t="n">
-        <v>36.04</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AP16" t="n">
-        <v>497.47</v>
+        <v>12.69</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.279999999999999</v>
+        <v>4.66</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.69</v>
+        <v>0.52</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.66</v>
+        <v>0.22</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.22</v>
+        <v>1.37</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.41</v>
+        <v>1.39</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.39</v>
+        <v>0.06</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.17</v>
+        <v>0.02</v>
       </c>
       <c r="AZ16" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE16" t="n">
         <v>0.06</v>
       </c>
-      <c r="BA16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.64</v>
-      </c>
       <c r="BF16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BM16" t="n">
         <v>0.05</v>
       </c>
-      <c r="BG16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>315.7</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>24.52</v>
-      </c>
       <c r="BN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05</v>
+        <v>15.32</v>
       </c>
       <c r="BP16" t="n">
-        <v>89.53</v>
+        <v>2000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>15.32</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>2000</v>
@@ -4076,22 +4076,22 @@
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.72</v>
+        <v>37.13</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BZ16" t="n">
         <v>0.52</v>
@@ -4214,115 +4214,115 @@
       <c r="AE17" t="n">
         <v>141.02</v>
       </c>
-      <c r="AF17" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>592190.7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>124.79</v>
+      </c>
       <c r="AJ17" t="n">
-        <v>592190.7</v>
+        <v>20</v>
       </c>
       <c r="AK17" t="n">
-        <v>124.79</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>465.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>30.98</v>
       </c>
       <c r="AN17" t="n">
-        <v>465.81</v>
+        <v>499.64</v>
       </c>
       <c r="AO17" t="n">
-        <v>30.98</v>
+        <v>11.64</v>
       </c>
       <c r="AP17" t="n">
-        <v>499.64</v>
+        <v>11.29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.29</v>
+        <v>0.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.57</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.37</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.57</v>
+        <v>0.04</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.37</v>
+        <v>0.01</v>
       </c>
       <c r="AZ17" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BM17" t="n">
         <v>0.04</v>
       </c>
-      <c r="BA17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>303.97</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>19.57</v>
-      </c>
       <c r="BN17" t="n">
-        <v>0.66</v>
+        <v>96.87</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.04</v>
+        <v>12.23</v>
       </c>
       <c r="BP17" t="n">
-        <v>96.87</v>
+        <v>2000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>12.23</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>2000</v>
@@ -4331,22 +4331,22 @@
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.72</v>
+        <v>34.39</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BZ17" t="n">
         <v>0.53</v>
@@ -4469,115 +4469,115 @@
       <c r="AE18" t="n">
         <v>241.41</v>
       </c>
-      <c r="AF18" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>592235.54</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>116.4</v>
+      </c>
       <c r="AJ18" t="n">
-        <v>592235.54</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>116.4</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>472.77</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>38.37</v>
       </c>
       <c r="AN18" t="n">
-        <v>472.77</v>
+        <v>504.06</v>
       </c>
       <c r="AO18" t="n">
-        <v>38.37</v>
+        <v>14.01</v>
       </c>
       <c r="AP18" t="n">
-        <v>504.06</v>
+        <v>12.12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.01</v>
+        <v>1.94</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.94</v>
+        <v>0.53</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.06</v>
+        <v>2.36</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.36</v>
+        <v>0.04</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.92</v>
+        <v>0.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.04</v>
+        <v>3.57</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.57</v>
+        <v>1.67</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.67</v>
+        <v>0.05</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.64</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.05</v>
       </c>
-      <c r="BG18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>304.58</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>21.22</v>
-      </c>
       <c r="BN18" t="n">
-        <v>0.66</v>
+        <v>96.48</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.05</v>
+        <v>13.26</v>
       </c>
       <c r="BP18" t="n">
-        <v>96.48</v>
+        <v>2000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>13.26</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>2000</v>
@@ -4586,22 +4586,22 @@
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.72</v>
+        <v>35.38</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="BZ18" t="n">
         <v>0.53</v>
@@ -4724,115 +4724,115 @@
       <c r="AE19" t="n">
         <v>144.57</v>
       </c>
-      <c r="AF19" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>592200.27</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>117.12</v>
+      </c>
       <c r="AJ19" t="n">
-        <v>592200.27</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>117.12</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>20</v>
+        <v>467.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>24.91</v>
       </c>
       <c r="AN19" t="n">
-        <v>467.3</v>
+        <v>499.05</v>
       </c>
       <c r="AO19" t="n">
-        <v>24.91</v>
+        <v>17.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>499.05</v>
+        <v>10.39</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17.89</v>
+        <v>2.92</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.39</v>
+        <v>1.39</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.92</v>
+        <v>0.82</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.39</v>
+        <v>0.02</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.82</v>
+        <v>0.02</v>
       </c>
       <c r="AV19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BD19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AW19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BE19" t="n">
-        <v>0.47</v>
+        <v>0.04</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.02</v>
+        <v>0.59</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.59</v>
+        <v>18.43</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.26</v>
+        <v>0.73</v>
       </c>
       <c r="BJ19" t="n">
-        <v>18.43</v>
+        <v>306.12</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.73</v>
+        <v>14.77</v>
       </c>
       <c r="BL19" t="n">
-        <v>306.12</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>14.77</v>
+        <v>0.03</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.67</v>
+        <v>95.52</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.03</v>
+        <v>9.23</v>
       </c>
       <c r="BP19" t="n">
-        <v>95.52</v>
+        <v>2000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.23</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
         <v>2000</v>
@@ -4841,22 +4841,22 @@
         <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.72</v>
+        <v>34.58</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>0.53</v>
@@ -4988,27 +4988,23 @@
         <v>423.28</v>
       </c>
       <c r="AF20" t="n">
-        <v>80.27</v>
+        <v>0.03</v>
       </c>
       <c r="AG20" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI20" t="n">
         <v>0.02</v>
       </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
+      <c r="AL20" t="n">
         <v>517.2</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AM20" t="n">
         <v>36.65</v>
       </c>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
@@ -5027,55 +5023,59 @@
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
+      <c r="BH20" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BJ20" t="n">
-        <v>22.85</v>
+        <v>395.99</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.8</v>
+        <v>16.28</v>
       </c>
       <c r="BL20" t="n">
-        <v>395.99</v>
+        <v>0.86</v>
       </c>
       <c r="BM20" t="n">
-        <v>16.28</v>
+        <v>0.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.86</v>
+        <v>39.35</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.04</v>
+        <v>10.18</v>
       </c>
       <c r="BP20" t="n">
-        <v>39.35</v>
+        <v>2000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>10.18</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
         <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>19</v>
+        <v>0.79</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.79</v>
+        <v>80.27</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="BZ20" t="n">
         <v>0.48</v>
@@ -5203,27 +5203,23 @@
         <v>393.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>77.51000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI21" t="n">
         <v>0.1</v>
       </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="n">
+      <c r="AL21" t="n">
         <v>567.65</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AM21" t="n">
         <v>103.37</v>
       </c>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
@@ -5242,55 +5238,59 @@
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
+      <c r="BH21" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.93</v>
+      </c>
       <c r="BJ21" t="n">
-        <v>21.61</v>
+        <v>370.64</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.93</v>
+        <v>39.1</v>
       </c>
       <c r="BL21" t="n">
-        <v>370.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM21" t="n">
-        <v>39.1</v>
+        <v>0.09</v>
       </c>
       <c r="BN21" t="n">
-        <v>0.8100000000000001</v>
+        <v>55.19</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.09</v>
+        <v>24.44</v>
       </c>
       <c r="BP21" t="n">
-        <v>55.19</v>
+        <v>2000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>24.44</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
         <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU21" t="n">
         <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>19</v>
+        <v>0.79</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.79</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>15.42</v>
       </c>
       <c r="BZ21" t="n">
         <v>0.43</v>
@@ -5418,27 +5418,23 @@
         <v>479.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>101.47</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI22" t="n">
         <v>0.06</v>
       </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="n">
+      <c r="AL22" t="n">
         <v>498.3</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AM22" t="n">
         <v>49.19</v>
       </c>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
@@ -5457,55 +5453,59 @@
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
+      <c r="BH22" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.42</v>
+      </c>
       <c r="BJ22" t="n">
-        <v>23.05</v>
+        <v>399.94</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.42</v>
+        <v>28.9</v>
       </c>
       <c r="BL22" t="n">
-        <v>399.94</v>
+        <v>0.87</v>
       </c>
       <c r="BM22" t="n">
-        <v>28.9</v>
+        <v>0.06</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.87</v>
+        <v>36.88</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.06</v>
+        <v>18.06</v>
       </c>
       <c r="BP22" t="n">
-        <v>36.88</v>
+        <v>2000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>18.06</v>
+        <v>0</v>
       </c>
       <c r="BR22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
         <v>0</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
       </c>
       <c r="BV22" t="n">
-        <v>19</v>
+        <v>0.79</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.79</v>
+        <v>101.47</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>52.75</v>
       </c>
       <c r="BZ22" t="n">
         <v>0.5</v>
@@ -5633,27 +5633,23 @@
         <v>289.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>78.02</v>
+        <v>0.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI23" t="n">
         <v>0.03</v>
       </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="n">
+      <c r="AL23" t="n">
         <v>497.57</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AM23" t="n">
         <v>47.07</v>
       </c>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
@@ -5672,55 +5668,59 @@
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
-      <c r="BI23" t="inlineStr"/>
+      <c r="BH23" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.99</v>
+      </c>
       <c r="BJ23" t="n">
-        <v>22.55</v>
+        <v>389.88</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.99</v>
+        <v>20.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>389.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM23" t="n">
-        <v>20.01</v>
+        <v>0.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.85</v>
+        <v>43.17</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.04</v>
+        <v>12.5</v>
       </c>
       <c r="BP23" t="n">
-        <v>43.17</v>
+        <v>2000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BR23" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
         <v>0</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BU23" t="n">
         <v>0</v>
       </c>
       <c r="BV23" t="n">
-        <v>19</v>
+        <v>0.79</v>
       </c>
       <c r="BW23" t="n">
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.79</v>
+        <v>78.02</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>10.48</v>
       </c>
       <c r="BZ23" t="n">
         <v>0.5</v>
@@ -5852,27 +5852,23 @@
         <v>4.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>70.09999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI24" t="n">
         <v>0.01</v>
       </c>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="n">
+      <c r="AL24" t="n">
         <v>458.37</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AM24" t="n">
         <v>24.12</v>
       </c>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
@@ -5891,55 +5887,59 @@
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="inlineStr"/>
-      <c r="BI24" t="inlineStr"/>
+      <c r="BH24" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.28</v>
+      </c>
       <c r="BJ24" t="n">
-        <v>18.8</v>
+        <v>313.67</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.28</v>
+        <v>5.73</v>
       </c>
       <c r="BL24" t="n">
-        <v>313.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM24" t="n">
-        <v>5.73</v>
+        <v>0.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.68</v>
+        <v>90.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.01</v>
+        <v>3.58</v>
       </c>
       <c r="BP24" t="n">
-        <v>90.8</v>
+        <v>4500</v>
       </c>
       <c r="BQ24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BR24" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS24" t="n">
         <v>0</v>
       </c>
       <c r="BT24" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU24" t="n">
         <v>0</v>
       </c>
       <c r="BV24" t="n">
-        <v>10</v>
+        <v>0.54</v>
       </c>
       <c r="BW24" t="n">
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>0.54</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="BZ24" t="n">
         <v>0.54</v>
@@ -6067,27 +6067,23 @@
         <v>12.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>69.55</v>
+        <v>0.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI25" t="n">
         <v>0.01</v>
       </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="n">
+      <c r="AL25" t="n">
         <v>484.91</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AM25" t="n">
         <v>63.86</v>
       </c>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
@@ -6106,55 +6102,59 @@
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="inlineStr"/>
-      <c r="BI25" t="inlineStr"/>
+      <c r="BH25" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="BJ25" t="n">
-        <v>19.17</v>
+        <v>321.26</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.9399999999999999</v>
+        <v>19.08</v>
       </c>
       <c r="BL25" t="n">
-        <v>321.26</v>
+        <v>0.7</v>
       </c>
       <c r="BM25" t="n">
-        <v>19.08</v>
+        <v>0.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.7</v>
+        <v>86.06</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.04</v>
+        <v>11.93</v>
       </c>
       <c r="BP25" t="n">
-        <v>86.06</v>
+        <v>4500</v>
       </c>
       <c r="BQ25" t="n">
-        <v>11.93</v>
+        <v>0</v>
       </c>
       <c r="BR25" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS25" t="n">
         <v>0</v>
       </c>
       <c r="BT25" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
       </c>
       <c r="BV25" t="n">
-        <v>10</v>
+        <v>0.54</v>
       </c>
       <c r="BW25" t="n">
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>0.54</v>
+        <v>69.55</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BZ25" t="n">
         <v>0.52</v>
@@ -6282,27 +6282,23 @@
         <v>3.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>72.20999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="n">
+      <c r="AL26" t="n">
         <v>447.24</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AM26" t="n">
         <v>11.29</v>
       </c>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr"/>
@@ -6321,55 +6317,59 @@
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
       <c r="BG26" t="inlineStr"/>
-      <c r="BH26" t="inlineStr"/>
-      <c r="BI26" t="inlineStr"/>
+      <c r="BH26" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.83</v>
+      </c>
       <c r="BJ26" t="n">
-        <v>20.2</v>
+        <v>342.02</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.83</v>
+        <v>16.9</v>
       </c>
       <c r="BL26" t="n">
-        <v>342.02</v>
+        <v>0.75</v>
       </c>
       <c r="BM26" t="n">
-        <v>16.9</v>
+        <v>0.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>0.75</v>
+        <v>73.08</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.04</v>
+        <v>10.56</v>
       </c>
       <c r="BP26" t="n">
-        <v>73.08</v>
+        <v>4500</v>
       </c>
       <c r="BQ26" t="n">
-        <v>10.56</v>
+        <v>0</v>
       </c>
       <c r="BR26" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS26" t="n">
         <v>0</v>
       </c>
       <c r="BT26" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU26" t="n">
         <v>0</v>
       </c>
       <c r="BV26" t="n">
-        <v>10</v>
+        <v>0.54</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
       </c>
       <c r="BX26" t="n">
-        <v>0.54</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="BZ26" t="n">
         <v>0.55</v>
@@ -6497,27 +6497,23 @@
         <v>2.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>72.58</v>
+        <v>0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="AH27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI27" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="n">
+      <c r="AL27" t="n">
         <v>450.2</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AM27" t="n">
         <v>29.2</v>
       </c>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
@@ -6536,55 +6532,59 @@
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
-      <c r="BI27" t="inlineStr"/>
+      <c r="BH27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.18</v>
+      </c>
       <c r="BJ27" t="n">
-        <v>19.51</v>
+        <v>328.17</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.18</v>
+        <v>24.05</v>
       </c>
       <c r="BL27" t="n">
-        <v>328.17</v>
+        <v>0.72</v>
       </c>
       <c r="BM27" t="n">
-        <v>24.05</v>
+        <v>0.05</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.72</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.05</v>
+        <v>15.03</v>
       </c>
       <c r="BP27" t="n">
-        <v>81.73999999999999</v>
+        <v>4500</v>
       </c>
       <c r="BQ27" t="n">
-        <v>15.03</v>
+        <v>0</v>
       </c>
       <c r="BR27" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="BS27" t="n">
         <v>0</v>
       </c>
       <c r="BT27" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="BU27" t="n">
         <v>0</v>
       </c>
       <c r="BV27" t="n">
-        <v>10</v>
+        <v>0.54</v>
       </c>
       <c r="BW27" t="n">
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>0.54</v>
+        <v>72.58</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="BZ27" t="n">
         <v>0.55</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH27"/>
+  <dimension ref="A1:CL27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,40 +690,52 @@
       <c r="BV1" s="1" t="n"/>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (g/cm²)</t>
+          <t>Bloque</t>
         </is>
       </c>
       <c r="BX1" s="1" t="n"/>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>leaf water content</t>
+          <t>Specific leaf area (cm²/g)</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="n"/>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>C:N</t>
+          <t>LMA g/m2</t>
         </is>
       </c>
       <c r="CB1" s="1" t="n"/>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>13dC/18dO</t>
+          <t>leaf water content</t>
         </is>
       </c>
       <c r="CD1" s="1" t="n"/>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>Narea</t>
+          <t>C:N</t>
         </is>
       </c>
       <c r="CF1" s="1" t="n"/>
       <c r="CG1" s="1" t="inlineStr">
         <is>
+          <t>13dC/18dO</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="n"/>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Narea</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="n"/>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
           <t>Carea</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="n"/>
+      <c r="CL1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1147,6 +1159,26 @@
           <t>std</t>
         </is>
       </c>
+      <c r="CI2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CJ2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="CK2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CL2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1380,39 +1412,51 @@
         <v>0</v>
       </c>
       <c r="BW4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BY4" t="n">
         <v>35.39</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BZ4" t="n">
         <v>4.16</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CA4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.54</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CD4" t="n">
         <v>0.04</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CE4" t="n">
         <v>43.02</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CF4" t="n">
         <v>6.87</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CG4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="CD4" t="n">
+      <c r="CH4" t="n">
         <v>0.05</v>
       </c>
-      <c r="CE4" t="n">
+      <c r="CI4" t="n">
         <v>0.33</v>
       </c>
-      <c r="CF4" t="n">
+      <c r="CJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="CG4" t="n">
+      <c r="CK4" t="n">
         <v>14.01</v>
       </c>
-      <c r="CH4" t="n">
+      <c r="CL4" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -1632,39 +1676,51 @@
         <v>0</v>
       </c>
       <c r="BW5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BY5" t="n">
         <v>35.34</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BZ5" t="n">
         <v>4.79</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CA5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CD5" t="n">
         <v>0.04</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CE5" t="n">
         <v>37.95</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CF5" t="n">
         <v>4.98</v>
       </c>
-      <c r="CC5" t="n">
+      <c r="CG5" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CD5" t="n">
+      <c r="CH5" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE5" t="n">
+      <c r="CI5" t="n">
         <v>0.37</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CJ5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CK5" t="n">
         <v>14</v>
       </c>
-      <c r="CH5" t="n">
+      <c r="CL5" t="n">
         <v>2.09</v>
       </c>
     </row>
@@ -1884,39 +1940,51 @@
         <v>0</v>
       </c>
       <c r="BW6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BY6" t="n">
         <v>36.46</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BZ6" t="n">
         <v>3.96</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CA6" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC6" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CD6" t="n">
         <v>0.05</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CE6" t="n">
         <v>40.44</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CF6" t="n">
         <v>4.32</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CG6" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CD6" t="n">
+      <c r="CH6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CI6" t="n">
         <v>0.33</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CJ6" t="n">
         <v>0.06</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CK6" t="n">
         <v>13.29</v>
       </c>
-      <c r="CH6" t="n">
+      <c r="CL6" t="n">
         <v>1.15</v>
       </c>
     </row>
@@ -2136,39 +2204,51 @@
         <v>0</v>
       </c>
       <c r="BW7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BY7" t="n">
         <v>35.91</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="BZ7" t="n">
         <v>3.67</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CA7" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.55</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CD7" t="n">
         <v>0.03</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CE7" t="n">
         <v>44.34</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CF7" t="n">
         <v>5.43</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CG7" t="n">
         <v>-0.92</v>
       </c>
-      <c r="CD7" t="n">
+      <c r="CH7" t="n">
         <v>0.09</v>
       </c>
-      <c r="CE7" t="n">
+      <c r="CI7" t="n">
         <v>0.31</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CJ7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CK7" t="n">
         <v>13.65</v>
       </c>
-      <c r="CH7" t="n">
+      <c r="CL7" t="n">
         <v>1.51</v>
       </c>
     </row>
@@ -2352,39 +2432,51 @@
         <v>0</v>
       </c>
       <c r="BW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY8" t="n">
         <v>92.05</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="BZ8" t="n">
         <v>10.83</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CA8" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.54</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CD8" t="n">
         <v>0.03</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CE8" t="n">
         <v>24.51</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CF8" t="n">
         <v>2.92</v>
       </c>
-      <c r="CC8" t="n">
+      <c r="CG8" t="n">
         <v>-1.16</v>
       </c>
-      <c r="CD8" t="n">
+      <c r="CH8" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE8" t="n">
+      <c r="CI8" t="n">
         <v>0.19</v>
       </c>
-      <c r="CF8" t="n">
+      <c r="CJ8" t="n">
         <v>0.02</v>
       </c>
-      <c r="CG8" t="n">
+      <c r="CK8" t="n">
         <v>4.61</v>
       </c>
-      <c r="CH8" t="n">
+      <c r="CL8" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -2516,29 +2608,37 @@
       </c>
       <c r="BV9" t="inlineStr"/>
       <c r="BW9" t="n">
-        <v>112.06</v>
+        <v>2</v>
       </c>
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="n">
-        <v>0.5600000000000001</v>
+        <v>112.06</v>
       </c>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="n">
-        <v>22.29</v>
+        <v>8.92</v>
       </c>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="n">
-        <v>-1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="n">
-        <v>0.18</v>
+        <v>22.29</v>
       </c>
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="n">
         <v>3.99</v>
       </c>
-      <c r="CH9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2614,16 +2714,16 @@
         <v>0.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.36</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.2</v>
+        <v>1.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.26</v>
+        <v>6.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.96</v>
+        <v>0.59</v>
       </c>
       <c r="AC10" t="n">
         <v>705.84</v>
@@ -2642,10 +2742,10 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="n">
-        <v>461.81</v>
+        <v>420.49</v>
       </c>
       <c r="AL10" t="n">
-        <v>65.73</v>
+        <v>27.09</v>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -2716,40 +2816,52 @@
         <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>91.5</v>
+        <v>3</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.65</v>
+        <v>0.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.54</v>
+        <v>108.27</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.07000000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="CA10" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CE10" t="n">
         <v>18.28</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CF10" t="n">
         <v>1.73</v>
       </c>
-      <c r="CC10" t="n">
+      <c r="CG10" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CD10" t="n">
+      <c r="CH10" t="n">
         <v>0.08</v>
       </c>
-      <c r="CE10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="CF10" t="n">
+      <c r="CI10" t="n">
         <v>0.22</v>
       </c>
-      <c r="CG10" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>4.46</v>
+      <c r="CJ10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="11">
@@ -2928,39 +3040,51 @@
         <v>0</v>
       </c>
       <c r="BW11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY11" t="n">
         <v>95.65000000000001</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="BZ11" t="n">
         <v>6.27</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CA11" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CC11" t="n">
         <v>0.55</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CD11" t="n">
         <v>0.02</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CE11" t="n">
         <v>22.65</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CF11" t="n">
         <v>3.13</v>
       </c>
-      <c r="CC11" t="n">
+      <c r="CG11" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CD11" t="n">
+      <c r="CH11" t="n">
         <v>0.11</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CI11" t="n">
         <v>0.21</v>
       </c>
-      <c r="CF11" t="n">
+      <c r="CJ11" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG11" t="n">
+      <c r="CK11" t="n">
         <v>4.59</v>
       </c>
-      <c r="CH11" t="n">
+      <c r="CL11" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -3144,39 +3268,51 @@
         <v>0</v>
       </c>
       <c r="BW12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BY12" t="n">
         <v>68.88</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="BZ12" t="n">
         <v>16.18</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CA12" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.72</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CD12" t="n">
         <v>0.05</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CE12" t="n">
         <v>30.78</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CF12" t="n">
         <v>2.77</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CG12" t="n">
         <v>-1.02</v>
       </c>
-      <c r="CD12" t="n">
+      <c r="CH12" t="n">
         <v>0.08</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CI12" t="n">
         <v>0.21</v>
       </c>
-      <c r="CF12" t="n">
+      <c r="CJ12" t="n">
         <v>0.04</v>
       </c>
-      <c r="CG12" t="n">
+      <c r="CK12" t="n">
         <v>6.66</v>
       </c>
-      <c r="CH12" t="n">
+      <c r="CL12" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -3356,39 +3492,51 @@
         <v>0</v>
       </c>
       <c r="BW13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BY13" t="n">
         <v>60.87</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="BZ13" t="n">
         <v>6.61</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CA13" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.7</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CD13" t="n">
         <v>0.02</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CE13" t="n">
         <v>25.77</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CF13" t="n">
         <v>5.26</v>
       </c>
-      <c r="CC13" t="n">
+      <c r="CG13" t="n">
         <v>-0.96</v>
       </c>
-      <c r="CD13" t="n">
+      <c r="CH13" t="n">
         <v>0.12</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CI13" t="n">
         <v>0.28</v>
       </c>
-      <c r="CF13" t="n">
+      <c r="CJ13" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG13" t="n">
+      <c r="CK13" t="n">
         <v>7.21</v>
       </c>
-      <c r="CH13" t="n">
+      <c r="CL13" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -3568,39 +3716,51 @@
         <v>0</v>
       </c>
       <c r="BW14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BY14" t="n">
         <v>65.98</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="BZ14" t="n">
         <v>5.04</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CA14" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.74</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
         <v>26.1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CF14" t="n">
         <v>2.81</v>
       </c>
-      <c r="CC14" t="n">
+      <c r="CG14" t="n">
         <v>-0.93</v>
       </c>
-      <c r="CD14" t="n">
+      <c r="CH14" t="n">
         <v>0.1</v>
       </c>
-      <c r="CE14" t="n">
+      <c r="CI14" t="n">
         <v>0.26</v>
       </c>
-      <c r="CF14" t="n">
+      <c r="CJ14" t="n">
         <v>0.02</v>
       </c>
-      <c r="CG14" t="n">
+      <c r="CK14" t="n">
         <v>6.74</v>
       </c>
-      <c r="CH14" t="n">
+      <c r="CL14" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -3780,39 +3940,51 @@
         <v>0</v>
       </c>
       <c r="BW15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BY15" t="n">
         <v>75.91</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="BZ15" t="n">
         <v>12.42</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CA15" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CD15" t="n">
         <v>0.01</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CE15" t="n">
         <v>28.12</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CF15" t="n">
         <v>2.51</v>
       </c>
-      <c r="CC15" t="n">
+      <c r="CG15" t="n">
         <v>-1</v>
       </c>
-      <c r="CD15" t="n">
+      <c r="CH15" t="n">
         <v>0.08</v>
       </c>
-      <c r="CE15" t="n">
+      <c r="CI15" t="n">
         <v>0.21</v>
       </c>
-      <c r="CF15" t="n">
+      <c r="CJ15" t="n">
         <v>0.05</v>
       </c>
-      <c r="CG15" t="n">
+      <c r="CK15" t="n">
         <v>5.89</v>
       </c>
-      <c r="CH15" t="n">
+      <c r="CL15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4036,39 +4208,51 @@
         <v>0</v>
       </c>
       <c r="BW16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BY16" t="n">
         <v>37.13</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="BZ16" t="n">
         <v>3.92</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CA16" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.52</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>-0.91</v>
       </c>
       <c r="CD16" t="n">
         <v>0.04</v>
       </c>
       <c r="CE16" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CI16" t="n">
         <v>0.28</v>
       </c>
-      <c r="CF16" t="n">
+      <c r="CJ16" t="n">
         <v>0.17</v>
       </c>
-      <c r="CG16" t="n">
+      <c r="CK16" t="n">
         <v>12.86</v>
       </c>
-      <c r="CH16" t="n">
+      <c r="CL16" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -4288,39 +4472,51 @@
         <v>0</v>
       </c>
       <c r="BW17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BY17" t="n">
         <v>34.39</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="BZ17" t="n">
         <v>1.95</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CA17" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.53</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CD17" t="n">
         <v>0.03</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CE17" t="n">
         <v>47.43</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CF17" t="n">
         <v>4.13</v>
       </c>
-      <c r="CC17" t="n">
+      <c r="CG17" t="n">
         <v>-0.86</v>
       </c>
-      <c r="CD17" t="n">
+      <c r="CH17" t="n">
         <v>0.05</v>
       </c>
-      <c r="CE17" t="n">
+      <c r="CI17" t="n">
         <v>0.29</v>
       </c>
-      <c r="CF17" t="n">
+      <c r="CJ17" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG17" t="n">
+      <c r="CK17" t="n">
         <v>13.73</v>
       </c>
-      <c r="CH17" t="n">
+      <c r="CL17" t="n">
         <v>0.76</v>
       </c>
     </row>
@@ -4540,39 +4736,51 @@
         <v>0</v>
       </c>
       <c r="BW18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BY18" t="n">
         <v>35.38</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="BZ18" t="n">
         <v>3.41</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CA18" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.53</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CD18" t="n">
         <v>0.04</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CE18" t="n">
         <v>47.79</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CF18" t="n">
         <v>4.16</v>
       </c>
-      <c r="CC18" t="n">
+      <c r="CG18" t="n">
         <v>-0.88</v>
       </c>
-      <c r="CD18" t="n">
+      <c r="CH18" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE18" t="n">
+      <c r="CI18" t="n">
         <v>0.28</v>
       </c>
-      <c r="CF18" t="n">
+      <c r="CJ18" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG18" t="n">
+      <c r="CK18" t="n">
         <v>13.25</v>
       </c>
-      <c r="CH18" t="n">
+      <c r="CL18" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -4792,39 +5000,51 @@
         <v>0</v>
       </c>
       <c r="BW19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BY19" t="n">
         <v>34.58</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="BZ19" t="n">
         <v>4.01</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CA19" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.53</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CD19" t="n">
         <v>0.02</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CE19" t="n">
         <v>58.87</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CF19" t="n">
         <v>5.8</v>
       </c>
-      <c r="CC19" t="n">
+      <c r="CG19" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CD19" t="n">
+      <c r="CH19" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE19" t="n">
+      <c r="CI19" t="n">
         <v>0.23</v>
       </c>
-      <c r="CF19" t="n">
+      <c r="CJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="CG19" t="n">
+      <c r="CK19" t="n">
         <v>13.75</v>
       </c>
-      <c r="CH19" t="n">
+      <c r="CL19" t="n">
         <v>1.88</v>
       </c>
     </row>
@@ -5008,39 +5228,51 @@
         <v>0</v>
       </c>
       <c r="BW20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BY20" t="n">
         <v>80.27</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="BZ20" t="n">
         <v>8.75</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CA20" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.48</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CD20" t="n">
         <v>0.04</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CE20" t="n">
         <v>31.55</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CF20" t="n">
         <v>2.43</v>
       </c>
-      <c r="CC20" t="n">
+      <c r="CG20" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CD20" t="n">
+      <c r="CH20" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE20" t="n">
+      <c r="CI20" t="n">
         <v>0.19</v>
       </c>
-      <c r="CF20" t="n">
+      <c r="CJ20" t="n">
         <v>0.02</v>
       </c>
-      <c r="CG20" t="n">
+      <c r="CK20" t="n">
         <v>6.05</v>
       </c>
-      <c r="CH20" t="n">
+      <c r="CL20" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -5118,16 +5350,16 @@
         <v>0.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>34.73</v>
+        <v>36.83</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.74</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.18</v>
+        <v>18.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.49</v>
+        <v>3.58</v>
       </c>
       <c r="AC21" t="n">
         <v>1481.98</v>
@@ -5146,10 +5378,10 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="n">
-        <v>567.65</v>
+        <v>514.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>103.37</v>
+        <v>34.66</v>
       </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
@@ -5220,40 +5452,52 @@
         <v>0</v>
       </c>
       <c r="BW21" t="n">
-        <v>77.51000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>15.42</v>
+        <v>1.32</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.43</v>
+        <v>78.19</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.1</v>
+        <v>14.39</v>
       </c>
       <c r="CA21" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CE21" t="n">
         <v>30.55</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CF21" t="n">
         <v>2.74</v>
       </c>
-      <c r="CC21" t="n">
+      <c r="CG21" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CD21" t="n">
+      <c r="CH21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CE21" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="CF21" t="n">
+      <c r="CI21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CJ21" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG21" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="CH21" t="n">
-        <v>1.34</v>
+      <c r="CK21" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="22">
@@ -5330,16 +5574,16 @@
         <v>0.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>28.98</v>
+        <v>32.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>10.17</v>
+        <v>8.44</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.71</v>
+        <v>16.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.75</v>
+        <v>4.27</v>
       </c>
       <c r="AC22" t="n">
         <v>1332.49</v>
@@ -5358,10 +5602,10 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="n">
-        <v>498.3</v>
+        <v>511.24</v>
       </c>
       <c r="AL22" t="n">
-        <v>49.19</v>
+        <v>18.81</v>
       </c>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
@@ -5432,40 +5676,52 @@
         <v>0</v>
       </c>
       <c r="BW22" t="n">
-        <v>101.47</v>
+        <v>1.71</v>
       </c>
       <c r="BX22" t="n">
-        <v>52.75</v>
+        <v>1.11</v>
       </c>
       <c r="BY22" t="n">
-        <v>0.5</v>
+        <v>79.48</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.05</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="CA22" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CE22" t="n">
         <v>29.27</v>
       </c>
-      <c r="CB22" t="n">
+      <c r="CF22" t="n">
         <v>1.73</v>
       </c>
-      <c r="CC22" t="n">
+      <c r="CG22" t="n">
         <v>-1.12</v>
       </c>
-      <c r="CD22" t="n">
+      <c r="CH22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CE22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="CF22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="CG22" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="CH22" t="n">
-        <v>1.53</v>
+      <c r="CI22" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="23">
@@ -5644,39 +5900,51 @@
         <v>0</v>
       </c>
       <c r="BW23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BY23" t="n">
         <v>78.02</v>
       </c>
-      <c r="BX23" t="n">
+      <c r="BZ23" t="n">
         <v>10.48</v>
       </c>
-      <c r="BY23" t="n">
+      <c r="CA23" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CC23" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CC23" t="n">
-        <v>-1.08</v>
       </c>
       <c r="CD23" t="n">
         <v>0.05</v>
       </c>
       <c r="CE23" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CI23" t="n">
         <v>0.22</v>
       </c>
-      <c r="CF23" t="n">
+      <c r="CJ23" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG23" t="n">
+      <c r="CK23" t="n">
         <v>6.25</v>
       </c>
-      <c r="CH23" t="n">
+      <c r="CL23" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -5860,39 +6128,51 @@
         <v>0</v>
       </c>
       <c r="BW24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BY24" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="BX24" t="n">
+      <c r="BZ24" t="n">
         <v>5.89</v>
       </c>
-      <c r="BY24" t="n">
+      <c r="CA24" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CC24" t="n">
         <v>0.54</v>
       </c>
-      <c r="BZ24" t="n">
+      <c r="CD24" t="n">
         <v>0.02</v>
       </c>
-      <c r="CA24" t="n">
+      <c r="CE24" t="n">
         <v>43.15</v>
       </c>
-      <c r="CB24" t="n">
+      <c r="CF24" t="n">
         <v>5.79</v>
       </c>
-      <c r="CC24" t="n">
+      <c r="CG24" t="n">
         <v>-1.05</v>
       </c>
-      <c r="CD24" t="n">
+      <c r="CH24" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE24" t="n">
+      <c r="CI24" t="n">
         <v>0.15</v>
       </c>
-      <c r="CF24" t="n">
+      <c r="CJ24" t="n">
         <v>0.01</v>
       </c>
-      <c r="CG24" t="n">
+      <c r="CK24" t="n">
         <v>6.37</v>
       </c>
-      <c r="CH24" t="n">
+      <c r="CL24" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6072,39 +6352,51 @@
         <v>0</v>
       </c>
       <c r="BW25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY25" t="n">
         <v>69.55</v>
       </c>
-      <c r="BX25" t="n">
+      <c r="BZ25" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="BY25" t="n">
+      <c r="CA25" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CC25" t="n">
         <v>0.52</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="CB25" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="CC25" t="n">
-        <v>-1.06</v>
       </c>
       <c r="CD25" t="n">
         <v>0.06</v>
       </c>
       <c r="CE25" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CI25" t="n">
         <v>0.17</v>
       </c>
-      <c r="CF25" t="n">
+      <c r="CJ25" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG25" t="n">
+      <c r="CK25" t="n">
         <v>6.51</v>
       </c>
-      <c r="CH25" t="n">
+      <c r="CL25" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -6284,39 +6576,51 @@
         <v>0</v>
       </c>
       <c r="BW26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BY26" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="BX26" t="n">
+      <c r="BZ26" t="n">
         <v>6.39</v>
       </c>
-      <c r="BY26" t="n">
+      <c r="CA26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CC26" t="n">
         <v>0.55</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="CD26" t="n">
         <v>0.01</v>
       </c>
-      <c r="CA26" t="n">
+      <c r="CE26" t="n">
         <v>41.18</v>
       </c>
-      <c r="CB26" t="n">
+      <c r="CF26" t="n">
         <v>0.31</v>
       </c>
-      <c r="CC26" t="n">
+      <c r="CG26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="CD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE26" t="n">
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="n">
         <v>0.16</v>
       </c>
-      <c r="CF26" t="n">
+      <c r="CJ26" t="n">
         <v>0.01</v>
       </c>
-      <c r="CG26" t="n">
+      <c r="CK26" t="n">
         <v>6.39</v>
       </c>
-      <c r="CH26" t="n">
+      <c r="CL26" t="n">
         <v>0.44</v>
       </c>
     </row>
@@ -6496,50 +6800,64 @@
         <v>0</v>
       </c>
       <c r="BW27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BY27" t="n">
         <v>72.58</v>
       </c>
-      <c r="BX27" t="n">
+      <c r="BZ27" t="n">
         <v>4.07</v>
       </c>
-      <c r="BY27" t="n">
+      <c r="CA27" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CC27" t="n">
         <v>0.55</v>
       </c>
-      <c r="BZ27" t="n">
+      <c r="CD27" t="n">
         <v>0.03</v>
       </c>
-      <c r="CA27" t="n">
+      <c r="CE27" t="n">
         <v>41.73</v>
       </c>
-      <c r="CB27" t="n">
+      <c r="CF27" t="n">
         <v>5.19</v>
       </c>
-      <c r="CC27" t="n">
+      <c r="CG27" t="n">
         <v>-1.09</v>
       </c>
-      <c r="CD27" t="n">
+      <c r="CH27" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE27" t="n">
+      <c r="CI27" t="n">
         <v>0.15</v>
       </c>
-      <c r="CF27" t="n">
+      <c r="CJ27" t="n">
         <v>0.03</v>
       </c>
-      <c r="CG27" t="n">
+      <c r="CK27" t="n">
         <v>6.09</v>
       </c>
-      <c r="CH27" t="n">
+      <c r="CL27" t="n">
         <v>0.37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="50">
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="AI1:AJ1"/>
     <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="CI1:CJ1"/>
     <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="CA1:CB1"/>
+    <mergeCell ref="CK1:CL1"/>
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="CC1:CD1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL27"/>
+  <dimension ref="A1:CP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +736,18 @@
         </is>
       </c>
       <c r="CL1" s="1" t="n"/>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="n"/>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1179,6 +1191,26 @@
           <t>std</t>
         </is>
       </c>
+      <c r="CM2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CN2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="CO2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CP2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1459,6 +1491,18 @@
       <c r="CL4" t="n">
         <v>1.57</v>
       </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -1723,6 +1767,18 @@
       <c r="CL5" t="n">
         <v>2.09</v>
       </c>
+      <c r="CM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -1987,6 +2043,18 @@
       <c r="CL6" t="n">
         <v>1.15</v>
       </c>
+      <c r="CM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -2250,6 +2318,18 @@
       </c>
       <c r="CL7" t="n">
         <v>1.51</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2478,6 +2558,18 @@
       </c>
       <c r="CL8" t="n">
         <v>0.41</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2639,6 +2731,14 @@
         <v>3.99</v>
       </c>
       <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2863,6 +2963,18 @@
       <c r="CL10" t="n">
         <v>0.43</v>
       </c>
+      <c r="CM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -3087,6 +3199,18 @@
       <c r="CL11" t="n">
         <v>0.24</v>
       </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3315,6 +3439,18 @@
       <c r="CL12" t="n">
         <v>1.65</v>
       </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -3539,6 +3675,18 @@
       <c r="CL13" t="n">
         <v>0.8100000000000001</v>
       </c>
+      <c r="CM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -3763,6 +3911,18 @@
       <c r="CL14" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="CM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -3987,6 +4147,18 @@
       <c r="CL15" t="n">
         <v>1</v>
       </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -4255,6 +4427,18 @@
       <c r="CL16" t="n">
         <v>1.47</v>
       </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -4519,6 +4703,18 @@
       <c r="CL17" t="n">
         <v>0.76</v>
       </c>
+      <c r="CM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -4783,6 +4979,18 @@
       <c r="CL18" t="n">
         <v>1.3</v>
       </c>
+      <c r="CM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -5046,6 +5254,18 @@
       </c>
       <c r="CL19" t="n">
         <v>1.88</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5275,6 +5495,18 @@
       <c r="CL20" t="n">
         <v>0.74</v>
       </c>
+      <c r="CM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -5499,6 +5731,18 @@
       <c r="CL21" t="n">
         <v>1.18</v>
       </c>
+      <c r="CM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -5723,6 +5967,18 @@
       <c r="CL22" t="n">
         <v>0.66</v>
       </c>
+      <c r="CM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -5947,6 +6203,18 @@
       <c r="CL23" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="CM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -6175,6 +6443,18 @@
       <c r="CL24" t="n">
         <v>0.5</v>
       </c>
+      <c r="CM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -6399,6 +6679,18 @@
       <c r="CL25" t="n">
         <v>0.96</v>
       </c>
+      <c r="CM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -6623,6 +6915,18 @@
       <c r="CL26" t="n">
         <v>0.44</v>
       </c>
+      <c r="CM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -6847,9 +7151,21 @@
       <c r="CL27" t="n">
         <v>0.37</v>
       </c>
+      <c r="CM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="52">
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="AI1:AJ1"/>
@@ -6861,6 +7177,7 @@
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="CC1:CD1"/>
+    <mergeCell ref="CO1:CP1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -6884,6 +7201,7 @@
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="CM1:CN1"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="AW1:AX1"/>
     <mergeCell ref="CE1:CF1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -2940,10 +2940,10 @@
         <v>0.03</v>
       </c>
       <c r="CE10" t="n">
-        <v>18.28</v>
+        <v>18.89</v>
       </c>
       <c r="CF10" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="CG10" t="n">
         <v>-1.01</v>
@@ -2955,7 +2955,7 @@
         <v>0.22</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>4</v>
@@ -4187,7 +4187,7 @@
         <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>-3.58</v>
@@ -4404,10 +4404,10 @@
         <v>0.04</v>
       </c>
       <c r="CE16" t="n">
-        <v>51.73</v>
+        <v>53.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>11.71</v>
+        <v>7.31</v>
       </c>
       <c r="CG16" t="n">
         <v>-0.91</v>
@@ -4416,10 +4416,10 @@
         <v>0.04</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="CK16" t="n">
         <v>12.86</v>
@@ -5558,10 +5558,10 @@
         <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>-30.37</v>
+        <v>-31.27</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
         <v>12.58</v>
@@ -5636,28 +5636,28 @@
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="n">
-        <v>21.61</v>
+        <v>22.56</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.93</v>
+        <v>0.91</v>
       </c>
       <c r="BI21" t="n">
-        <v>370.64</v>
+        <v>389.95</v>
       </c>
       <c r="BJ21" t="n">
-        <v>39.1</v>
+        <v>18.56</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="BM21" t="n">
-        <v>55.19</v>
+        <v>43.13</v>
       </c>
       <c r="BN21" t="n">
-        <v>24.44</v>
+        <v>11.6</v>
       </c>
       <c r="BO21" t="n">
         <v>2000</v>
@@ -5714,10 +5714,10 @@
         <v>2.74</v>
       </c>
       <c r="CG21" t="n">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="CI21" t="n">
         <v>0.2</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP27"/>
+  <dimension ref="A1:CN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,22 +732,16 @@
       <c r="CJ1" s="1" t="n"/>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>Carea</t>
+          <t>N</t>
         </is>
       </c>
       <c r="CL1" s="1" t="n"/>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="CN1" s="1" t="n"/>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1201,16 +1195,6 @@
           <t>std</t>
         </is>
       </c>
-      <c r="CO2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="CP2" s="1" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1480,27 +1464,21 @@
         <v>0.05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.33</v>
+        <v>3.3</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.05</v>
+        <v>0.47</v>
       </c>
       <c r="CK4" t="n">
-        <v>14.01</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1756,27 +1734,21 @@
         <v>0.06</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.37</v>
+        <v>3.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="CK5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2032,27 +2004,21 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.33</v>
+        <v>3.33</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CK6" t="n">
-        <v>13.29</v>
+        <v>1</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
         <v>1</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2308,27 +2274,21 @@
         <v>0.09</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.31</v>
+        <v>3.14</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="CK7" t="n">
-        <v>13.65</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2548,27 +2508,21 @@
         <v>0.02</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.19</v>
+        <v>1.89</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="CK8" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2724,21 +2678,17 @@
       </c>
       <c r="CH9" t="inlineStr"/>
       <c r="CI9" t="n">
-        <v>0.18</v>
+        <v>1.79</v>
       </c>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="n">
-        <v>3.99</v>
+        <v>1</v>
       </c>
       <c r="CL9" t="inlineStr"/>
       <c r="CM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2952,27 +2902,21 @@
         <v>0.08</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="CK10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>1</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3188,27 +3132,21 @@
         <v>0.11</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.21</v>
+        <v>2.05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="CK11" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3428,27 +3366,21 @@
         <v>0.08</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.21</v>
+        <v>2.15</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.04</v>
+        <v>0.39</v>
       </c>
       <c r="CK12" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3664,27 +3596,21 @@
         <v>0.12</v>
       </c>
       <c r="CI13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CJ13" t="n">
         <v>0.28</v>
       </c>
-      <c r="CJ13" t="n">
-        <v>0.03</v>
-      </c>
       <c r="CK13" t="n">
-        <v>7.21</v>
+        <v>1</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3900,27 +3826,21 @@
         <v>0.1</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.26</v>
+        <v>2.59</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="CK14" t="n">
-        <v>6.74</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>1</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4136,27 +4056,21 @@
         <v>0.08</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.21</v>
+        <v>2.12</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="CK15" t="n">
-        <v>5.89</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
         <v>1</v>
       </c>
-      <c r="CM15" t="n">
-        <v>0</v>
-      </c>
       <c r="CN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4416,27 +4330,21 @@
         <v>0.04</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.25</v>
+        <v>2.46</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="CK16" t="n">
-        <v>12.86</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4692,27 +4600,21 @@
         <v>0.05</v>
       </c>
       <c r="CI17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CJ17" t="n">
         <v>0.29</v>
       </c>
-      <c r="CJ17" t="n">
-        <v>0.03</v>
-      </c>
       <c r="CK17" t="n">
-        <v>13.73</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4968,27 +4870,21 @@
         <v>0.06</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.28</v>
+        <v>2.79</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="CK18" t="n">
-        <v>13.25</v>
+        <v>1</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>1</v>
       </c>
       <c r="CN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5244,27 +5140,21 @@
         <v>0.03</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.23</v>
+        <v>2.34</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.02</v>
+        <v>0.24</v>
       </c>
       <c r="CK19" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5484,27 +5374,21 @@
         <v>0.06</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.19</v>
+        <v>1.92</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="CK20" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5720,27 +5604,21 @@
         <v>0.04</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.2</v>
+        <v>2.05</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="CK21" t="n">
-        <v>6.29</v>
+        <v>1</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5956,27 +5834,21 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.21</v>
+        <v>2.07</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="CK22" t="n">
-        <v>6.08</v>
+        <v>1</v>
       </c>
       <c r="CL22" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="CM22" t="n">
         <v>1</v>
       </c>
       <c r="CN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO22" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6192,27 +6064,21 @@
         <v>0.05</v>
       </c>
       <c r="CI23" t="n">
-        <v>0.22</v>
+        <v>2.17</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6432,27 +6298,21 @@
         <v>0.06</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.15</v>
+        <v>1.48</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="CK24" t="n">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="CM24" t="n">
         <v>0</v>
       </c>
       <c r="CN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6668,27 +6528,21 @@
         <v>0.06</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="CK25" t="n">
-        <v>6.51</v>
+        <v>1</v>
       </c>
       <c r="CL25" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="CM25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6904,27 +6758,21 @@
         <v>0</v>
       </c>
       <c r="CI26" t="n">
-        <v>0.16</v>
+        <v>1.55</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="CK26" t="n">
-        <v>6.39</v>
+        <v>1</v>
       </c>
       <c r="CL26" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="CM26" t="n">
         <v>1</v>
       </c>
       <c r="CN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,32 +6988,26 @@
         <v>0.06</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.15</v>
+        <v>1.48</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="CK27" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="CL27" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO27" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP27" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="51">
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="AI1:AJ1"/>
@@ -7177,7 +7019,6 @@
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="CC1:CD1"/>
-    <mergeCell ref="CO1:CP1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN27"/>
+  <dimension ref="A1:CP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,184 +564,190 @@
       <c r="AF1" s="1" t="n"/>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>sample-ID</t>
+          <t>Al (mg/g)</t>
         </is>
       </c>
       <c r="AH1" s="1" t="n"/>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>number of leaves</t>
+          <t>Ca (mg/g)</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="n"/>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dry matter content (mg/g)</t>
+          <t>Fe (mg/g)</t>
         </is>
       </c>
       <c r="AL1" s="1" t="n"/>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>C (mg/g)</t>
+          <t>K (mg/g)</t>
         </is>
       </c>
       <c r="AN1" s="1" t="n"/>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>N (mg/g)</t>
+          <t>Mg (mg/g)</t>
         </is>
       </c>
       <c r="AP1" s="1" t="n"/>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>P (mg/g)</t>
+          <t>Mn (mg/g)</t>
         </is>
       </c>
       <c r="AR1" s="1" t="n"/>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Al (mg/g)</t>
+          <t>Na (mg/g)</t>
         </is>
       </c>
       <c r="AT1" s="1" t="n"/>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Ca (mg/g)</t>
+          <t>P (mg/g)</t>
         </is>
       </c>
       <c r="AV1" s="1" t="n"/>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>Fe (mg/g)</t>
+          <t>S (mg/g)</t>
         </is>
       </c>
       <c r="AX1" s="1" t="n"/>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>K (mg/g)</t>
+          <t>sample-ID</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="n"/>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>Mg (mg/g)</t>
+          <t>number of leaves</t>
         </is>
       </c>
       <c r="BB1" s="1" t="n"/>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Na (mg/g)</t>
+          <t>dry matter content (mg/g)</t>
         </is>
       </c>
       <c r="BD1" s="1" t="n"/>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>S (mg/g)</t>
+          <t>C (mg/g)</t>
         </is>
       </c>
       <c r="BF1" s="1" t="n"/>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>△13C_cell</t>
+          <t>N (mg/g)</t>
         </is>
       </c>
       <c r="BH1" s="1" t="n"/>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>Ci</t>
+          <t>△13C_cell</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="n"/>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>Ci/Ca</t>
+          <t>Ci</t>
         </is>
       </c>
       <c r="BL1" s="1" t="n"/>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>iWUE (μmol/mol)</t>
+          <t>Ci/Ca</t>
         </is>
       </c>
       <c r="BN1" s="1" t="n"/>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>annual_precipitation_mm</t>
+          <t>iWUE (μmol/mol)</t>
         </is>
       </c>
       <c r="BP1" s="1" t="n"/>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>elevation_m</t>
+          <t>annual_precipitation_mm</t>
         </is>
       </c>
       <c r="BR1" s="1" t="n"/>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>mean_annual_temperature_C</t>
+          <t>elevation_m</t>
         </is>
       </c>
       <c r="BT1" s="1" t="n"/>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>mean_annual_temperature_C</t>
         </is>
       </c>
       <c r="BV1" s="1" t="n"/>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>Bloque</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="BX1" s="1" t="n"/>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (cm²/g)</t>
+          <t>Bloque</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="n"/>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>LMA g/m2</t>
+          <t>Specific leaf area (cm²/g)</t>
         </is>
       </c>
       <c r="CB1" s="1" t="n"/>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>leaf water content</t>
+          <t>LMA g/m2</t>
         </is>
       </c>
       <c r="CD1" s="1" t="n"/>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>C:N</t>
+          <t>leaf water content</t>
         </is>
       </c>
       <c r="CF1" s="1" t="n"/>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>13dC/18dO</t>
+          <t>C:N</t>
         </is>
       </c>
       <c r="CH1" s="1" t="n"/>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>Narea</t>
+          <t>13dC/18dO</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="n"/>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Narea</t>
         </is>
       </c>
       <c r="CL1" s="1" t="n"/>
       <c r="CM1" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="n"/>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="n"/>
+      <c r="CP1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr"/>
@@ -1195,6 +1201,16 @@
           <t>std</t>
         </is>
       </c>
+      <c r="CO2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="CP2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1302,112 +1318,108 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AY4" t="n">
         <v>592166.17</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AZ4" t="n">
         <v>131.93</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="BA4" t="n">
         <v>20</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
         <v>458.84</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="BD4" t="n">
         <v>40.17</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="BE4" t="n">
         <v>510.89</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="BF4" t="n">
         <v>13.98</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="BG4" t="n">
         <v>12.75</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="BH4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BI4" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BN4" t="n">
         <v>0.04</v>
       </c>
-      <c r="AT4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>288.48</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BO4" t="n">
         <v>106.54</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BP4" t="n">
         <v>11.75</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
       </c>
       <c r="BQ4" t="n">
         <v>2000</v>
@@ -1416,69 +1428,75 @@
         <v>0</v>
       </c>
       <c r="BS4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
         <v>15</v>
       </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
         <v>0.52</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
         <v>2.33</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BZ4" t="n">
         <v>1.23</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CA4" t="n">
         <v>35.39</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CB4" t="n">
         <v>4.16</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CC4" t="n">
         <v>28.59</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CD4" t="n">
         <v>3.15</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CE4" t="n">
         <v>0.54</v>
       </c>
-      <c r="CD4" t="n">
+      <c r="CF4" t="n">
         <v>0.04</v>
       </c>
-      <c r="CE4" t="n">
+      <c r="CG4" t="n">
         <v>43.02</v>
       </c>
-      <c r="CF4" t="n">
+      <c r="CH4" t="n">
         <v>6.87</v>
       </c>
-      <c r="CG4" t="n">
+      <c r="CI4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="CH4" t="n">
+      <c r="CJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="CI4" t="n">
+      <c r="CK4" t="n">
         <v>3.3</v>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CL4" t="n">
         <v>0.47</v>
       </c>
-      <c r="CK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>0</v>
-      </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1572,112 +1590,108 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AY5" t="n">
         <v>592154.89</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AZ5" t="n">
         <v>91.08</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="BA5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
         <v>436.5</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BD5" t="n">
         <v>43.22</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BE5" t="n">
         <v>512.6900000000001</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BF5" t="n">
         <v>9.93</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="BG5" t="n">
         <v>11.67</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="BH5" t="n">
         <v>1.6</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BI5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>293.36</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN5" t="n">
         <v>0.05</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>293.36</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>22.36</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BO5" t="n">
         <v>103.5</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BP5" t="n">
         <v>13.97</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
       </c>
       <c r="BQ5" t="n">
         <v>2000</v>
@@ -1686,69 +1700,75 @@
         <v>0</v>
       </c>
       <c r="BS5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
         <v>15</v>
       </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
         <v>0.52</v>
       </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
         <v>2</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BZ5" t="n">
         <v>0.87</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CA5" t="n">
         <v>35.34</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CB5" t="n">
         <v>4.79</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CC5" t="n">
         <v>28.8</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CD5" t="n">
         <v>4.17</v>
       </c>
-      <c r="CC5" t="n">
+      <c r="CE5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="CD5" t="n">
+      <c r="CF5" t="n">
         <v>0.04</v>
       </c>
-      <c r="CE5" t="n">
+      <c r="CG5" t="n">
         <v>37.95</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CH5" t="n">
         <v>4.98</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CI5" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CH5" t="n">
+      <c r="CJ5" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI5" t="n">
+      <c r="CK5" t="n">
         <v>3.74</v>
       </c>
-      <c r="CJ5" t="n">
+      <c r="CL5" t="n">
         <v>0.68</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CM5" t="n">
         <v>1</v>
       </c>
-      <c r="CL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>0</v>
-      </c>
       <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1842,112 +1862,108 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AY6" t="n">
         <v>592184.38</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AZ6" t="n">
         <v>102.74</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="BA6" t="n">
         <v>20</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
         <v>443.24</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="BD6" t="n">
         <v>46.75</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BE6" t="n">
         <v>509.58</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="BF6" t="n">
         <v>15.91</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="BG6" t="n">
         <v>13.03</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="BH6" t="n">
         <v>2.6</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BG6" t="n">
+      <c r="BI6" t="n">
         <v>17.83</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BJ6" t="n">
         <v>1.52</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BK6" t="n">
         <v>293.97</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>30.77</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
         <v>0.64</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BN6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BO6" t="n">
         <v>103.12</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BP6" t="n">
         <v>19.23</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
       </c>
       <c r="BQ6" t="n">
         <v>2000</v>
@@ -1956,69 +1972,75 @@
         <v>0</v>
       </c>
       <c r="BS6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
         <v>15</v>
       </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
         <v>0.52</v>
       </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
         <v>1.88</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BZ6" t="n">
         <v>1.13</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CA6" t="n">
         <v>36.46</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CB6" t="n">
         <v>3.96</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CC6" t="n">
         <v>27.71</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CD6" t="n">
         <v>2.96</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CE6" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="CD6" t="n">
+      <c r="CF6" t="n">
         <v>0.05</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CG6" t="n">
         <v>40.44</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CH6" t="n">
         <v>4.32</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CI6" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CH6" t="n">
+      <c r="CJ6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CK6" t="n">
         <v>3.33</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CL6" t="n">
         <v>0.5600000000000001</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>0</v>
       </c>
       <c r="CM6" t="n">
         <v>1</v>
       </c>
       <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2112,112 +2134,108 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AY7" t="n">
         <v>592154.27</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AZ7" t="n">
         <v>103.52</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="BA7" t="n">
         <v>20</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
         <v>445.05</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="BD7" t="n">
         <v>31.92</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BE7" t="n">
         <v>506.63</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BF7" t="n">
         <v>11.49</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="BG7" t="n">
         <v>13.43</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="BH7" t="n">
         <v>2.12</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BI7" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>300.04</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BD7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>300.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BO7" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BP7" t="n">
         <v>20.01</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
       </c>
       <c r="BQ7" t="n">
         <v>2000</v>
@@ -2226,69 +2244,75 @@
         <v>0</v>
       </c>
       <c r="BS7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
         <v>15</v>
       </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
         <v>0.52</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
         <v>2.13</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="BZ7" t="n">
         <v>1.13</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CA7" t="n">
         <v>35.91</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CB7" t="n">
         <v>3.67</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CC7" t="n">
         <v>28.14</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CD7" t="n">
         <v>3.01</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CE7" t="n">
         <v>0.55</v>
       </c>
-      <c r="CD7" t="n">
+      <c r="CF7" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE7" t="n">
+      <c r="CG7" t="n">
         <v>44.34</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CH7" t="n">
         <v>5.43</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CI7" t="n">
         <v>-0.92</v>
       </c>
-      <c r="CH7" t="n">
+      <c r="CJ7" t="n">
         <v>0.09</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CK7" t="n">
         <v>3.14</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CL7" t="n">
         <v>0.66</v>
       </c>
-      <c r="CK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0</v>
-      </c>
       <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
         <v>1</v>
       </c>
-      <c r="CN7" t="n">
+      <c r="CP7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,136 +2417,174 @@
       <c r="AF8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>4.79</v>
+      </c>
       <c r="AK8" t="n">
-        <v>462.21</v>
+        <v>0.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>462.21</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>25.6</v>
+      </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="n">
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="n">
         <v>21.88</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BJ8" t="n">
         <v>0.45</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BK8" t="n">
         <v>376.21</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>0.82</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BN8" t="n">
         <v>0.02</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BO8" t="n">
         <v>51.71</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BP8" t="n">
         <v>5.65</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BQ8" t="n">
         <v>2000</v>
       </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
         <v>1000</v>
       </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
         <v>19</v>
       </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
         <v>3</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="BZ8" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CA8" t="n">
         <v>92.05</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CB8" t="n">
         <v>10.83</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CC8" t="n">
         <v>10.96</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="CC8" t="n">
+      <c r="CE8" t="n">
         <v>0.54</v>
       </c>
-      <c r="CD8" t="n">
+      <c r="CF8" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE8" t="n">
+      <c r="CG8" t="n">
         <v>24.51</v>
       </c>
-      <c r="CF8" t="n">
+      <c r="CH8" t="n">
         <v>2.92</v>
       </c>
-      <c r="CG8" t="n">
+      <c r="CI8" t="n">
         <v>-1.16</v>
       </c>
-      <c r="CH8" t="n">
+      <c r="CJ8" t="n">
         <v>0.02</v>
       </c>
-      <c r="CI8" t="n">
+      <c r="CK8" t="n">
         <v>1.89</v>
       </c>
-      <c r="CJ8" t="n">
+      <c r="CL8" t="n">
         <v>0.22</v>
       </c>
-      <c r="CK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0</v>
-      </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2593,102 +2655,122 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>10.52</v>
+      </c>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="n">
-        <v>444.58</v>
+        <v>0.03</v>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>13.27</v>
+      </c>
       <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>0.13</v>
+      </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>0.19</v>
+      </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>0.96</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>1.25</v>
+      </c>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>444.58</v>
+      </c>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="n">
-        <v>23.11</v>
-      </c>
+      <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="n">
-        <v>401.28</v>
+        <v>23.11</v>
       </c>
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="n">
-        <v>0.87</v>
+        <v>401.28</v>
       </c>
       <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="n">
-        <v>36.04</v>
+        <v>0.87</v>
       </c>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="n">
-        <v>2000</v>
+        <v>36.04</v>
       </c>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="n">
-        <v>0.58</v>
+        <v>19</v>
       </c>
       <c r="BV9" t="inlineStr"/>
       <c r="BW9" t="n">
-        <v>2</v>
+        <v>0.58</v>
       </c>
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="n">
-        <v>112.06</v>
+        <v>2</v>
       </c>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="n">
-        <v>8.92</v>
+        <v>112.06</v>
       </c>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="n">
-        <v>0.5600000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="n">
-        <v>22.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="n">
-        <v>-1.02</v>
+        <v>22.29</v>
       </c>
       <c r="CH9" t="inlineStr"/>
       <c r="CI9" t="n">
-        <v>1.79</v>
+        <v>-1.02</v>
       </c>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="n">
-        <v>1</v>
+        <v>1.79</v>
       </c>
       <c r="CL9" t="inlineStr"/>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2787,136 +2869,174 @@
       <c r="AF10" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.53</v>
+      </c>
       <c r="AK10" t="n">
-        <v>420.49</v>
+        <v>0.05</v>
       </c>
       <c r="AL10" t="n">
-        <v>27.09</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.14</v>
+      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>420.49</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27.09</v>
+      </c>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="n">
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="n">
         <v>22.14</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
         <v>0.38</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BK10" t="n">
         <v>381.45</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>7.72</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BM10" t="n">
         <v>0.83</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BN10" t="n">
         <v>0.02</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BO10" t="n">
         <v>48.44</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BP10" t="n">
         <v>4.83</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BQ10" t="n">
         <v>2000</v>
       </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
         <v>1000</v>
       </c>
-      <c r="BR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
         <v>19</v>
       </c>
-      <c r="BT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU10" t="n">
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
         <v>3</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="BZ10" t="n">
         <v>0.82</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CA10" t="n">
         <v>108.27</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CB10" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CC10" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CD10" t="n">
         <v>0.73</v>
       </c>
-      <c r="CC10" t="n">
+      <c r="CE10" t="n">
         <v>0.58</v>
       </c>
-      <c r="CD10" t="n">
+      <c r="CF10" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE10" t="n">
+      <c r="CG10" t="n">
         <v>18.89</v>
       </c>
-      <c r="CF10" t="n">
+      <c r="CH10" t="n">
         <v>1.51</v>
       </c>
-      <c r="CG10" t="n">
+      <c r="CI10" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CH10" t="n">
+      <c r="CJ10" t="n">
         <v>0.08</v>
       </c>
-      <c r="CI10" t="n">
+      <c r="CK10" t="n">
         <v>2.21</v>
       </c>
-      <c r="CJ10" t="n">
+      <c r="CL10" t="n">
         <v>0.04</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>1</v>
       </c>
       <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3017,136 +3137,174 @@
       <c r="AF11" t="n">
         <v>0.04</v>
       </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.73</v>
+      </c>
       <c r="AK11" t="n">
-        <v>452.38</v>
+        <v>0.04</v>
       </c>
       <c r="AL11" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>452.38</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>16.12</v>
+      </c>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="n">
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="n">
         <v>21.05</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BJ11" t="n">
         <v>1.3</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BK11" t="n">
         <v>359.39</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>26.48</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BM11" t="n">
         <v>0.78</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BN11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BO11" t="n">
         <v>62.23</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BP11" t="n">
         <v>16.55</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BQ11" t="n">
         <v>2000</v>
       </c>
-      <c r="BP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ11" t="n">
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
         <v>1000</v>
       </c>
-      <c r="BR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS11" t="n">
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
         <v>19</v>
       </c>
-      <c r="BT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU11" t="n">
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW11" t="n">
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
         <v>2.5</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="BZ11" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CA11" t="n">
         <v>95.65000000000001</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CB11" t="n">
         <v>6.27</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CC11" t="n">
         <v>10.49</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CD11" t="n">
         <v>0.66</v>
       </c>
-      <c r="CC11" t="n">
+      <c r="CE11" t="n">
         <v>0.55</v>
       </c>
-      <c r="CD11" t="n">
+      <c r="CF11" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CG11" t="n">
         <v>22.65</v>
       </c>
-      <c r="CF11" t="n">
+      <c r="CH11" t="n">
         <v>3.13</v>
       </c>
-      <c r="CG11" t="n">
+      <c r="CI11" t="n">
         <v>-1.01</v>
       </c>
-      <c r="CH11" t="n">
+      <c r="CJ11" t="n">
         <v>0.11</v>
       </c>
-      <c r="CI11" t="n">
+      <c r="CK11" t="n">
         <v>2.05</v>
       </c>
-      <c r="CJ11" t="n">
+      <c r="CL11" t="n">
         <v>0.25</v>
       </c>
-      <c r="CK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>0</v>
-      </c>
       <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
         <v>1</v>
       </c>
-      <c r="CN11" t="n">
+      <c r="CP11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3251,136 +3409,174 @@
       <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.65</v>
+      </c>
       <c r="AK12" t="n">
-        <v>276.6</v>
+        <v>0.06</v>
       </c>
       <c r="AL12" t="n">
-        <v>45.98</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.34</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>45.98</v>
+      </c>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="n">
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="n">
         <v>17.87</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BJ12" t="n">
         <v>1.51</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BK12" t="n">
         <v>294.7</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>30.67</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BM12" t="n">
         <v>0.64</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BN12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BO12" t="n">
         <v>102.66</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BP12" t="n">
         <v>19.17</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BQ12" t="n">
         <v>4500</v>
       </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
         <v>3000</v>
       </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
         <v>10</v>
       </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
         <v>2.8</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="BZ12" t="n">
         <v>1.3</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CA12" t="n">
         <v>68.88</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CB12" t="n">
         <v>16.18</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CC12" t="n">
         <v>15.17</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CD12" t="n">
         <v>3.61</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CE12" t="n">
         <v>0.72</v>
       </c>
-      <c r="CD12" t="n">
+      <c r="CF12" t="n">
         <v>0.05</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CG12" t="n">
         <v>30.78</v>
       </c>
-      <c r="CF12" t="n">
+      <c r="CH12" t="n">
         <v>2.77</v>
       </c>
-      <c r="CG12" t="n">
+      <c r="CI12" t="n">
         <v>-1.02</v>
       </c>
-      <c r="CH12" t="n">
+      <c r="CJ12" t="n">
         <v>0.08</v>
       </c>
-      <c r="CI12" t="n">
+      <c r="CK12" t="n">
         <v>2.15</v>
       </c>
-      <c r="CJ12" t="n">
+      <c r="CL12" t="n">
         <v>0.39</v>
       </c>
-      <c r="CK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>0</v>
-      </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3481,136 +3677,174 @@
       <c r="AF13" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AG13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.2</v>
+      </c>
       <c r="AK13" t="n">
-        <v>303.57</v>
+        <v>0.06</v>
       </c>
       <c r="AL13" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>303.57</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>21.05</v>
+      </c>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="n">
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="n">
         <v>17.39</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BJ13" t="n">
         <v>2.15</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>285.13</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>43.7</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>0.62</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BN13" t="n">
         <v>0.1</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BO13" t="n">
         <v>108.64</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BP13" t="n">
         <v>27.31</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BQ13" t="n">
         <v>4500</v>
       </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
         <v>3000</v>
       </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
         <v>10</v>
       </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
         <v>3.33</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="BZ13" t="n">
         <v>0.82</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CA13" t="n">
         <v>60.87</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CB13" t="n">
         <v>6.61</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CC13" t="n">
         <v>16.58</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CD13" t="n">
         <v>1.64</v>
       </c>
-      <c r="CC13" t="n">
+      <c r="CE13" t="n">
         <v>0.7</v>
       </c>
-      <c r="CD13" t="n">
+      <c r="CF13" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CG13" t="n">
         <v>25.77</v>
       </c>
-      <c r="CF13" t="n">
+      <c r="CH13" t="n">
         <v>5.26</v>
       </c>
-      <c r="CG13" t="n">
+      <c r="CI13" t="n">
         <v>-0.96</v>
       </c>
-      <c r="CH13" t="n">
+      <c r="CJ13" t="n">
         <v>0.12</v>
       </c>
-      <c r="CI13" t="n">
+      <c r="CK13" t="n">
         <v>2.85</v>
       </c>
-      <c r="CJ13" t="n">
+      <c r="CL13" t="n">
         <v>0.28</v>
       </c>
-      <c r="CK13" t="n">
+      <c r="CM13" t="n">
         <v>1</v>
       </c>
-      <c r="CL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>0</v>
-      </c>
       <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3711,136 +3945,174 @@
       <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AK14" t="n">
-        <v>263.47</v>
+        <v>0.06</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.18</v>
+      </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>263.47</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.56</v>
+      </c>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="n">
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="n">
         <v>15.82</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BJ14" t="n">
         <v>1.32</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BK14" t="n">
         <v>253.23</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>26.77</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BM14" t="n">
         <v>0.55</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BN14" t="n">
         <v>0.06</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BO14" t="n">
         <v>128.58</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BP14" t="n">
         <v>16.73</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BQ14" t="n">
         <v>4500</v>
       </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
         <v>3000</v>
       </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
         <v>10</v>
       </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
         <v>2.67</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="BZ14" t="n">
         <v>1.53</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CA14" t="n">
         <v>65.98</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CB14" t="n">
         <v>5.04</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CC14" t="n">
         <v>15.22</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CD14" t="n">
         <v>1.21</v>
       </c>
-      <c r="CC14" t="n">
+      <c r="CE14" t="n">
         <v>0.74</v>
       </c>
-      <c r="CD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE14" t="n">
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
         <v>26.1</v>
       </c>
-      <c r="CF14" t="n">
+      <c r="CH14" t="n">
         <v>2.81</v>
       </c>
-      <c r="CG14" t="n">
+      <c r="CI14" t="n">
         <v>-0.93</v>
       </c>
-      <c r="CH14" t="n">
+      <c r="CJ14" t="n">
         <v>0.1</v>
       </c>
-      <c r="CI14" t="n">
+      <c r="CK14" t="n">
         <v>2.59</v>
       </c>
-      <c r="CJ14" t="n">
+      <c r="CL14" t="n">
         <v>0.23</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>1</v>
       </c>
       <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3941,136 +4213,174 @@
       <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AK15" t="n">
-        <v>248.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AL15" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>248.34</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>11.95</v>
+      </c>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="n">
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="n">
         <v>18.37</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BJ15" t="n">
         <v>1.66</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BK15" t="n">
         <v>304.97</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>33.73</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>0.66</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BN15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BO15" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BP15" t="n">
         <v>21.08</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BQ15" t="n">
         <v>4500</v>
       </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ15" t="n">
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
         <v>3000</v>
       </c>
-      <c r="BR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS15" t="n">
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
         <v>10</v>
       </c>
-      <c r="BT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU15" t="n">
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
         <v>0.58</v>
       </c>
-      <c r="BV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW15" t="n">
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
         <v>2.57</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="BZ15" t="n">
         <v>1.27</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CA15" t="n">
         <v>75.91</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CB15" t="n">
         <v>12.42</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CC15" t="n">
         <v>13.48</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CD15" t="n">
         <v>2.22</v>
       </c>
-      <c r="CC15" t="n">
+      <c r="CE15" t="n">
         <v>0.75</v>
       </c>
-      <c r="CD15" t="n">
+      <c r="CF15" t="n">
         <v>0.01</v>
       </c>
-      <c r="CE15" t="n">
+      <c r="CG15" t="n">
         <v>28.12</v>
       </c>
-      <c r="CF15" t="n">
+      <c r="CH15" t="n">
         <v>2.51</v>
       </c>
-      <c r="CG15" t="n">
+      <c r="CI15" t="n">
         <v>-1</v>
       </c>
-      <c r="CH15" t="n">
+      <c r="CJ15" t="n">
         <v>0.08</v>
       </c>
-      <c r="CI15" t="n">
+      <c r="CK15" t="n">
         <v>2.12</v>
       </c>
-      <c r="CJ15" t="n">
+      <c r="CL15" t="n">
         <v>0.46</v>
       </c>
-      <c r="CK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>0</v>
-      </c>
       <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
         <v>1</v>
       </c>
-      <c r="CN15" t="n">
+      <c r="CP15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4168,112 +4478,108 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>592162.27</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AZ16" t="n">
         <v>130.48</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="BA16" t="n">
         <v>20</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
         <v>479.82</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="BD16" t="n">
         <v>36.04</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="BE16" t="n">
         <v>497.47</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="BF16" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="BG16" t="n">
         <v>12.69</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="BH16" t="n">
         <v>4.66</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BI16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BN16" t="n">
         <v>0.05</v>
       </c>
-      <c r="BD16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>315.7</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>24.52</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM16" t="n">
+      <c r="BO16" t="n">
         <v>89.53</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BP16" t="n">
         <v>15.32</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
       </c>
       <c r="BQ16" t="n">
         <v>2000</v>
@@ -4282,69 +4588,75 @@
         <v>0</v>
       </c>
       <c r="BS16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
         <v>15</v>
       </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
         <v>0.72</v>
       </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
         <v>2.27</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="BZ16" t="n">
         <v>1.16</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CA16" t="n">
         <v>37.13</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CB16" t="n">
         <v>3.92</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CC16" t="n">
         <v>27.2</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CD16" t="n">
         <v>2.75</v>
       </c>
-      <c r="CC16" t="n">
+      <c r="CE16" t="n">
         <v>0.52</v>
       </c>
-      <c r="CD16" t="n">
+      <c r="CF16" t="n">
         <v>0.04</v>
       </c>
-      <c r="CE16" t="n">
+      <c r="CG16" t="n">
         <v>53.43</v>
       </c>
-      <c r="CF16" t="n">
+      <c r="CH16" t="n">
         <v>7.31</v>
       </c>
-      <c r="CG16" t="n">
+      <c r="CI16" t="n">
         <v>-0.91</v>
       </c>
-      <c r="CH16" t="n">
+      <c r="CJ16" t="n">
         <v>0.04</v>
       </c>
-      <c r="CI16" t="n">
+      <c r="CK16" t="n">
         <v>2.46</v>
       </c>
-      <c r="CJ16" t="n">
+      <c r="CL16" t="n">
         <v>0.49</v>
       </c>
-      <c r="CK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4438,112 +4750,108 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AY17" t="n">
         <v>592190.7</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AZ17" t="n">
         <v>124.79</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="BA17" t="n">
         <v>20</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
         <v>465.81</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="BD17" t="n">
         <v>30.98</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="BE17" t="n">
         <v>499.64</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="BF17" t="n">
         <v>11.64</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="BG17" t="n">
         <v>11.29</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="BH17" t="n">
         <v>0.89</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="BI17" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BN17" t="n">
         <v>0.04</v>
       </c>
-      <c r="AX17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>303.97</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM17" t="n">
+      <c r="BO17" t="n">
         <v>96.87</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BP17" t="n">
         <v>12.23</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>2000</v>
@@ -4552,69 +4860,75 @@
         <v>0</v>
       </c>
       <c r="BS17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
         <v>15</v>
       </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
         <v>0.72</v>
       </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
         <v>2.3</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="BZ17" t="n">
         <v>1.16</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CA17" t="n">
         <v>34.39</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CB17" t="n">
         <v>1.95</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CC17" t="n">
         <v>29.16</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CD17" t="n">
         <v>1.56</v>
       </c>
-      <c r="CC17" t="n">
+      <c r="CE17" t="n">
         <v>0.53</v>
       </c>
-      <c r="CD17" t="n">
+      <c r="CF17" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE17" t="n">
+      <c r="CG17" t="n">
         <v>47.43</v>
       </c>
-      <c r="CF17" t="n">
+      <c r="CH17" t="n">
         <v>4.13</v>
       </c>
-      <c r="CG17" t="n">
+      <c r="CI17" t="n">
         <v>-0.86</v>
       </c>
-      <c r="CH17" t="n">
+      <c r="CJ17" t="n">
         <v>0.05</v>
       </c>
-      <c r="CI17" t="n">
+      <c r="CK17" t="n">
         <v>2.91</v>
       </c>
-      <c r="CJ17" t="n">
+      <c r="CL17" t="n">
         <v>0.29</v>
       </c>
-      <c r="CK17" t="n">
+      <c r="CM17" t="n">
         <v>1</v>
       </c>
-      <c r="CL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>0</v>
-      </c>
       <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4708,112 +5022,108 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY18" t="n">
         <v>592235.54</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AZ18" t="n">
         <v>116.4</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="BA18" t="n">
         <v>20</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
         <v>472.77</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="BD18" t="n">
         <v>38.37</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="BE18" t="n">
         <v>504.06</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="BF18" t="n">
         <v>14.01</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="BG18" t="n">
         <v>12.12</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="BH18" t="n">
         <v>1.94</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BC18" t="n">
+      <c r="BI18" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BN18" t="n">
         <v>0.05</v>
       </c>
-      <c r="BD18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>304.58</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM18" t="n">
+      <c r="BO18" t="n">
         <v>96.48</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BP18" t="n">
         <v>13.26</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
       </c>
       <c r="BQ18" t="n">
         <v>2000</v>
@@ -4822,69 +5132,75 @@
         <v>0</v>
       </c>
       <c r="BS18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
         <v>15</v>
       </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
         <v>0.72</v>
       </c>
-      <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
         <v>2.46</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="BZ18" t="n">
         <v>1.27</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CA18" t="n">
         <v>35.38</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CB18" t="n">
         <v>3.41</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CC18" t="n">
         <v>28.51</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CD18" t="n">
         <v>2.75</v>
       </c>
-      <c r="CC18" t="n">
+      <c r="CE18" t="n">
         <v>0.53</v>
       </c>
-      <c r="CD18" t="n">
+      <c r="CF18" t="n">
         <v>0.04</v>
       </c>
-      <c r="CE18" t="n">
+      <c r="CG18" t="n">
         <v>47.79</v>
       </c>
-      <c r="CF18" t="n">
+      <c r="CH18" t="n">
         <v>4.16</v>
       </c>
-      <c r="CG18" t="n">
+      <c r="CI18" t="n">
         <v>-0.88</v>
       </c>
-      <c r="CH18" t="n">
+      <c r="CJ18" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI18" t="n">
+      <c r="CK18" t="n">
         <v>2.79</v>
       </c>
-      <c r="CJ18" t="n">
+      <c r="CL18" t="n">
         <v>0.35</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>1</v>
       </c>
       <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4978,112 +5294,108 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>592200.27</v>
+        <v>0.02</v>
       </c>
       <c r="AH19" t="n">
-        <v>117.12</v>
+        <v>0.02</v>
       </c>
       <c r="AI19" t="n">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK19" t="n">
-        <v>467.3</v>
+        <v>0.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>24.91</v>
+        <v>0.05</v>
       </c>
       <c r="AM19" t="n">
-        <v>499.05</v>
+        <v>3.75</v>
       </c>
       <c r="AN19" t="n">
-        <v>17.89</v>
+        <v>0.46</v>
       </c>
       <c r="AO19" t="n">
-        <v>10.39</v>
+        <v>1.57</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.82</v>
-      </c>
+        <v>0.47</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>0.02</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.79</v>
+        <v>0.82</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.06</v>
+        <v>0.59</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.75</v>
+        <v>592200.27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.46</v>
+        <v>117.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.57</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.02</v>
+        <v>467.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.04</v>
+        <v>24.91</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.59</v>
+        <v>499.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.26</v>
+        <v>17.89</v>
       </c>
       <c r="BG19" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI19" t="n">
         <v>18.43</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BJ19" t="n">
         <v>0.73</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BK19" t="n">
         <v>306.12</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>14.77</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BM19" t="n">
         <v>0.67</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BN19" t="n">
         <v>0.03</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BO19" t="n">
         <v>95.52</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BP19" t="n">
         <v>9.23</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0</v>
       </c>
       <c r="BQ19" t="n">
         <v>2000</v>
@@ -5092,69 +5404,75 @@
         <v>0</v>
       </c>
       <c r="BS19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
         <v>15</v>
       </c>
-      <c r="BT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU19" t="n">
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
         <v>0.72</v>
       </c>
-      <c r="BV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW19" t="n">
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
         <v>2.64</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="BZ19" t="n">
         <v>1.29</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CA19" t="n">
         <v>34.58</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CB19" t="n">
         <v>4.01</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CC19" t="n">
         <v>29.34</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CD19" t="n">
         <v>3.99</v>
       </c>
-      <c r="CC19" t="n">
+      <c r="CE19" t="n">
         <v>0.53</v>
       </c>
-      <c r="CD19" t="n">
+      <c r="CF19" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE19" t="n">
+      <c r="CG19" t="n">
         <v>58.87</v>
       </c>
-      <c r="CF19" t="n">
+      <c r="CH19" t="n">
         <v>5.8</v>
       </c>
-      <c r="CG19" t="n">
+      <c r="CI19" t="n">
         <v>-0.9</v>
       </c>
-      <c r="CH19" t="n">
+      <c r="CJ19" t="n">
         <v>0.03</v>
       </c>
-      <c r="CI19" t="n">
+      <c r="CK19" t="n">
         <v>2.34</v>
       </c>
-      <c r="CJ19" t="n">
+      <c r="CL19" t="n">
         <v>0.24</v>
       </c>
-      <c r="CK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>0</v>
-      </c>
       <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
         <v>1</v>
       </c>
-      <c r="CN19" t="n">
+      <c r="CP19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5259,136 +5577,174 @@
       <c r="AF20" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AG20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.54</v>
+      </c>
       <c r="AK20" t="n">
-        <v>517.2</v>
+        <v>0.03</v>
       </c>
       <c r="AL20" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.22</v>
+      </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
+      <c r="BC20" t="n">
+        <v>517.2</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>36.65</v>
+      </c>
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
-      <c r="BG20" t="n">
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="n">
         <v>22.85</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BJ20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BK20" t="n">
         <v>395.99</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BL20" t="n">
         <v>16.28</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BM20" t="n">
         <v>0.86</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BN20" t="n">
         <v>0.04</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BO20" t="n">
         <v>39.35</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BP20" t="n">
         <v>10.18</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BQ20" t="n">
         <v>2000</v>
       </c>
-      <c r="BP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ20" t="n">
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
         <v>1000</v>
       </c>
-      <c r="BR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS20" t="n">
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
         <v>19</v>
       </c>
-      <c r="BT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU20" t="n">
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
         <v>0.79</v>
       </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
         <v>2</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="BZ20" t="n">
         <v>0.63</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CA20" t="n">
         <v>80.27</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CB20" t="n">
         <v>8.75</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CC20" t="n">
         <v>12.58</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CD20" t="n">
         <v>1.21</v>
       </c>
-      <c r="CC20" t="n">
+      <c r="CE20" t="n">
         <v>0.48</v>
       </c>
-      <c r="CD20" t="n">
+      <c r="CF20" t="n">
         <v>0.04</v>
       </c>
-      <c r="CE20" t="n">
+      <c r="CG20" t="n">
         <v>31.55</v>
       </c>
-      <c r="CF20" t="n">
+      <c r="CH20" t="n">
         <v>2.43</v>
       </c>
-      <c r="CG20" t="n">
+      <c r="CI20" t="n">
         <v>-1.04</v>
       </c>
-      <c r="CH20" t="n">
+      <c r="CJ20" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI20" t="n">
+      <c r="CK20" t="n">
         <v>1.92</v>
       </c>
-      <c r="CJ20" t="n">
+      <c r="CL20" t="n">
         <v>0.22</v>
       </c>
-      <c r="CK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL20" t="n">
-        <v>0</v>
-      </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5489,136 +5845,174 @@
       <c r="AF21" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AG21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AK21" t="n">
-        <v>514.8</v>
+        <v>0.03</v>
       </c>
       <c r="AL21" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
+      <c r="BC21" t="n">
+        <v>514.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>34.66</v>
+      </c>
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="n">
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="n">
         <v>22.56</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BJ21" t="n">
         <v>0.91</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BK21" t="n">
         <v>389.95</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>18.56</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BM21" t="n">
         <v>0.85</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BN21" t="n">
         <v>0.04</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BO21" t="n">
         <v>43.13</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BP21" t="n">
         <v>11.6</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BQ21" t="n">
         <v>2000</v>
       </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
         <v>1000</v>
       </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS21" t="n">
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
         <v>19</v>
       </c>
-      <c r="BT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU21" t="n">
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
         <v>0.79</v>
       </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
         <v>2.8</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="BZ21" t="n">
         <v>1.32</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CA21" t="n">
         <v>78.19</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CB21" t="n">
         <v>14.39</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CC21" t="n">
         <v>13.16</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CD21" t="n">
         <v>2.25</v>
       </c>
-      <c r="CC21" t="n">
+      <c r="CE21" t="n">
         <v>0.49</v>
       </c>
-      <c r="CD21" t="n">
+      <c r="CF21" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE21" t="n">
+      <c r="CG21" t="n">
         <v>30.55</v>
       </c>
-      <c r="CF21" t="n">
+      <c r="CH21" t="n">
         <v>2.74</v>
       </c>
-      <c r="CG21" t="n">
+      <c r="CI21" t="n">
         <v>-1.07</v>
       </c>
-      <c r="CH21" t="n">
+      <c r="CJ21" t="n">
         <v>0.04</v>
       </c>
-      <c r="CI21" t="n">
+      <c r="CK21" t="n">
         <v>2.05</v>
       </c>
-      <c r="CJ21" t="n">
+      <c r="CL21" t="n">
         <v>0.26</v>
       </c>
-      <c r="CK21" t="n">
+      <c r="CM21" t="n">
         <v>1</v>
       </c>
-      <c r="CL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM21" t="n">
-        <v>0</v>
-      </c>
       <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5719,136 +6113,174 @@
       <c r="AF22" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AG22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.47</v>
+      </c>
       <c r="AK22" t="n">
-        <v>511.24</v>
+        <v>0.04</v>
       </c>
       <c r="AL22" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.24</v>
+      </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
+      <c r="BC22" t="n">
+        <v>511.24</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>18.81</v>
+      </c>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="n">
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="n">
         <v>23.05</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BJ22" t="n">
         <v>1.42</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BK22" t="n">
         <v>399.94</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>28.9</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BM22" t="n">
         <v>0.87</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BN22" t="n">
         <v>0.06</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BO22" t="n">
         <v>36.88</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BP22" t="n">
         <v>18.06</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BQ22" t="n">
         <v>2000</v>
       </c>
-      <c r="BP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="n">
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
         <v>1000</v>
       </c>
-      <c r="BR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS22" t="n">
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
         <v>19</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU22" t="n">
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
         <v>0.79</v>
       </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW22" t="n">
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
         <v>1.71</v>
       </c>
-      <c r="BX22" t="n">
+      <c r="BZ22" t="n">
         <v>1.11</v>
       </c>
-      <c r="BY22" t="n">
+      <c r="CA22" t="n">
         <v>79.48</v>
       </c>
-      <c r="BZ22" t="n">
+      <c r="CB22" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="CA22" t="n">
+      <c r="CC22" t="n">
         <v>12.72</v>
       </c>
-      <c r="CB22" t="n">
+      <c r="CD22" t="n">
         <v>1.4</v>
       </c>
-      <c r="CC22" t="n">
+      <c r="CE22" t="n">
         <v>0.49</v>
       </c>
-      <c r="CD22" t="n">
+      <c r="CF22" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE22" t="n">
+      <c r="CG22" t="n">
         <v>29.27</v>
       </c>
-      <c r="CF22" t="n">
+      <c r="CH22" t="n">
         <v>1.73</v>
       </c>
-      <c r="CG22" t="n">
+      <c r="CI22" t="n">
         <v>-1.12</v>
       </c>
-      <c r="CH22" t="n">
+      <c r="CJ22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="CI22" t="n">
+      <c r="CK22" t="n">
         <v>2.07</v>
       </c>
-      <c r="CJ22" t="n">
+      <c r="CL22" t="n">
         <v>0.16</v>
-      </c>
-      <c r="CK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL22" t="n">
-        <v>0</v>
       </c>
       <c r="CM22" t="n">
         <v>1</v>
       </c>
       <c r="CN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5949,136 +6381,174 @@
       <c r="AF23" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="AK23" t="n">
-        <v>497.57</v>
+        <v>0.04</v>
       </c>
       <c r="AL23" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="inlineStr"/>
+      <c r="BC23" t="n">
+        <v>497.57</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>47.07</v>
+      </c>
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
-      <c r="BG23" t="n">
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="n">
         <v>22.55</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BJ23" t="n">
         <v>0.99</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BK23" t="n">
         <v>389.88</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>20.01</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BM23" t="n">
         <v>0.85</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BN23" t="n">
         <v>0.04</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BO23" t="n">
         <v>43.17</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BP23" t="n">
         <v>12.5</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BQ23" t="n">
         <v>2000</v>
       </c>
-      <c r="BP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ23" t="n">
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
         <v>1000</v>
       </c>
-      <c r="BR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS23" t="n">
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
         <v>19</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU23" t="n">
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
         <v>0.79</v>
       </c>
-      <c r="BV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW23" t="n">
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
         <v>2.12</v>
       </c>
-      <c r="BX23" t="n">
+      <c r="BZ23" t="n">
         <v>1.13</v>
       </c>
-      <c r="BY23" t="n">
+      <c r="CA23" t="n">
         <v>78.02</v>
       </c>
-      <c r="BZ23" t="n">
+      <c r="CB23" t="n">
         <v>10.48</v>
       </c>
-      <c r="CA23" t="n">
+      <c r="CC23" t="n">
         <v>13.05</v>
       </c>
-      <c r="CB23" t="n">
+      <c r="CD23" t="n">
         <v>1.97</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CE23" t="n">
         <v>0.5</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CF23" t="n">
         <v>0.05</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CG23" t="n">
         <v>28.9</v>
       </c>
-      <c r="CF23" t="n">
+      <c r="CH23" t="n">
         <v>2.18</v>
       </c>
-      <c r="CG23" t="n">
+      <c r="CI23" t="n">
         <v>-1.08</v>
       </c>
-      <c r="CH23" t="n">
+      <c r="CJ23" t="n">
         <v>0.05</v>
       </c>
-      <c r="CI23" t="n">
+      <c r="CK23" t="n">
         <v>2.17</v>
       </c>
-      <c r="CJ23" t="n">
+      <c r="CL23" t="n">
         <v>0.32</v>
       </c>
-      <c r="CK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL23" t="n">
-        <v>0</v>
-      </c>
       <c r="CM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO23" t="n">
         <v>1</v>
       </c>
-      <c r="CN23" t="n">
+      <c r="CP23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6183,136 +6653,174 @@
       <c r="AF24" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AG24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.82</v>
+      </c>
       <c r="AK24" t="n">
-        <v>458.37</v>
+        <v>0.06</v>
       </c>
       <c r="AL24" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.37</v>
+      </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="inlineStr"/>
+      <c r="BC24" t="n">
+        <v>458.37</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>24.12</v>
+      </c>
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
-      <c r="BG24" t="n">
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="n">
         <v>18.8</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BJ24" t="n">
         <v>0.28</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BK24" t="n">
         <v>313.67</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>5.73</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BM24" t="n">
         <v>0.68</v>
       </c>
-      <c r="BL24" t="n">
+      <c r="BN24" t="n">
         <v>0.01</v>
       </c>
-      <c r="BM24" t="n">
+      <c r="BO24" t="n">
         <v>90.8</v>
       </c>
-      <c r="BN24" t="n">
+      <c r="BP24" t="n">
         <v>3.58</v>
       </c>
-      <c r="BO24" t="n">
+      <c r="BQ24" t="n">
         <v>4500</v>
       </c>
-      <c r="BP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ24" t="n">
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
         <v>3000</v>
       </c>
-      <c r="BR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS24" t="n">
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
         <v>10</v>
       </c>
-      <c r="BT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU24" t="n">
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
         <v>0.54</v>
       </c>
-      <c r="BV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW24" t="n">
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
         <v>1.8</v>
       </c>
-      <c r="BX24" t="n">
+      <c r="BZ24" t="n">
         <v>0.84</v>
       </c>
-      <c r="BY24" t="n">
+      <c r="CA24" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="BZ24" t="n">
+      <c r="CB24" t="n">
         <v>5.89</v>
       </c>
-      <c r="CA24" t="n">
+      <c r="CC24" t="n">
         <v>14.35</v>
       </c>
-      <c r="CB24" t="n">
+      <c r="CD24" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC24" t="n">
+      <c r="CE24" t="n">
         <v>0.54</v>
       </c>
-      <c r="CD24" t="n">
+      <c r="CF24" t="n">
         <v>0.02</v>
       </c>
-      <c r="CE24" t="n">
+      <c r="CG24" t="n">
         <v>43.15</v>
       </c>
-      <c r="CF24" t="n">
+      <c r="CH24" t="n">
         <v>5.79</v>
       </c>
-      <c r="CG24" t="n">
+      <c r="CI24" t="n">
         <v>-1.05</v>
       </c>
-      <c r="CH24" t="n">
+      <c r="CJ24" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI24" t="n">
+      <c r="CK24" t="n">
         <v>1.48</v>
       </c>
-      <c r="CJ24" t="n">
+      <c r="CL24" t="n">
         <v>0.08</v>
       </c>
-      <c r="CK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL24" t="n">
-        <v>0</v>
-      </c>
       <c r="CM24" t="n">
         <v>0</v>
       </c>
       <c r="CN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6413,136 +6921,174 @@
       <c r="AF25" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AG25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.52</v>
+      </c>
       <c r="AK25" t="n">
-        <v>484.91</v>
+        <v>0.05</v>
       </c>
       <c r="AL25" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.16</v>
+      </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr"/>
-      <c r="BD25" t="inlineStr"/>
+      <c r="BC25" t="n">
+        <v>484.91</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>63.86</v>
+      </c>
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
-      <c r="BG25" t="n">
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="n">
         <v>19.17</v>
       </c>
-      <c r="BH25" t="n">
+      <c r="BJ25" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BK25" t="n">
         <v>321.26</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>19.08</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BM25" t="n">
         <v>0.7</v>
       </c>
-      <c r="BL25" t="n">
+      <c r="BN25" t="n">
         <v>0.04</v>
       </c>
-      <c r="BM25" t="n">
+      <c r="BO25" t="n">
         <v>86.06</v>
       </c>
-      <c r="BN25" t="n">
+      <c r="BP25" t="n">
         <v>11.93</v>
       </c>
-      <c r="BO25" t="n">
+      <c r="BQ25" t="n">
         <v>4500</v>
       </c>
-      <c r="BP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ25" t="n">
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
         <v>3000</v>
       </c>
-      <c r="BR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS25" t="n">
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
         <v>10</v>
       </c>
-      <c r="BT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU25" t="n">
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
         <v>0.54</v>
       </c>
-      <c r="BV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW25" t="n">
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
         <v>2</v>
       </c>
-      <c r="BX25" t="n">
+      <c r="BZ25" t="n">
         <v>1</v>
       </c>
-      <c r="BY25" t="n">
+      <c r="CA25" t="n">
         <v>69.55</v>
       </c>
-      <c r="BZ25" t="n">
+      <c r="CB25" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="CA25" t="n">
+      <c r="CC25" t="n">
         <v>14.6</v>
       </c>
-      <c r="CB25" t="n">
+      <c r="CD25" t="n">
         <v>1.99</v>
       </c>
-      <c r="CC25" t="n">
+      <c r="CE25" t="n">
         <v>0.52</v>
       </c>
-      <c r="CD25" t="n">
+      <c r="CF25" t="n">
         <v>0.06</v>
       </c>
-      <c r="CE25" t="n">
+      <c r="CG25" t="n">
         <v>39.49</v>
       </c>
-      <c r="CF25" t="n">
+      <c r="CH25" t="n">
         <v>5.23</v>
       </c>
-      <c r="CG25" t="n">
+      <c r="CI25" t="n">
         <v>-1.06</v>
       </c>
-      <c r="CH25" t="n">
+      <c r="CJ25" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI25" t="n">
+      <c r="CK25" t="n">
         <v>1.67</v>
       </c>
-      <c r="CJ25" t="n">
+      <c r="CL25" t="n">
         <v>0.3</v>
       </c>
-      <c r="CK25" t="n">
+      <c r="CM25" t="n">
         <v>1</v>
       </c>
-      <c r="CL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM25" t="n">
-        <v>0</v>
-      </c>
       <c r="CN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6643,136 +7189,174 @@
       <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AG26" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
       <c r="AK26" t="n">
-        <v>447.24</v>
+        <v>0.05</v>
       </c>
       <c r="AL26" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
-      <c r="BD26" t="inlineStr"/>
+      <c r="BC26" t="n">
+        <v>447.24</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>11.29</v>
+      </c>
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
-      <c r="BG26" t="n">
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="n">
         <v>20.2</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BJ26" t="n">
         <v>0.83</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BK26" t="n">
         <v>342.02</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>16.9</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BM26" t="n">
         <v>0.75</v>
       </c>
-      <c r="BL26" t="n">
+      <c r="BN26" t="n">
         <v>0.04</v>
       </c>
-      <c r="BM26" t="n">
+      <c r="BO26" t="n">
         <v>73.08</v>
       </c>
-      <c r="BN26" t="n">
+      <c r="BP26" t="n">
         <v>10.56</v>
       </c>
-      <c r="BO26" t="n">
+      <c r="BQ26" t="n">
         <v>4500</v>
       </c>
-      <c r="BP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ26" t="n">
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
         <v>3000</v>
       </c>
-      <c r="BR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS26" t="n">
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
         <v>10</v>
       </c>
-      <c r="BT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU26" t="n">
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
         <v>0.54</v>
       </c>
-      <c r="BV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW26" t="n">
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
         <v>2.5</v>
       </c>
-      <c r="BX26" t="n">
+      <c r="BZ26" t="n">
         <v>0.71</v>
       </c>
-      <c r="BY26" t="n">
+      <c r="CA26" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="CB26" t="n">
         <v>6.39</v>
       </c>
-      <c r="CA26" t="n">
+      <c r="CC26" t="n">
         <v>13.9</v>
       </c>
-      <c r="CB26" t="n">
+      <c r="CD26" t="n">
         <v>1.23</v>
       </c>
-      <c r="CC26" t="n">
+      <c r="CE26" t="n">
         <v>0.55</v>
       </c>
-      <c r="CD26" t="n">
+      <c r="CF26" t="n">
         <v>0.01</v>
       </c>
-      <c r="CE26" t="n">
+      <c r="CG26" t="n">
         <v>41.18</v>
       </c>
-      <c r="CF26" t="n">
+      <c r="CH26" t="n">
         <v>0.31</v>
       </c>
-      <c r="CG26" t="n">
+      <c r="CI26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="CH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI26" t="n">
+      <c r="CJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK26" t="n">
         <v>1.55</v>
       </c>
-      <c r="CJ26" t="n">
+      <c r="CL26" t="n">
         <v>0.12</v>
-      </c>
-      <c r="CK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL26" t="n">
-        <v>0</v>
       </c>
       <c r="CM26" t="n">
         <v>1</v>
       </c>
       <c r="CN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6873,141 +7457,179 @@
       <c r="AF27" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AG27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AK27" t="n">
-        <v>450.2</v>
+        <v>0.06</v>
       </c>
       <c r="AL27" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.12</v>
+      </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
+      <c r="BC27" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>29.2</v>
+      </c>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
-      <c r="BG27" t="n">
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="n">
         <v>19.51</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BJ27" t="n">
         <v>1.18</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BK27" t="n">
         <v>328.17</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>24.05</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BM27" t="n">
         <v>0.72</v>
       </c>
-      <c r="BL27" t="n">
+      <c r="BN27" t="n">
         <v>0.05</v>
       </c>
-      <c r="BM27" t="n">
+      <c r="BO27" t="n">
         <v>81.73999999999999</v>
       </c>
-      <c r="BN27" t="n">
+      <c r="BP27" t="n">
         <v>15.03</v>
       </c>
-      <c r="BO27" t="n">
+      <c r="BQ27" t="n">
         <v>4500</v>
       </c>
-      <c r="BP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ27" t="n">
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
         <v>3000</v>
       </c>
-      <c r="BR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS27" t="n">
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
         <v>10</v>
       </c>
-      <c r="BT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU27" t="n">
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
         <v>0.54</v>
       </c>
-      <c r="BV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW27" t="n">
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
         <v>2.17</v>
       </c>
-      <c r="BX27" t="n">
+      <c r="BZ27" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY27" t="n">
+      <c r="CA27" t="n">
         <v>72.58</v>
       </c>
-      <c r="BZ27" t="n">
+      <c r="CB27" t="n">
         <v>4.07</v>
       </c>
-      <c r="CA27" t="n">
+      <c r="CC27" t="n">
         <v>13.81</v>
       </c>
-      <c r="CB27" t="n">
+      <c r="CD27" t="n">
         <v>0.75</v>
       </c>
-      <c r="CC27" t="n">
+      <c r="CE27" t="n">
         <v>0.55</v>
       </c>
-      <c r="CD27" t="n">
+      <c r="CF27" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE27" t="n">
+      <c r="CG27" t="n">
         <v>41.73</v>
       </c>
-      <c r="CF27" t="n">
+      <c r="CH27" t="n">
         <v>5.19</v>
       </c>
-      <c r="CG27" t="n">
+      <c r="CI27" t="n">
         <v>-1.09</v>
       </c>
-      <c r="CH27" t="n">
+      <c r="CJ27" t="n">
         <v>0.06</v>
       </c>
-      <c r="CI27" t="n">
+      <c r="CK27" t="n">
         <v>1.48</v>
       </c>
-      <c r="CJ27" t="n">
+      <c r="CL27" t="n">
         <v>0.26</v>
       </c>
-      <c r="CK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL27" t="n">
-        <v>0</v>
-      </c>
       <c r="CM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="n">
         <v>1</v>
       </c>
-      <c r="CN27" t="n">
+      <c r="CP27" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="AI1:AJ1"/>
@@ -7019,6 +7641,7 @@
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="CC1:CD1"/>
+    <mergeCell ref="CO1:CP1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -758,10 +758,10 @@
         <v>14.05</v>
       </c>
       <c r="L6" t="n">
-        <v>23.08</v>
+        <v>23.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="N6" t="n">
         <v>1.15</v>
@@ -770,16 +770,16 @@
         <v>0.14</v>
       </c>
       <c r="P6" t="n">
-        <v>20.2</v>
+        <v>20.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.97</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>18.89</v>
+        <v>18.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -870,10 +870,10 @@
         <v>8.75</v>
       </c>
       <c r="J8" t="n">
-        <v>480.48</v>
+        <v>478</v>
       </c>
       <c r="K8" t="n">
-        <v>28.38</v>
+        <v>5.31</v>
       </c>
       <c r="L8" t="n">
         <v>15.29</v>
@@ -915,10 +915,10 @@
         <v>0.87</v>
       </c>
       <c r="F9" t="n">
-        <v>88.72</v>
+        <v>99.8</v>
       </c>
       <c r="G9" t="n">
-        <v>10.65</v>
+        <v>22.43</v>
       </c>
       <c r="H9" t="n">
         <v>78.19</v>
@@ -927,10 +927,10 @@
         <v>14.39</v>
       </c>
       <c r="J9" t="n">
-        <v>476.52</v>
+        <v>480.5</v>
       </c>
       <c r="K9" t="n">
-        <v>13.88</v>
+        <v>6.22</v>
       </c>
       <c r="L9" t="n">
         <v>15.69</v>
@@ -1218,10 +1218,10 @@
         <v>3.27</v>
       </c>
       <c r="J14" t="n">
-        <v>481.32</v>
+        <v>490.56</v>
       </c>
       <c r="K14" t="n">
-        <v>27.85</v>
+        <v>10.44</v>
       </c>
       <c r="L14" t="n">
         <v>12.04</v>
@@ -1275,10 +1275,10 @@
         <v>5.12</v>
       </c>
       <c r="J15" t="n">
-        <v>485.14</v>
+        <v>486.93</v>
       </c>
       <c r="K15" t="n">
-        <v>8.49</v>
+        <v>5.09</v>
       </c>
       <c r="L15" t="n">
         <v>11.1</v>
@@ -1287,10 +1287,10 @@
         <v>1.37</v>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="P15" t="n">
         <v>8.94</v>
@@ -1342,10 +1342,10 @@
         <v>9.44</v>
       </c>
       <c r="L16" t="n">
-        <v>10.2</v>
+        <v>8.82</v>
       </c>
       <c r="M16" t="n">
-        <v>5.48</v>
+        <v>1.17</v>
       </c>
       <c r="N16" t="n">
         <v>0.43</v>
@@ -1753,10 +1753,10 @@
         <v>1.54</v>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="O23" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="P23" t="n">
         <v>11.12</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -894,10 +894,10 @@
         <v>5.16</v>
       </c>
       <c r="R8" t="n">
-        <v>31.55</v>
+        <v>31.01</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -951,10 +951,10 @@
         <v>5.44</v>
       </c>
       <c r="R9" t="n">
-        <v>30.55</v>
+        <v>31.01</v>
       </c>
       <c r="S9" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -1242,10 +1242,10 @@
         <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>40.44</v>
+        <v>40.47</v>
       </c>
       <c r="S14" t="n">
-        <v>4.32</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="15">
@@ -1293,16 +1293,16 @@
         <v>0.28</v>
       </c>
       <c r="P15" t="n">
-        <v>8.94</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>44.34</v>
+        <v>43.44</v>
       </c>
       <c r="S15" t="n">
-        <v>5.43</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="16">
@@ -1354,16 +1354,16 @@
         <v>0.17</v>
       </c>
       <c r="P16" t="n">
-        <v>23.28</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>51.73</v>
+        <v>54.22</v>
       </c>
       <c r="S16" t="n">
-        <v>11.71</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="17">
@@ -1759,10 +1759,10 @@
         <v>0.44</v>
       </c>
       <c r="P23" t="n">
-        <v>11.12</v>
+        <v>12.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.43</v>
+        <v>3.82</v>
       </c>
       <c r="R23" t="n">
         <v>28.12</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -642,10 +642,10 @@
         <v>0.42</v>
       </c>
       <c r="F4" t="n">
-        <v>96.61</v>
+        <v>36.73</v>
       </c>
       <c r="G4" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="H4" t="n">
         <v>92.05</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>82.22</v>
+        <v>22.27</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
@@ -740,10 +740,10 @@
         <v>0.36</v>
       </c>
       <c r="F6" t="n">
-        <v>93.59999999999999</v>
+        <v>33.71</v>
       </c>
       <c r="G6" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="H6" t="n">
         <v>108.27</v>
@@ -797,10 +797,10 @@
         <v>1.24</v>
       </c>
       <c r="F7" t="n">
-        <v>106.26</v>
+        <v>46.43</v>
       </c>
       <c r="G7" t="n">
-        <v>15.19</v>
+        <v>15.27</v>
       </c>
       <c r="H7" t="n">
         <v>95.65000000000001</v>
@@ -858,10 +858,10 @@
         <v>0.76</v>
       </c>
       <c r="F8" t="n">
-        <v>85.26000000000001</v>
+        <v>25.33</v>
       </c>
       <c r="G8" t="n">
-        <v>9.34</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>80.27</v>
@@ -915,10 +915,10 @@
         <v>0.87</v>
       </c>
       <c r="F9" t="n">
-        <v>99.8</v>
+        <v>39.94</v>
       </c>
       <c r="G9" t="n">
-        <v>22.43</v>
+        <v>22.55</v>
       </c>
       <c r="H9" t="n">
         <v>78.19</v>
@@ -972,10 +972,10 @@
         <v>1.35</v>
       </c>
       <c r="F10" t="n">
-        <v>82.98999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="G10" t="n">
-        <v>16.58</v>
+        <v>16.66</v>
       </c>
       <c r="H10" t="n">
         <v>79.48</v>
@@ -1029,10 +1029,10 @@
         <v>0.93</v>
       </c>
       <c r="F11" t="n">
-        <v>88.76000000000001</v>
+        <v>28.85</v>
       </c>
       <c r="G11" t="n">
-        <v>11.48</v>
+        <v>11.54</v>
       </c>
       <c r="H11" t="n">
         <v>78.02</v>
@@ -1092,10 +1092,10 @@
         <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>146.94</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>10.79</v>
+        <v>10.84</v>
       </c>
       <c r="H12" t="n">
         <v>35.67</v>
@@ -1149,10 +1149,10 @@
         <v>1.13</v>
       </c>
       <c r="F13" t="n">
-        <v>146.26</v>
+        <v>86.63</v>
       </c>
       <c r="G13" t="n">
-        <v>13.81</v>
+        <v>13.88</v>
       </c>
       <c r="H13" t="n">
         <v>36.94</v>
@@ -1206,10 +1206,10 @@
         <v>1.45</v>
       </c>
       <c r="F14" t="n">
-        <v>143.79</v>
+        <v>84.16</v>
       </c>
       <c r="G14" t="n">
-        <v>17.65</v>
+        <v>17.74</v>
       </c>
       <c r="H14" t="n">
         <v>34.5</v>
@@ -1263,10 +1263,10 @@
         <v>1.51</v>
       </c>
       <c r="F15" t="n">
-        <v>140.31</v>
+        <v>80.66</v>
       </c>
       <c r="G15" t="n">
-        <v>18.37</v>
+        <v>18.46</v>
       </c>
       <c r="H15" t="n">
         <v>36</v>
@@ -1324,10 +1324,10 @@
         <v>1.15</v>
       </c>
       <c r="F16" t="n">
-        <v>131.33</v>
+        <v>71.63</v>
       </c>
       <c r="G16" t="n">
-        <v>14.07</v>
+        <v>14.14</v>
       </c>
       <c r="H16" t="n">
         <v>36.24</v>
@@ -1381,10 +1381,10 @@
         <v>0.92</v>
       </c>
       <c r="F17" t="n">
-        <v>138.06</v>
+        <v>78.39</v>
       </c>
       <c r="G17" t="n">
-        <v>11.23</v>
+        <v>11.29</v>
       </c>
       <c r="H17" t="n">
         <v>35.42</v>
@@ -1438,10 +1438,10 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>137.71</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>12.18</v>
+        <v>12.24</v>
       </c>
       <c r="H18" t="n">
         <v>35.88</v>
@@ -1495,10 +1495,10 @@
         <v>0.66</v>
       </c>
       <c r="F19" t="n">
-        <v>136.92</v>
+        <v>77.25</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>34.37</v>
@@ -1558,10 +1558,10 @@
         <v>1.44</v>
       </c>
       <c r="F20" t="n">
-        <v>143.37</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>17.6</v>
+        <v>17.69</v>
       </c>
       <c r="H20" t="n">
         <v>68.88</v>
@@ -1615,10 +1615,10 @@
         <v>2.06</v>
       </c>
       <c r="F21" t="n">
-        <v>148.86</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>25.07</v>
+        <v>25.2</v>
       </c>
       <c r="H21" t="n">
         <v>60.87</v>
@@ -1672,10 +1672,10 @@
         <v>1.27</v>
       </c>
       <c r="F22" t="n">
-        <v>167.17</v>
+        <v>107.65</v>
       </c>
       <c r="G22" t="n">
-        <v>15.36</v>
+        <v>15.44</v>
       </c>
       <c r="H22" t="n">
         <v>65.98</v>
@@ -1729,10 +1729,10 @@
         <v>1.59</v>
       </c>
       <c r="F23" t="n">
-        <v>137.48</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>19.36</v>
+        <v>19.45</v>
       </c>
       <c r="H23" t="n">
         <v>75.91</v>
@@ -1790,10 +1790,10 @@
         <v>0.27</v>
       </c>
       <c r="F24" t="n">
-        <v>132.49</v>
+        <v>72.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
         <v>70.09999999999999</v>
@@ -1847,10 +1847,10 @@
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>128.13</v>
+        <v>68.42</v>
       </c>
       <c r="G25" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="H25" t="n">
         <v>69.55</v>
@@ -1904,10 +1904,10 @@
         <v>0.79</v>
       </c>
       <c r="F26" t="n">
-        <v>116.22</v>
+        <v>56.45</v>
       </c>
       <c r="G26" t="n">
-        <v>9.699999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="H26" t="n">
         <v>72.20999999999999</v>
@@ -1961,10 +1961,10 @@
         <v>1.13</v>
       </c>
       <c r="F27" t="n">
-        <v>124.17</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8</v>
+        <v>13.87</v>
       </c>
       <c r="H27" t="n">
         <v>72.58</v>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -50,27 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -467,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,49 +456,121 @@
           <t>δ13C (‰ v.s.V-PDB)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>iWUE (μmol/mol)</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Specific leaf area (cm²/g)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LCC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LNC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LPC</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>N:P</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>C:N</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>N:P</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>C_area</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>N_area</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>P_area</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>δ13C (‰ v.s.V-PDB)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>iWUE (μmol/mol)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Specific leaf area (cm²/g)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LCC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LNC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LPC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>N:P</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>C:N</t>
         </is>
       </c>
-      <c r="S1" s="1" t="n"/>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>N:P</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>C_area</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>N_area</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>P_area</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" s="1" t="inlineStr"/>
@@ -530,75 +581,115 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
           <t>std</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
@@ -639,49 +730,73 @@
         <v>-30.63</v>
       </c>
       <c r="E4" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="F4" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>421.37</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K4" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.42</v>
       </c>
-      <c r="F4" t="n">
-        <v>36.73</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="H4" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="Q4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="R4" t="n">
         <v>10.83</v>
       </c>
-      <c r="J4" t="n">
-        <v>421.37</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="S4" t="n">
         <v>14.36</v>
       </c>
-      <c r="L4" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="T4" t="n">
         <v>2.56</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
         <v>0.05</v>
       </c>
-      <c r="P4" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R4" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.92</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
@@ -695,35 +810,51 @@
       <c r="D5" t="n">
         <v>-31.8</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>22.59</v>
+      </c>
       <c r="F5" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>112.06</v>
+      </c>
+      <c r="G5" t="n">
+        <v>447.15</v>
+      </c>
       <c r="H5" t="n">
-        <v>112.06</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>20.06</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.96</v>
+      </c>
       <c r="J5" t="n">
-        <v>447.15</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22.29</v>
+      </c>
       <c r="L5" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>39.9</v>
+      </c>
       <c r="N5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>20.86</v>
-      </c>
+        <v>1.79</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>22.29</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -737,49 +868,73 @@
         <v>-30.88</v>
       </c>
       <c r="E6" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="F6" t="n">
+        <v>108.27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P6" t="n">
         <v>0.36</v>
       </c>
-      <c r="F6" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="H6" t="n">
-        <v>108.27</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="Q6" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="R6" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="J6" t="n">
-        <v>430.5</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="S6" t="n">
         <v>14.05</v>
       </c>
-      <c r="L6" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="T6" t="n">
         <v>1.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
         <v>0.14</v>
       </c>
-      <c r="P6" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.73</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
@@ -794,49 +949,73 @@
         <v>-29.84</v>
       </c>
       <c r="E7" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>438.34</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.24</v>
       </c>
-      <c r="F7" t="n">
-        <v>46.43</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15.27</v>
-      </c>
-      <c r="H7" t="n">
-        <v>95.65000000000001</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="Q7" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="R7" t="n">
         <v>6.27</v>
       </c>
-      <c r="J7" t="n">
-        <v>438.34</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="S7" t="n">
         <v>12.74</v>
       </c>
-      <c r="L7" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="T7" t="n">
         <v>2.69</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="U7" t="n">
         <v>0.17</v>
       </c>
-      <c r="P7" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R7" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="n">
         <v>3.13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="8">
@@ -855,49 +1034,73 @@
         <v>-31.55</v>
       </c>
       <c r="E8" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F8" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="G8" t="n">
+        <v>478</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P8" t="n">
         <v>0.76</v>
       </c>
-      <c r="F8" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>80.27</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="Q8" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="R8" t="n">
         <v>8.75</v>
       </c>
-      <c r="J8" t="n">
-        <v>478</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="S8" t="n">
         <v>5.31</v>
       </c>
-      <c r="L8" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="T8" t="n">
         <v>1.26</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="U8" t="n">
         <v>0.12</v>
       </c>
-      <c r="P8" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="R8" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
@@ -912,49 +1115,73 @@
         <v>-31.27</v>
       </c>
       <c r="E9" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="G9" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P9" t="n">
         <v>0.87</v>
       </c>
-      <c r="F9" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="G9" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="H9" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="Q9" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="R9" t="n">
         <v>14.39</v>
       </c>
-      <c r="J9" t="n">
-        <v>480.5</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="S9" t="n">
         <v>6.22</v>
       </c>
-      <c r="L9" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="T9" t="n">
         <v>1.16</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
         <v>0.2</v>
       </c>
-      <c r="P9" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="R9" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.44</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
@@ -969,49 +1196,73 @@
         <v>-31.74</v>
       </c>
       <c r="E10" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>477.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.35</v>
       </c>
-      <c r="F10" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="G10" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="H10" t="n">
-        <v>79.48</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="Q10" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="R10" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="J10" t="n">
-        <v>477.95</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="S10" t="n">
         <v>5.16</v>
       </c>
-      <c r="L10" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="T10" t="n">
         <v>0.98</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="U10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P10" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R10" t="n">
-        <v>29.27</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.73</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="11">
@@ -1026,49 +1277,73 @@
         <v>-31.27</v>
       </c>
       <c r="E11" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="G11" t="n">
+        <v>479.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P11" t="n">
         <v>0.93</v>
       </c>
-      <c r="F11" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="H11" t="n">
-        <v>78.02</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="Q11" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="R11" t="n">
         <v>10.48</v>
       </c>
-      <c r="J11" t="n">
-        <v>479.21</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="S11" t="n">
         <v>5.51</v>
       </c>
-      <c r="L11" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="T11" t="n">
         <v>1.52</v>
       </c>
-      <c r="N11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="U11" t="n">
         <v>0.13</v>
       </c>
-      <c r="P11" t="n">
-        <v>22.47</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="R11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W11" t="n">
         <v>2.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="12">
@@ -1089,49 +1364,73 @@
         <v>-26.51</v>
       </c>
       <c r="E12" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>489.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K12" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M12" t="n">
+        <v>139.17</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P12" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" t="n">
-        <v>87.31999999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="H12" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="Q12" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="R12" t="n">
         <v>4.22</v>
       </c>
-      <c r="J12" t="n">
-        <v>489.94</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="S12" t="n">
         <v>9.19</v>
       </c>
-      <c r="L12" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="T12" t="n">
         <v>1.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
         <v>0.12</v>
       </c>
-      <c r="P12" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R12" t="n">
-        <v>43.02</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="n">
         <v>6.87</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="13">
@@ -1146,49 +1445,73 @@
         <v>-26.57</v>
       </c>
       <c r="E13" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G13" t="n">
+        <v>487.69</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>133.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.13</v>
       </c>
-      <c r="F13" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="H13" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="Q13" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="R13" t="n">
         <v>3.38</v>
       </c>
-      <c r="J13" t="n">
-        <v>487.69</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="S13" t="n">
         <v>10.08</v>
       </c>
-      <c r="L13" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="T13" t="n">
         <v>1.82</v>
       </c>
-      <c r="N13" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="U13" t="n">
         <v>0.15</v>
       </c>
-      <c r="P13" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R13" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W13" t="n">
         <v>4.76</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="14">
@@ -1203,49 +1526,73 @@
         <v>-26.77</v>
       </c>
       <c r="E14" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>490.56</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>145.22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.45</v>
       </c>
-      <c r="F14" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="H14" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="Q14" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="R14" t="n">
         <v>3.27</v>
       </c>
-      <c r="J14" t="n">
-        <v>490.56</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="S14" t="n">
         <v>10.44</v>
       </c>
-      <c r="L14" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="T14" t="n">
         <v>1.6</v>
       </c>
-      <c r="N14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="U14" t="n">
         <v>0.33</v>
       </c>
-      <c r="P14" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R14" t="n">
-        <v>40.47</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W14" t="n">
         <v>4.66</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -1260,49 +1607,73 @@
         <v>-27.06</v>
       </c>
       <c r="E15" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>486.93</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K15" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M15" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.51</v>
       </c>
-      <c r="F15" t="n">
-        <v>80.66</v>
-      </c>
-      <c r="G15" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="H15" t="n">
-        <v>36</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="Q15" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="R15" t="n">
         <v>5.12</v>
       </c>
-      <c r="J15" t="n">
-        <v>486.93</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="S15" t="n">
         <v>5.09</v>
       </c>
-      <c r="L15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="T15" t="n">
         <v>1.37</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="U15" t="n">
         <v>0.28</v>
       </c>
-      <c r="P15" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R15" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="W15" t="n">
         <v>4.35</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -1321,49 +1692,73 @@
         <v>-27.79</v>
       </c>
       <c r="E16" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>472.37</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K16" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>131.99</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.15</v>
       </c>
-      <c r="F16" t="n">
-        <v>71.63</v>
-      </c>
-      <c r="G16" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>36.24</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="Q16" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="R16" t="n">
         <v>4.23</v>
       </c>
-      <c r="J16" t="n">
-        <v>472.37</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="S16" t="n">
         <v>9.44</v>
       </c>
-      <c r="L16" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="T16" t="n">
         <v>1.17</v>
       </c>
-      <c r="N16" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="U16" t="n">
         <v>0.17</v>
       </c>
-      <c r="P16" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>54.22</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W16" t="n">
         <v>6.88</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="17">
@@ -1378,49 +1773,73 @@
         <v>-27.24</v>
       </c>
       <c r="E17" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>470.86</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K17" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>133.61</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P17" t="n">
         <v>0.92</v>
       </c>
-      <c r="F17" t="n">
-        <v>78.39</v>
-      </c>
-      <c r="G17" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="H17" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="Q17" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.48</v>
       </c>
-      <c r="J17" t="n">
-        <v>470.86</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="S17" t="n">
         <v>6.79</v>
       </c>
-      <c r="L17" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="T17" t="n">
         <v>0.83</v>
       </c>
-      <c r="N17" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="U17" t="n">
         <v>0.03</v>
       </c>
-      <c r="P17" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R17" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W17" t="n">
         <v>4.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1435,49 +1854,73 @@
         <v>-27.27</v>
       </c>
       <c r="E18" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>464.64</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K18" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M18" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="H18" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="Q18" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.64</v>
       </c>
-      <c r="J18" t="n">
-        <v>464.64</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="S18" t="n">
         <v>6.03</v>
       </c>
-      <c r="L18" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="T18" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="N18" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="U18" t="n">
         <v>0.36</v>
       </c>
-      <c r="P18" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R18" t="n">
-        <v>47.79</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W18" t="n">
         <v>4.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1492,49 +1935,73 @@
         <v>-27.34</v>
       </c>
       <c r="E19" t="n">
+        <v>77.63</v>
+      </c>
+      <c r="F19" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="G19" t="n">
+        <v>469.88</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>138.18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P19" t="n">
         <v>0.66</v>
       </c>
-      <c r="F19" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="H19" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="Q19" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R19" t="n">
         <v>3.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>469.88</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="S19" t="n">
         <v>9.99</v>
       </c>
-      <c r="L19" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="T19" t="n">
         <v>0.95</v>
       </c>
-      <c r="N19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="U19" t="n">
         <v>0.66</v>
       </c>
-      <c r="P19" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R19" t="n">
-        <v>58.04</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W19" t="n">
         <v>6.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="20">
@@ -1555,49 +2022,73 @@
         <v>-26.81</v>
       </c>
       <c r="E20" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="G20" t="n">
+        <v>438.02</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.44</v>
       </c>
-      <c r="F20" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="H20" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="Q20" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R20" t="n">
         <v>16.18</v>
       </c>
-      <c r="J20" t="n">
-        <v>438.02</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="S20" t="n">
         <v>6.14</v>
       </c>
-      <c r="L20" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="T20" t="n">
         <v>1.09</v>
       </c>
-      <c r="N20" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="U20" t="n">
         <v>0.08</v>
       </c>
-      <c r="P20" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.77</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1612,49 +2103,73 @@
         <v>-26.35</v>
       </c>
       <c r="E21" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="G21" t="n">
+        <v>434.85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.06</v>
       </c>
-      <c r="F21" t="n">
-        <v>89.26000000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="Q21" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="R21" t="n">
         <v>6.61</v>
       </c>
-      <c r="J21" t="n">
-        <v>434.85</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="S21" t="n">
         <v>10.11</v>
       </c>
-      <c r="L21" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="T21" t="n">
         <v>3.63</v>
       </c>
-      <c r="N21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="U21" t="n">
         <v>0.05</v>
       </c>
-      <c r="P21" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R21" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W21" t="n">
         <v>5.26</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -1669,49 +2184,73 @@
         <v>-24.85</v>
       </c>
       <c r="E22" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="G22" t="n">
+        <v>442.68</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K22" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" t="n">
-        <v>107.65</v>
-      </c>
-      <c r="G22" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="H22" t="n">
-        <v>65.98</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="Q22" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="R22" t="n">
         <v>5.04</v>
       </c>
-      <c r="J22" t="n">
-        <v>442.68</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="S22" t="n">
         <v>6.62</v>
       </c>
-      <c r="L22" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="T22" t="n">
         <v>1.68</v>
       </c>
-      <c r="N22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="U22" t="n">
         <v>0.08</v>
       </c>
-      <c r="P22" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="R22" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.81</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="23">
@@ -1726,49 +2265,73 @@
         <v>-27.29</v>
       </c>
       <c r="E23" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="G23" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.59</v>
       </c>
-      <c r="F23" t="n">
-        <v>77.81999999999999</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="H23" t="n">
-        <v>75.91</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="Q23" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="R23" t="n">
         <v>12.42</v>
       </c>
-      <c r="J23" t="n">
-        <v>436.7</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="S23" t="n">
         <v>5.99</v>
       </c>
-      <c r="L23" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="T23" t="n">
         <v>1.54</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="U23" t="n">
         <v>0.44</v>
       </c>
-      <c r="P23" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R23" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.51</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1787,49 +2350,73 @@
         <v>-27.7</v>
       </c>
       <c r="E24" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="F24" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>444.08</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K24" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M24" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P24" t="n">
         <v>0.27</v>
       </c>
-      <c r="F24" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="Q24" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R24" t="n">
         <v>5.89</v>
       </c>
-      <c r="J24" t="n">
-        <v>444.08</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="S24" t="n">
         <v>7.83</v>
       </c>
-      <c r="L24" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="T24" t="n">
         <v>1.34</v>
       </c>
-      <c r="N24" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="U24" t="n">
         <v>0.05</v>
       </c>
-      <c r="P24" t="n">
-        <v>18.65</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R24" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W24" t="n">
         <v>5.79</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -1844,49 +2431,73 @@
         <v>-28.06</v>
       </c>
       <c r="E25" t="n">
+        <v>68.51000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="G25" t="n">
+        <v>445.46</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K25" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M25" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P25" t="n">
         <v>0.9</v>
       </c>
-      <c r="F25" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="G25" t="n">
-        <v>11</v>
-      </c>
-      <c r="H25" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="Q25" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="R25" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="J25" t="n">
-        <v>445.46</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="S25" t="n">
         <v>14.2</v>
       </c>
-      <c r="L25" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="T25" t="n">
         <v>1.77</v>
       </c>
-      <c r="N25" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="U25" t="n">
         <v>0.05</v>
       </c>
-      <c r="P25" t="n">
-        <v>18.89</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R25" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W25" t="n">
         <v>5.23</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -1901,49 +2512,73 @@
         <v>-29.03</v>
       </c>
       <c r="E26" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>460.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K26" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M26" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P26" t="n">
         <v>0.79</v>
       </c>
-      <c r="F26" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="G26" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="H26" t="n">
-        <v>72.20999999999999</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="Q26" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="R26" t="n">
         <v>6.39</v>
       </c>
-      <c r="J26" t="n">
-        <v>460.1</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="S26" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="L26" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="T26" t="n">
         <v>0.14</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="U26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P26" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W26" t="n">
         <v>0.31</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1958,70 +2593,86 @@
         <v>-28.38</v>
       </c>
       <c r="E27" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="G27" t="n">
+        <v>440.55</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.13</v>
       </c>
-      <c r="F27" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="H27" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="Q27" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="R27" t="n">
         <v>4.07</v>
       </c>
-      <c r="J27" t="n">
-        <v>440.55</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="S27" t="n">
         <v>11.17</v>
       </c>
-      <c r="L27" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="T27" t="n">
         <v>1.7</v>
       </c>
-      <c r="N27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="U27" t="n">
         <v>0.44</v>
       </c>
-      <c r="P27" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="R27" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W27" t="n">
         <v>5.19</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="9">
     <mergeCell ref="A4:A11"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A12:A19"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A20:A27"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="B24:B27"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,40 +486,52 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (cm²/g)</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>LCC</t>
+          <t>LPC</t>
         </is>
       </c>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>LCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>LPC</t>
+          <t>N_area</t>
         </is>
       </c>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>N:P</t>
+          <t>P_area</t>
         </is>
       </c>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>N:P</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>C:N</t>
         </is>
       </c>
-      <c r="S1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>LMA g/m2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="C2" s="1" t="inlineStr"/>
@@ -603,6 +615,26 @@
           <t>std</t>
         </is>
       </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -648,40 +680,52 @@
         <v>5.19</v>
       </c>
       <c r="H4" t="n">
-        <v>92.05</v>
+        <v>17.39</v>
       </c>
       <c r="I4" t="n">
-        <v>10.83</v>
+        <v>2.56</v>
       </c>
       <c r="J4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L4" t="n">
         <v>421.37</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>14.36</v>
       </c>
-      <c r="L4" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.56</v>
-      </c>
       <c r="N4" t="n">
-        <v>0.79</v>
+        <v>1.89</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="P4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R4" t="n">
         <v>21.87</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>2.18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>24.51</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>2.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
@@ -701,29 +745,37 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>112.06</v>
+        <v>20.06</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>447.15</v>
+        <v>0.96</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>20.06</v>
+        <v>447.15</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.96</v>
+        <v>1.79</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>20.86</v>
+        <v>0.09</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
         <v>22.29</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -746,40 +798,52 @@
         <v>4.43</v>
       </c>
       <c r="H6" t="n">
-        <v>108.27</v>
+        <v>23.65</v>
       </c>
       <c r="I6" t="n">
-        <v>8.869999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L6" t="n">
         <v>430.5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>14.05</v>
       </c>
-      <c r="L6" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>2.19</v>
       </c>
       <c r="O6" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R6" t="n">
         <v>20.83</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>3.48</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>18.28</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>1.73</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="7">
@@ -803,40 +867,52 @@
         <v>15.2</v>
       </c>
       <c r="H7" t="n">
-        <v>95.65000000000001</v>
+        <v>19.62</v>
       </c>
       <c r="I7" t="n">
-        <v>6.27</v>
+        <v>2.69</v>
       </c>
       <c r="J7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L7" t="n">
         <v>438.34</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>12.74</v>
       </c>
-      <c r="L7" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.69</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="P7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R7" t="n">
         <v>16.87</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>2.64</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>22.65</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>3.13</v>
+      </c>
+      <c r="V7" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -864,40 +940,52 @@
         <v>9.34</v>
       </c>
       <c r="H8" t="n">
-        <v>80.27</v>
+        <v>15.29</v>
       </c>
       <c r="I8" t="n">
-        <v>8.75</v>
+        <v>1.26</v>
       </c>
       <c r="J8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L8" t="n">
         <v>478</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>5.31</v>
       </c>
-      <c r="L8" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.26</v>
-      </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="P8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R8" t="n">
         <v>24.45</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>5.16</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>31.01</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="9">
@@ -921,40 +1009,52 @@
         <v>22.44</v>
       </c>
       <c r="H9" t="n">
-        <v>78.19</v>
+        <v>15.69</v>
       </c>
       <c r="I9" t="n">
-        <v>14.39</v>
+        <v>1.16</v>
       </c>
       <c r="J9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="n">
         <v>480.5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>6.22</v>
       </c>
-      <c r="L9" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.16</v>
-      </c>
       <c r="N9" t="n">
-        <v>0.64</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="P9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R9" t="n">
         <v>25.95</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>5.44</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>31.01</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>2.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="10">
@@ -978,40 +1078,52 @@
         <v>16.58</v>
       </c>
       <c r="H10" t="n">
-        <v>79.48</v>
+        <v>16.38</v>
       </c>
       <c r="I10" t="n">
-        <v>9.220000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="J10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L10" t="n">
         <v>477.95</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>5.16</v>
       </c>
-      <c r="L10" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.98</v>
-      </c>
       <c r="N10" t="n">
-        <v>0.73</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="P10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R10" t="n">
         <v>22.58</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>1.81</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>29.27</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -1035,40 +1147,52 @@
         <v>11.48</v>
       </c>
       <c r="H11" t="n">
-        <v>78.02</v>
+        <v>16.68</v>
       </c>
       <c r="I11" t="n">
-        <v>10.48</v>
+        <v>1.52</v>
       </c>
       <c r="J11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L11" t="n">
         <v>479.21</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>5.51</v>
       </c>
-      <c r="L11" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.77</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R11" t="n">
         <v>22.47</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>5.11</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>28.9</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>2.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="12">
@@ -1098,40 +1222,52 @@
         <v>10.75</v>
       </c>
       <c r="H12" t="n">
-        <v>35.67</v>
+        <v>11.61</v>
       </c>
       <c r="I12" t="n">
-        <v>4.22</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L12" t="n">
         <v>489.94</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>9.19</v>
       </c>
-      <c r="L12" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="N12" t="n">
-        <v>0.78</v>
+        <v>3.27</v>
       </c>
       <c r="O12" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="P12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R12" t="n">
         <v>15.07</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>2.24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>43.02</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>6.87</v>
+      </c>
+      <c r="V12" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -1155,40 +1291,52 @@
         <v>13.72</v>
       </c>
       <c r="H13" t="n">
-        <v>36.94</v>
+        <v>13.14</v>
       </c>
       <c r="I13" t="n">
-        <v>3.38</v>
+        <v>1.82</v>
       </c>
       <c r="J13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L13" t="n">
         <v>487.69</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>10.08</v>
       </c>
-      <c r="L13" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.82</v>
-      </c>
       <c r="N13" t="n">
-        <v>0.79</v>
+        <v>3.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="P13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R13" t="n">
         <v>16.83</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>1.83</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>37.7</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>4.76</v>
+      </c>
+      <c r="V13" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="14">
@@ -1212,40 +1360,52 @@
         <v>17.61</v>
       </c>
       <c r="H14" t="n">
-        <v>34.5</v>
+        <v>12.04</v>
       </c>
       <c r="I14" t="n">
-        <v>3.27</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L14" t="n">
         <v>490.56</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>10.44</v>
       </c>
-      <c r="L14" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>3.51</v>
       </c>
       <c r="O14" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="P14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R14" t="n">
         <v>9.59</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>2.28</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>40.47</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>4.66</v>
+      </c>
+      <c r="V14" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="15">
@@ -1269,40 +1429,52 @@
         <v>18.29</v>
       </c>
       <c r="H15" t="n">
-        <v>36</v>
+        <v>11.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.12</v>
+        <v>1.37</v>
       </c>
       <c r="J15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L15" t="n">
         <v>486.93</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>5.09</v>
       </c>
-      <c r="L15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>3.14</v>
       </c>
       <c r="O15" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="P15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R15" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>2.34</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>43.44</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>4.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.22</v>
       </c>
     </row>
     <row r="16">
@@ -1330,40 +1502,52 @@
         <v>13.97</v>
       </c>
       <c r="H16" t="n">
-        <v>36.24</v>
+        <v>8.82</v>
       </c>
       <c r="I16" t="n">
-        <v>4.23</v>
+        <v>1.17</v>
       </c>
       <c r="J16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L16" t="n">
         <v>472.37</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>9.44</v>
       </c>
-      <c r="L16" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="N16" t="n">
-        <v>0.43</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="P16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R16" t="n">
         <v>22.9</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>4.05</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>54.22</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>6.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1387,40 +1571,52 @@
         <v>11.13</v>
       </c>
       <c r="H17" t="n">
-        <v>35.42</v>
+        <v>9.99</v>
       </c>
       <c r="I17" t="n">
-        <v>2.48</v>
+        <v>0.83</v>
       </c>
       <c r="J17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L17" t="n">
         <v>470.86</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>6.79</v>
       </c>
-      <c r="L17" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.83</v>
-      </c>
       <c r="N17" t="n">
-        <v>0.43</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="P17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R17" t="n">
         <v>23.54</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>2.22</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>47.43</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>4.13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="18">
@@ -1444,40 +1640,52 @@
         <v>12.19</v>
       </c>
       <c r="H18" t="n">
-        <v>35.88</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L18" t="n">
         <v>464.64</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>6.03</v>
       </c>
-      <c r="L18" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="N18" t="n">
-        <v>0.88</v>
+        <v>2.73</v>
       </c>
       <c r="O18" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="P18" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R18" t="n">
         <v>12.42</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>3.68</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>47.79</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>4.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="19">
@@ -1501,40 +1709,52 @@
         <v>8.050000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>34.37</v>
+        <v>8.19</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>0.95</v>
       </c>
       <c r="J19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L19" t="n">
         <v>469.88</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>9.99</v>
       </c>
-      <c r="L19" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.95</v>
-      </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="P19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="R19" t="n">
         <v>6.34</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>5.05</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>58.04</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>6.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="20">
@@ -1564,40 +1784,52 @@
         <v>17.6</v>
       </c>
       <c r="H20" t="n">
-        <v>68.88</v>
+        <v>14.31</v>
       </c>
       <c r="I20" t="n">
-        <v>16.18</v>
+        <v>1.09</v>
       </c>
       <c r="J20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L20" t="n">
         <v>438.02</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>6.14</v>
       </c>
-      <c r="L20" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.84</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="P20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R20" t="n">
         <v>17.17</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>1.02</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>30.78</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>2.77</v>
+      </c>
+      <c r="V20" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.61</v>
       </c>
     </row>
     <row r="21">
@@ -1621,40 +1853,52 @@
         <v>25.08</v>
       </c>
       <c r="H21" t="n">
-        <v>60.87</v>
+        <v>17.47</v>
       </c>
       <c r="I21" t="n">
-        <v>6.61</v>
+        <v>3.63</v>
       </c>
       <c r="J21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L21" t="n">
         <v>434.85</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>10.11</v>
       </c>
-      <c r="L21" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.63</v>
-      </c>
       <c r="N21" t="n">
-        <v>0.8</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
       <c r="P21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R21" t="n">
         <v>21.78</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>4.15</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>25.77</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>5.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="22">
@@ -1678,40 +1922,52 @@
         <v>15.36</v>
       </c>
       <c r="H22" t="n">
-        <v>65.98</v>
+        <v>17.08</v>
       </c>
       <c r="I22" t="n">
-        <v>5.04</v>
+        <v>1.68</v>
       </c>
       <c r="J22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L22" t="n">
         <v>442.68</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>6.62</v>
       </c>
-      <c r="L22" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.68</v>
-      </c>
       <c r="N22" t="n">
-        <v>1.07</v>
+        <v>2.59</v>
       </c>
       <c r="O22" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="P22" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R22" t="n">
         <v>15.94</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.42</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>26.1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>2.81</v>
+      </c>
+      <c r="V22" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="23">
@@ -1735,40 +1991,52 @@
         <v>19.36</v>
       </c>
       <c r="H23" t="n">
-        <v>75.91</v>
+        <v>15.65</v>
       </c>
       <c r="I23" t="n">
-        <v>12.42</v>
+        <v>1.54</v>
       </c>
       <c r="J23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L23" t="n">
         <v>436.7</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>5.99</v>
       </c>
-      <c r="L23" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.54</v>
-      </c>
       <c r="N23" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="O23" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="P23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R23" t="n">
         <v>12.15</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>3.82</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>28.12</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>2.51</v>
+      </c>
+      <c r="V23" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="24">
@@ -1796,40 +2064,52 @@
         <v>3.29</v>
       </c>
       <c r="H24" t="n">
-        <v>70.09999999999999</v>
+        <v>10.43</v>
       </c>
       <c r="I24" t="n">
-        <v>5.89</v>
+        <v>1.34</v>
       </c>
       <c r="J24" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L24" t="n">
         <v>444.08</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>7.83</v>
       </c>
-      <c r="L24" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="N24" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="O24" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="P24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R24" t="n">
         <v>18.65</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>1.67</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>43.15</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>5.79</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -1853,40 +2133,52 @@
         <v>10.95</v>
       </c>
       <c r="H25" t="n">
-        <v>69.55</v>
+        <v>11.47</v>
       </c>
       <c r="I25" t="n">
-        <v>9.630000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="J25" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L25" t="n">
         <v>445.46</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>14.2</v>
       </c>
-      <c r="L25" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.77</v>
-      </c>
       <c r="N25" t="n">
-        <v>0.61</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="P25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R25" t="n">
         <v>18.89</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>1.99</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>39.49</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>5.23</v>
+      </c>
+      <c r="V25" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="26">
@@ -1910,40 +2202,52 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>72.20999999999999</v>
+        <v>11.17</v>
       </c>
       <c r="I26" t="n">
-        <v>6.39</v>
+        <v>0.14</v>
       </c>
       <c r="J26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L26" t="n">
         <v>460.1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="L26" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.14</v>
-      </c>
       <c r="N26" t="n">
-        <v>0.72</v>
+        <v>1.55</v>
       </c>
       <c r="O26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="P26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>15.57</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>1.25</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>41.18</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.31</v>
+      </c>
+      <c r="V26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="27">
@@ -1967,58 +2271,72 @@
         <v>13.8</v>
       </c>
       <c r="H27" t="n">
-        <v>72.58</v>
+        <v>10.73</v>
       </c>
       <c r="I27" t="n">
-        <v>4.07</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L27" t="n">
         <v>440.55</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>11.17</v>
       </c>
-      <c r="L27" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N27" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="O27" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="P27" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R27" t="n">
         <v>7.31</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>3.43</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>41.73</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>5.19</v>
       </c>
+      <c r="V27" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.75</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A4:A11"/>
-    <mergeCell ref="N1:O1"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A20:A27"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A20:A27"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B24:B27"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -722,10 +722,10 @@
         <v>2.92</v>
       </c>
       <c r="V4" t="n">
-        <v>10.96</v>
+        <v>109.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="5">
@@ -773,7 +773,7 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>8.92</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="W5" t="inlineStr"/>
     </row>
@@ -840,10 +840,10 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>9.279999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="W6" t="n">
-        <v>0.73</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="7">
@@ -909,10 +909,10 @@
         <v>3.13</v>
       </c>
       <c r="V7" t="n">
-        <v>10.49</v>
+        <v>104.87</v>
       </c>
       <c r="W7" t="n">
-        <v>0.66</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="8">
@@ -928,40 +928,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-31.55</v>
+        <v>-31.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="F8" t="n">
-        <v>25.62</v>
+        <v>34.24</v>
       </c>
       <c r="G8" t="n">
-        <v>9.34</v>
+        <v>22.81</v>
       </c>
       <c r="H8" t="n">
-        <v>15.29</v>
+        <v>15.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="K8" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="L8" t="n">
-        <v>478</v>
+        <v>478.45</v>
       </c>
       <c r="M8" t="n">
-        <v>5.31</v>
+        <v>7.46</v>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="P8" t="n">
         <v>0.08</v>
@@ -970,22 +970,22 @@
         <v>0.01</v>
       </c>
       <c r="R8" t="n">
-        <v>24.45</v>
+        <v>25.34</v>
       </c>
       <c r="S8" t="n">
-        <v>5.16</v>
+        <v>5.86</v>
       </c>
       <c r="T8" t="n">
-        <v>31.01</v>
+        <v>30.27</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>12.58</v>
+        <v>124.79</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="9">
@@ -997,64 +997,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-31.27</v>
+        <v>-30.96</v>
       </c>
       <c r="E9" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="F9" t="n">
-        <v>40.17</v>
+        <v>36.73</v>
       </c>
       <c r="G9" t="n">
-        <v>22.44</v>
+        <v>16.54</v>
       </c>
       <c r="H9" t="n">
-        <v>15.69</v>
+        <v>15.83</v>
       </c>
       <c r="I9" t="n">
         <v>1.16</v>
       </c>
       <c r="J9" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.2</v>
       </c>
       <c r="L9" t="n">
-        <v>480.5</v>
+        <v>479.33</v>
       </c>
       <c r="M9" t="n">
-        <v>6.22</v>
+        <v>5.57</v>
       </c>
       <c r="N9" t="n">
         <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R9" t="n">
-        <v>25.95</v>
+        <v>24.42</v>
       </c>
       <c r="S9" t="n">
-        <v>5.44</v>
+        <v>5.57</v>
       </c>
       <c r="T9" t="n">
-        <v>31.01</v>
+        <v>30.68</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V9" t="n">
-        <v>13.16</v>
+        <v>130.76</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="10">
@@ -1066,40 +1066,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-31.74</v>
+        <v>-32.15</v>
       </c>
       <c r="E10" t="n">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="F10" t="n">
-        <v>23.36</v>
+        <v>18.33</v>
       </c>
       <c r="G10" t="n">
-        <v>16.58</v>
+        <v>10.84</v>
       </c>
       <c r="H10" t="n">
-        <v>16.38</v>
+        <v>16.43</v>
       </c>
       <c r="I10" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="K10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>477.95</v>
+        <v>477.88</v>
       </c>
       <c r="M10" t="n">
-        <v>5.16</v>
+        <v>5.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="P10" t="n">
         <v>0.09</v>
@@ -1108,22 +1108,22 @@
         <v>0.01</v>
       </c>
       <c r="R10" t="n">
-        <v>22.58</v>
+        <v>23</v>
       </c>
       <c r="S10" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="T10" t="n">
-        <v>29.27</v>
+        <v>29.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>12.72</v>
+        <v>124.93</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="11">
@@ -1189,10 +1189,10 @@
         <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>13.05</v>
+        <v>130.47</v>
       </c>
       <c r="W11" t="n">
-        <v>1.97</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="12">
@@ -1264,10 +1264,10 @@
         <v>6.87</v>
       </c>
       <c r="V12" t="n">
-        <v>28.39</v>
+        <v>283.91</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>33.02</v>
       </c>
     </row>
     <row r="13">
@@ -1333,10 +1333,10 @@
         <v>4.76</v>
       </c>
       <c r="V13" t="n">
-        <v>27.27</v>
+        <v>272.72</v>
       </c>
       <c r="W13" t="n">
-        <v>2.47</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="14">
@@ -1402,10 +1402,10 @@
         <v>4.66</v>
       </c>
       <c r="V14" t="n">
-        <v>29.22</v>
+        <v>292.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2.87</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="15">
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-27.06</v>
+        <v>-26.78</v>
       </c>
       <c r="E15" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="F15" t="n">
-        <v>81.01000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>18.29</v>
+        <v>16.74</v>
       </c>
       <c r="H15" t="n">
-        <v>11.1</v>
+        <v>11.07</v>
       </c>
       <c r="I15" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="J15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="K15" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="L15" t="n">
-        <v>486.93</v>
+        <v>486.81</v>
       </c>
       <c r="M15" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="P15" t="n">
         <v>0.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="R15" t="n">
-        <v>9.359999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="T15" t="n">
-        <v>43.44</v>
+        <v>43.38</v>
       </c>
       <c r="U15" t="n">
-        <v>4.35</v>
+        <v>4.67</v>
       </c>
       <c r="V15" t="n">
-        <v>28.33</v>
+        <v>282.56</v>
       </c>
       <c r="W15" t="n">
-        <v>4.22</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="16">
@@ -1544,10 +1544,10 @@
         <v>6.88</v>
       </c>
       <c r="V16" t="n">
-        <v>27.92</v>
+        <v>279.18</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="17">
@@ -1613,10 +1613,10 @@
         <v>4.13</v>
       </c>
       <c r="V17" t="n">
-        <v>28.36</v>
+        <v>283.62</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="18">
@@ -1628,64 +1628,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-27.27</v>
+        <v>-27.39</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>78.33</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>12.19</v>
+        <v>11.46</v>
       </c>
       <c r="H18" t="n">
-        <v>9.789999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="J18" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="L18" t="n">
-        <v>464.64</v>
+        <v>464.73</v>
       </c>
       <c r="M18" t="n">
-        <v>6.03</v>
+        <v>6.29</v>
       </c>
       <c r="N18" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="P18" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0.1</v>
       </c>
       <c r="R18" t="n">
-        <v>12.42</v>
+        <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>3.81</v>
       </c>
       <c r="T18" t="n">
-        <v>47.79</v>
+        <v>47.26</v>
       </c>
       <c r="U18" t="n">
-        <v>4.16</v>
+        <v>3.86</v>
       </c>
       <c r="V18" t="n">
-        <v>28.01</v>
+        <v>277.49</v>
       </c>
       <c r="W18" t="n">
-        <v>2.07</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="19">
@@ -1751,10 +1751,10 @@
         <v>6.25</v>
       </c>
       <c r="V19" t="n">
-        <v>29.4</v>
+        <v>294.01</v>
       </c>
       <c r="W19" t="n">
-        <v>3.49</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="20">
@@ -1826,10 +1826,10 @@
         <v>2.77</v>
       </c>
       <c r="V20" t="n">
-        <v>15.17</v>
+        <v>151.75</v>
       </c>
       <c r="W20" t="n">
-        <v>3.61</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="21">
@@ -1841,40 +1841,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-26.35</v>
+        <v>-26.36</v>
       </c>
       <c r="E21" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="F21" t="n">
-        <v>89.25</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>25.08</v>
+        <v>22.89</v>
       </c>
       <c r="H21" t="n">
-        <v>17.47</v>
+        <v>17.31</v>
       </c>
       <c r="I21" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>434.85</v>
+        <v>434.66</v>
       </c>
       <c r="M21" t="n">
-        <v>10.11</v>
+        <v>9.24</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="O21" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="P21" t="n">
         <v>0.13</v>
@@ -1883,22 +1883,22 @@
         <v>0.01</v>
       </c>
       <c r="R21" t="n">
-        <v>21.78</v>
+        <v>21.41</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="T21" t="n">
-        <v>25.77</v>
+        <v>25.88</v>
       </c>
       <c r="U21" t="n">
-        <v>5.26</v>
+        <v>4.81</v>
       </c>
       <c r="V21" t="n">
-        <v>16.58</v>
+        <v>163.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.64</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="22">
@@ -1964,10 +1964,10 @@
         <v>2.81</v>
       </c>
       <c r="V22" t="n">
-        <v>15.22</v>
+        <v>152.19</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="23">
@@ -1979,64 +1979,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-27.29</v>
+        <v>-27.44</v>
       </c>
       <c r="E23" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="F23" t="n">
-        <v>77.86</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>19.36</v>
+        <v>20.52</v>
       </c>
       <c r="H23" t="n">
-        <v>15.65</v>
+        <v>15.53</v>
       </c>
       <c r="I23" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="J23" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="L23" t="n">
-        <v>436.7</v>
+        <v>437.23</v>
       </c>
       <c r="M23" t="n">
-        <v>5.99</v>
+        <v>6.37</v>
       </c>
       <c r="N23" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="P23" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>12.15</v>
+        <v>10.75</v>
       </c>
       <c r="S23" t="n">
-        <v>3.82</v>
+        <v>1.85</v>
       </c>
       <c r="T23" t="n">
-        <v>28.12</v>
+        <v>28.39</v>
       </c>
       <c r="U23" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>13.48</v>
+        <v>132.7</v>
       </c>
       <c r="W23" t="n">
-        <v>2.22</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="24">
@@ -2106,10 +2106,10 @@
         <v>5.79</v>
       </c>
       <c r="V24" t="n">
-        <v>14.35</v>
+        <v>143.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="25">
@@ -2175,10 +2175,10 @@
         <v>5.23</v>
       </c>
       <c r="V25" t="n">
-        <v>14.6</v>
+        <v>145.96</v>
       </c>
       <c r="W25" t="n">
-        <v>1.99</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="26">
@@ -2244,10 +2244,10 @@
         <v>0.31</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>139.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="27">
@@ -2313,10 +2313,10 @@
         <v>5.19</v>
       </c>
       <c r="V27" t="n">
-        <v>13.81</v>
+        <v>138.13</v>
       </c>
       <c r="W27" t="n">
-        <v>0.75</v>
+        <v>7.51</v>
       </c>
     </row>
   </sheetData>

--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -934,10 +934,10 @@
         <v>0.89</v>
       </c>
       <c r="F8" t="n">
-        <v>34.24</v>
+        <v>25.74</v>
       </c>
       <c r="G8" t="n">
-        <v>22.81</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
         <v>15.55</v>
@@ -1003,10 +1003,10 @@
         <v>0.99</v>
       </c>
       <c r="F9" t="n">
-        <v>36.73</v>
+        <v>32.91</v>
       </c>
       <c r="G9" t="n">
-        <v>16.54</v>
+        <v>12.12</v>
       </c>
       <c r="H9" t="n">
         <v>15.83</v>
